--- a/research/traditional_assets/database/data/tunisia/tunisia_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_telecom_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bvmt_sotet" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0428</v>
+        <v>-0.0187</v>
+      </c>
+      <c r="E2">
+        <v>-0.138</v>
       </c>
       <c r="G2">
-        <v>-0.1476923076923077</v>
+        <v>0.03875</v>
       </c>
       <c r="H2">
-        <v>-0.1476923076923077</v>
+        <v>0.03875</v>
       </c>
       <c r="I2">
-        <v>-0.1176923076923077</v>
+        <v>0.04361111111111111</v>
       </c>
       <c r="J2">
-        <v>-0.1162511773940345</v>
+        <v>0.0401845238095238</v>
       </c>
       <c r="K2">
-        <v>2.42</v>
+        <v>0.387</v>
       </c>
       <c r="L2">
-        <v>0.1861538461538461</v>
+        <v>0.026875</v>
       </c>
       <c r="M2">
-        <v>0.019</v>
+        <v>0.165</v>
       </c>
       <c r="N2">
-        <v>0.004175824175824176</v>
+        <v>0.03758542141230069</v>
       </c>
       <c r="O2">
-        <v>0.007851239669421488</v>
+        <v>0.4263565891472869</v>
       </c>
       <c r="P2">
-        <v>0.019</v>
+        <v>0.165</v>
       </c>
       <c r="Q2">
-        <v>0.004175824175824176</v>
+        <v>0.03758542141230069</v>
       </c>
       <c r="R2">
-        <v>0.007851239669421488</v>
+        <v>0.4263565891472869</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.509</v>
+        <v>0.35</v>
       </c>
       <c r="V2">
-        <v>0.1118681318681319</v>
+        <v>0.07972665148063782</v>
       </c>
       <c r="W2">
-        <v>0.3579881656804734</v>
+        <v>0.04121405750798722</v>
       </c>
       <c r="X2">
-        <v>0.1261758636162287</v>
+        <v>0.1905683856649812</v>
       </c>
       <c r="Y2">
-        <v>0.2318123020642447</v>
+        <v>-0.149354328156994</v>
       </c>
       <c r="Z2">
-        <v>1.479289940828402</v>
+        <v>1.146405540960115</v>
       </c>
       <c r="AA2">
-        <v>-0.1719691973284534</v>
+        <v>0.04606776075608175</v>
       </c>
       <c r="AB2">
-        <v>0.1028745857170133</v>
+        <v>0.1637775970075556</v>
       </c>
       <c r="AC2">
-        <v>-0.2748437830454667</v>
+        <v>-0.1177098362514738</v>
       </c>
       <c r="AD2">
-        <v>3.68</v>
+        <v>2.58</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.68</v>
+        <v>2.58</v>
       </c>
       <c r="AG2">
-        <v>3.171</v>
+        <v>2.23</v>
       </c>
       <c r="AH2">
-        <v>0.4471445929526124</v>
+        <v>0.3701578192252511</v>
       </c>
       <c r="AI2">
-        <v>0.2815608263198164</v>
+        <v>0.2291296625222025</v>
       </c>
       <c r="AJ2">
-        <v>0.4106980961015413</v>
+        <v>0.3368580060422961</v>
       </c>
       <c r="AK2">
-        <v>0.2524480534989252</v>
+        <v>0.2043996333638863</v>
       </c>
       <c r="AL2">
-        <v>0.555</v>
+        <v>0.462</v>
       </c>
       <c r="AM2">
-        <v>-3.825</v>
+        <v>0.242</v>
       </c>
       <c r="AN2">
-        <v>-3.572815533980583</v>
+        <v>2.457142857142857</v>
       </c>
       <c r="AO2">
-        <v>-2.756756756756757</v>
+        <v>1.359307359307359</v>
       </c>
       <c r="AP2">
-        <v>-3.078640776699029</v>
+        <v>2.123809523809524</v>
       </c>
       <c r="AQ2">
-        <v>0.4</v>
+        <v>2.595041322314049</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0428</v>
+        <v>-0.0187</v>
+      </c>
+      <c r="E3">
+        <v>-0.138</v>
       </c>
       <c r="G3">
-        <v>-0.1476923076923077</v>
+        <v>0.03875</v>
       </c>
       <c r="H3">
-        <v>-0.1476923076923077</v>
+        <v>0.03875</v>
       </c>
       <c r="I3">
-        <v>-0.1176923076923077</v>
+        <v>0.04361111111111111</v>
       </c>
       <c r="J3">
-        <v>-0.1162511773940345</v>
+        <v>0.0401845238095238</v>
       </c>
       <c r="K3">
-        <v>2.42</v>
+        <v>0.387</v>
       </c>
       <c r="L3">
-        <v>0.1861538461538461</v>
+        <v>0.026875</v>
       </c>
       <c r="M3">
-        <v>0.019</v>
+        <v>0.165</v>
       </c>
       <c r="N3">
-        <v>0.004175824175824176</v>
+        <v>0.03758542141230069</v>
       </c>
       <c r="O3">
-        <v>0.007851239669421488</v>
+        <v>0.4263565891472869</v>
       </c>
       <c r="P3">
-        <v>0.019</v>
+        <v>0.165</v>
       </c>
       <c r="Q3">
-        <v>0.004175824175824176</v>
+        <v>0.03758542141230069</v>
       </c>
       <c r="R3">
-        <v>0.007851239669421488</v>
+        <v>0.4263565891472869</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +772,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.509</v>
+        <v>0.35</v>
       </c>
       <c r="V3">
-        <v>0.1118681318681319</v>
+        <v>0.07972665148063782</v>
       </c>
       <c r="W3">
-        <v>0.3579881656804734</v>
+        <v>0.04121405750798722</v>
       </c>
       <c r="X3">
-        <v>0.1261758636162287</v>
+        <v>0.1905683856649812</v>
       </c>
       <c r="Y3">
-        <v>0.2318123020642447</v>
+        <v>-0.149354328156994</v>
       </c>
       <c r="Z3">
-        <v>1.479289940828402</v>
+        <v>1.146405540960115</v>
       </c>
       <c r="AA3">
-        <v>-0.1719691973284534</v>
+        <v>0.04606776075608175</v>
       </c>
       <c r="AB3">
-        <v>0.1028745857170133</v>
+        <v>0.1637775970075556</v>
       </c>
       <c r="AC3">
-        <v>-0.2748437830454667</v>
+        <v>-0.1177098362514738</v>
       </c>
       <c r="AD3">
-        <v>3.68</v>
+        <v>2.58</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.68</v>
+        <v>2.58</v>
       </c>
       <c r="AG3">
-        <v>3.171</v>
+        <v>2.23</v>
       </c>
       <c r="AH3">
-        <v>0.4471445929526124</v>
+        <v>0.3701578192252511</v>
       </c>
       <c r="AI3">
-        <v>0.2815608263198164</v>
+        <v>0.2291296625222025</v>
       </c>
       <c r="AJ3">
-        <v>0.4106980961015413</v>
+        <v>0.3368580060422961</v>
       </c>
       <c r="AK3">
-        <v>0.2524480534989252</v>
+        <v>0.2043996333638863</v>
       </c>
       <c r="AL3">
-        <v>0.555</v>
+        <v>0.462</v>
       </c>
       <c r="AM3">
-        <v>-3.825</v>
+        <v>0.242</v>
       </c>
       <c r="AN3">
-        <v>-3.572815533980583</v>
+        <v>2.457142857142857</v>
       </c>
       <c r="AO3">
-        <v>-2.756756756756757</v>
+        <v>1.359307359307359</v>
       </c>
       <c r="AP3">
-        <v>-3.078640776699029</v>
+        <v>2.123809523809524</v>
       </c>
       <c r="AQ3">
+        <v>2.595041322314049</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Société Tunisienne d'Entreprises de Télécommunications S.A. (BVMT:SOTET)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BVMT:SOTET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Telecom. Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.370157819225251</v>
+      </c>
+      <c r="F2">
+        <v>0.03</v>
+      </c>
+      <c r="G2">
+        <v>4.39</v>
+      </c>
+      <c r="H2">
+        <v>8.33309141976558</v>
+      </c>
+      <c r="I2">
+        <v>6.62</v>
+      </c>
+      <c r="J2">
+        <v>8.19219141976558</v>
+      </c>
+      <c r="K2">
+        <v>2.58</v>
+      </c>
+      <c r="L2">
+        <v>0.2091</v>
+      </c>
+      <c r="M2">
+        <v>0.163777597007556</v>
+      </c>
+      <c r="N2">
+        <v>0.139792719749424</v>
+      </c>
+      <c r="O2">
+        <v>0.118191720183486</v>
+      </c>
+      <c r="P2">
+        <v>0.04675</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.190568385664981</v>
+      </c>
+      <c r="T2">
+        <v>0.142670329638581</v>
+      </c>
+      <c r="U2">
+        <v>0.80485587712551</v>
+      </c>
+      <c r="V2">
+        <v>0.550843608846964</v>
+      </c>
+      <c r="W2">
+        <v>5.304117212295123</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>4.39</v>
+      </c>
+      <c r="AB2">
+        <v>0.1885659159339335</v>
+      </c>
+      <c r="AC2">
+        <v>0.1390490825688074</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1.05</v>
+      </c>
+      <c r="AH2">
+        <v>0.989</v>
+      </c>
+      <c r="AI2">
+        <v>0.3070000000000002</v>
+      </c>
+      <c r="AJ2">
+        <v>2.58</v>
+      </c>
+      <c r="AK2">
+        <v>2.58</v>
+      </c>
+      <c r="AL2">
+        <v>0.462</v>
+      </c>
+      <c r="AM2">
+        <v>2.58</v>
+      </c>
+      <c r="AN2">
+        <v>0.35</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1400096632339766</v>
+      </c>
+      <c r="C2">
+        <v>8.524631411205723</v>
+      </c>
+      <c r="D2">
+        <v>8.174631411205723</v>
+      </c>
+      <c r="E2">
+        <v>-2.58</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.35</v>
+      </c>
+      <c r="H2">
+        <v>4.39</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.05</v>
+      </c>
+      <c r="K2">
+        <v>0.989</v>
+      </c>
+      <c r="L2">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="O2">
+        <v>0.009150000000000009</v>
+      </c>
+      <c r="P2">
+        <v>0.05185000000000005</v>
+      </c>
+      <c r="Q2">
+        <v>1.04085</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1400096632339766</v>
+      </c>
+      <c r="T2">
+        <v>0.5367336017896081</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1398582987391256</v>
+      </c>
+      <c r="C3">
+        <v>8.467175323576978</v>
+      </c>
+      <c r="D3">
+        <v>8.186875323576977</v>
+      </c>
+      <c r="E3">
+        <v>-2.5103</v>
+      </c>
+      <c r="F3">
+        <v>0.0697</v>
+      </c>
+      <c r="G3">
+        <v>0.35</v>
+      </c>
+      <c r="H3">
+        <v>4.39</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.05</v>
+      </c>
+      <c r="K3">
+        <v>0.989</v>
+      </c>
+      <c r="L3">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M3">
+        <v>0.00318529</v>
+      </c>
+      <c r="N3">
+        <v>0.05781471000000005</v>
+      </c>
+      <c r="O3">
+        <v>0.00867220650000001</v>
+      </c>
+      <c r="P3">
+        <v>0.04914250350000005</v>
+      </c>
+      <c r="Q3">
+        <v>1.0381425035</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1408786350900258</v>
+      </c>
+      <c r="T3">
+        <v>0.5413419205928521</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>19.15053260456663</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1397987342442746</v>
+      </c>
+      <c r="C4">
+        <v>8.4023035731259</v>
+      </c>
+      <c r="D4">
+        <v>8.191703573125901</v>
+      </c>
+      <c r="E4">
+        <v>-2.4406</v>
+      </c>
+      <c r="F4">
+        <v>0.1394</v>
+      </c>
+      <c r="G4">
+        <v>0.35</v>
+      </c>
+      <c r="H4">
+        <v>4.39</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.05</v>
+      </c>
+      <c r="K4">
+        <v>0.989</v>
+      </c>
+      <c r="L4">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M4">
+        <v>0.00712334</v>
+      </c>
+      <c r="N4">
+        <v>0.05387666000000006</v>
+      </c>
+      <c r="O4">
+        <v>0.008081499000000009</v>
+      </c>
+      <c r="P4">
+        <v>0.04579516100000004</v>
+      </c>
+      <c r="Q4">
+        <v>1.034795161</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1417653410655864</v>
+      </c>
+      <c r="T4">
+        <v>0.5460442867186115</v>
+      </c>
+      <c r="U4">
+        <v>0.0511</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.043435</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>8.563398630417762</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1397927197494236</v>
+      </c>
+      <c r="C5">
+        <v>8.333091419765577</v>
+      </c>
+      <c r="D5">
+        <v>8.192191419765576</v>
+      </c>
+      <c r="E5">
+        <v>-2.3709</v>
+      </c>
+      <c r="F5">
+        <v>0.2091</v>
+      </c>
+      <c r="G5">
+        <v>0.35</v>
+      </c>
+      <c r="H5">
+        <v>4.39</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.05</v>
+      </c>
+      <c r="K5">
+        <v>0.989</v>
+      </c>
+      <c r="L5">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M5">
+        <v>0.0115005</v>
+      </c>
+      <c r="N5">
+        <v>0.04949950000000006</v>
+      </c>
+      <c r="O5">
+        <v>0.007424925000000009</v>
+      </c>
+      <c r="P5">
+        <v>0.04207457500000004</v>
+      </c>
+      <c r="Q5">
+        <v>1.031074575</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1426703296385811</v>
+      </c>
+      <c r="T5">
+        <v>0.5508436088469637</v>
+      </c>
+      <c r="U5">
+        <v>0.055</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.04675</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>5.304117212295123</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1402338052545727</v>
+      </c>
+      <c r="C6">
+        <v>8.227767626676121</v>
+      </c>
+      <c r="D6">
+        <v>8.156567626676122</v>
+      </c>
+      <c r="E6">
+        <v>-2.3012</v>
+      </c>
+      <c r="F6">
+        <v>0.2788</v>
+      </c>
+      <c r="G6">
+        <v>0.35</v>
+      </c>
+      <c r="H6">
+        <v>4.39</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.05</v>
+      </c>
+      <c r="K6">
+        <v>0.989</v>
+      </c>
+      <c r="L6">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M6">
+        <v>0.01954388</v>
+      </c>
+      <c r="N6">
+        <v>0.04145612000000005</v>
+      </c>
+      <c r="O6">
+        <v>0.006218418000000009</v>
+      </c>
+      <c r="P6">
+        <v>0.03523770200000004</v>
+      </c>
+      <c r="Q6">
+        <v>1.024237702</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1435941721401799</v>
+      </c>
+      <c r="T6">
+        <v>0.55574291685299</v>
+      </c>
+      <c r="U6">
+        <v>0.0701</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>3.121181669146559</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1420918407597217</v>
+      </c>
+      <c r="C7">
+        <v>8.011345560934574</v>
+      </c>
+      <c r="D7">
+        <v>8.009845560934574</v>
+      </c>
+      <c r="E7">
+        <v>-2.2315</v>
+      </c>
+      <c r="F7">
+        <v>0.3485</v>
+      </c>
+      <c r="G7">
+        <v>0.35</v>
+      </c>
+      <c r="H7">
+        <v>4.39</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.05</v>
+      </c>
+      <c r="K7">
+        <v>0.989</v>
+      </c>
+      <c r="L7">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M7">
+        <v>0.03920625</v>
+      </c>
+      <c r="N7">
+        <v>0.02179375000000005</v>
+      </c>
+      <c r="O7">
+        <v>0.003269062500000008</v>
+      </c>
+      <c r="P7">
+        <v>0.01852468750000004</v>
+      </c>
+      <c r="Q7">
+        <v>1.0075246875</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1445374639576018</v>
+      </c>
+      <c r="T7">
+        <v>0.5607453681854589</v>
+      </c>
+      <c r="U7">
+        <v>0.1125</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.095625</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>1.555874382273236</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1485754493716863</v>
+      </c>
+      <c r="C8">
+        <v>7.468564339617557</v>
+      </c>
+      <c r="D8">
+        <v>7.536764339617557</v>
+      </c>
+      <c r="E8">
+        <v>-2.1618</v>
+      </c>
+      <c r="F8">
+        <v>0.4182</v>
+      </c>
+      <c r="G8">
+        <v>0.35</v>
+      </c>
+      <c r="H8">
+        <v>4.39</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.05</v>
+      </c>
+      <c r="K8">
+        <v>0.989</v>
+      </c>
+      <c r="L8">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M8">
+        <v>0.08941115999999999</v>
+      </c>
+      <c r="N8">
+        <v>-0.02841115999999994</v>
+      </c>
+      <c r="O8">
+        <v>-0.004261673999999991</v>
+      </c>
+      <c r="P8">
+        <v>-0.02414948599999994</v>
+      </c>
+      <c r="Q8">
+        <v>0.9648505140000001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1458087429592865</v>
+      </c>
+      <c r="T8">
+        <v>0.5674871963434709</v>
+      </c>
+      <c r="U8">
+        <v>0.2138</v>
+      </c>
+      <c r="V8">
+        <v>0.1023362184317932</v>
+      </c>
+      <c r="W8">
+        <v>0.1919205164992826</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.6822414562119545</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1503254493716863</v>
+      </c>
+      <c r="C9">
+        <v>7.280601309352832</v>
+      </c>
+      <c r="D9">
+        <v>7.418501309352832</v>
+      </c>
+      <c r="E9">
+        <v>-2.0921</v>
+      </c>
+      <c r="F9">
+        <v>0.4879000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.35</v>
+      </c>
+      <c r="H9">
+        <v>4.39</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.05</v>
+      </c>
+      <c r="K9">
+        <v>0.989</v>
+      </c>
+      <c r="L9">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M9">
+        <v>0.10431302</v>
+      </c>
+      <c r="N9">
+        <v>-0.04331301999999995</v>
+      </c>
+      <c r="O9">
+        <v>-0.006496952999999994</v>
+      </c>
+      <c r="P9">
+        <v>-0.03681606699999996</v>
+      </c>
+      <c r="Q9">
+        <v>0.952183933</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.14695937460401</v>
+      </c>
+      <c r="T9">
+        <v>0.5735892092073791</v>
+      </c>
+      <c r="U9">
+        <v>0.2138</v>
+      </c>
+      <c r="V9">
+        <v>0.08771675865582274</v>
+      </c>
+      <c r="W9">
+        <v>0.1950461569993851</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.584778391038818</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1520754493716863</v>
+      </c>
+      <c r="C10">
+        <v>7.096292386030278</v>
+      </c>
+      <c r="D10">
+        <v>7.303892386030278</v>
+      </c>
+      <c r="E10">
+        <v>-2.0224</v>
+      </c>
+      <c r="F10">
+        <v>0.5576</v>
+      </c>
+      <c r="G10">
+        <v>0.35</v>
+      </c>
+      <c r="H10">
+        <v>4.39</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.05</v>
+      </c>
+      <c r="K10">
+        <v>0.989</v>
+      </c>
+      <c r="L10">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M10">
+        <v>0.11921488</v>
+      </c>
+      <c r="N10">
+        <v>-0.05821487999999994</v>
+      </c>
+      <c r="O10">
+        <v>-0.008732231999999993</v>
+      </c>
+      <c r="P10">
+        <v>-0.04948264799999995</v>
+      </c>
+      <c r="Q10">
+        <v>0.9395173520000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1481350199801406</v>
+      </c>
+      <c r="T10">
+        <v>0.5798238745248506</v>
+      </c>
+      <c r="U10">
+        <v>0.2138</v>
+      </c>
+      <c r="V10">
+        <v>0.07675216382384489</v>
+      </c>
+      <c r="W10">
+        <v>0.197390387374462</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.5116810921589658</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1561405085061343</v>
+      </c>
+      <c r="C11">
+        <v>6.773561656584401</v>
+      </c>
+      <c r="D11">
+        <v>7.050861656584401</v>
+      </c>
+      <c r="E11">
+        <v>-1.9527</v>
+      </c>
+      <c r="F11">
+        <v>0.6273</v>
+      </c>
+      <c r="G11">
+        <v>0.35</v>
+      </c>
+      <c r="H11">
+        <v>4.39</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.05</v>
+      </c>
+      <c r="K11">
+        <v>0.989</v>
+      </c>
+      <c r="L11">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M11">
+        <v>0.14979924</v>
+      </c>
+      <c r="N11">
+        <v>-0.08879923999999995</v>
+      </c>
+      <c r="O11">
+        <v>-0.01331988599999999</v>
+      </c>
+      <c r="P11">
+        <v>-0.07547935399999996</v>
+      </c>
+      <c r="Q11">
+        <v>0.913520646</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1494079972705245</v>
+      </c>
+      <c r="T11">
+        <v>0.5865747090225865</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.06108175181663144</v>
+      </c>
+      <c r="W11">
+        <v>0.2242136776661884</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.4072116787775429</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1581405085061343</v>
+      </c>
+      <c r="C12">
+        <v>6.585697895681337</v>
+      </c>
+      <c r="D12">
+        <v>6.932697895681337</v>
+      </c>
+      <c r="E12">
+        <v>-1.883</v>
+      </c>
+      <c r="F12">
+        <v>0.6970000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.35</v>
+      </c>
+      <c r="H12">
+        <v>4.39</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.05</v>
+      </c>
+      <c r="K12">
+        <v>0.989</v>
+      </c>
+      <c r="L12">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M12">
+        <v>0.1664436</v>
+      </c>
+      <c r="N12">
+        <v>-0.1054436</v>
+      </c>
+      <c r="O12">
+        <v>-0.01581654</v>
+      </c>
+      <c r="P12">
+        <v>-0.08962705999999998</v>
+      </c>
+      <c r="Q12">
+        <v>0.89937294</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1506369750179748</v>
+      </c>
+      <c r="T12">
+        <v>0.5930922057895041</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.0549735766349683</v>
+      </c>
+      <c r="W12">
+        <v>0.2256723098995696</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.3664905108997886</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1601405085061343</v>
+      </c>
+      <c r="C13">
+        <v>6.401729413028146</v>
+      </c>
+      <c r="D13">
+        <v>6.818429413028147</v>
+      </c>
+      <c r="E13">
+        <v>-1.8133</v>
+      </c>
+      <c r="F13">
+        <v>0.7666999999999999</v>
+      </c>
+      <c r="G13">
+        <v>0.35</v>
+      </c>
+      <c r="H13">
+        <v>4.39</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.05</v>
+      </c>
+      <c r="K13">
+        <v>0.989</v>
+      </c>
+      <c r="L13">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M13">
+        <v>0.18308796</v>
+      </c>
+      <c r="N13">
+        <v>-0.1220879599999999</v>
+      </c>
+      <c r="O13">
+        <v>-0.01831319399999999</v>
+      </c>
+      <c r="P13">
+        <v>-0.1037747659999999</v>
+      </c>
+      <c r="Q13">
+        <v>0.8852252340000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1518935702428958</v>
+      </c>
+      <c r="T13">
+        <v>0.5997561631579255</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.04997597875906209</v>
+      </c>
+      <c r="W13">
+        <v>0.226865736272336</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.3331731917270806</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1621405085061343</v>
+      </c>
+      <c r="C14">
+        <v>6.221466719625774</v>
+      </c>
+      <c r="D14">
+        <v>6.707866719625775</v>
+      </c>
+      <c r="E14">
+        <v>-1.7436</v>
+      </c>
+      <c r="F14">
+        <v>0.8363999999999999</v>
+      </c>
+      <c r="G14">
+        <v>0.35</v>
+      </c>
+      <c r="H14">
+        <v>4.39</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.05</v>
+      </c>
+      <c r="K14">
+        <v>0.989</v>
+      </c>
+      <c r="L14">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M14">
+        <v>0.19973232</v>
+      </c>
+      <c r="N14">
+        <v>-0.1387323199999999</v>
+      </c>
+      <c r="O14">
+        <v>-0.02080984799999999</v>
+      </c>
+      <c r="P14">
+        <v>-0.1179224719999999</v>
+      </c>
+      <c r="Q14">
+        <v>0.871077528</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1531787244502015</v>
+      </c>
+      <c r="T14">
+        <v>0.606571574102902</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.04581131386247358</v>
+      </c>
+      <c r="W14">
+        <v>0.2278602582496413</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.3054087590831572</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1641405085061343</v>
+      </c>
+      <c r="C15">
+        <v>6.04473242082528</v>
+      </c>
+      <c r="D15">
+        <v>6.600832420825281</v>
+      </c>
+      <c r="E15">
+        <v>-1.6739</v>
+      </c>
+      <c r="F15">
+        <v>0.9061</v>
+      </c>
+      <c r="G15">
+        <v>0.35</v>
+      </c>
+      <c r="H15">
+        <v>4.39</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.05</v>
+      </c>
+      <c r="K15">
+        <v>0.989</v>
+      </c>
+      <c r="L15">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M15">
+        <v>0.21637668</v>
+      </c>
+      <c r="N15">
+        <v>-0.15537668</v>
+      </c>
+      <c r="O15">
+        <v>-0.023306502</v>
+      </c>
+      <c r="P15">
+        <v>-0.132070178</v>
+      </c>
+      <c r="Q15">
+        <v>0.856929822</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1544934224323877</v>
+      </c>
+      <c r="T15">
+        <v>0.613543661161556</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.0422873666422833</v>
+      </c>
+      <c r="W15">
+        <v>0.2287017768458228</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.281915777615222</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1661405085061343</v>
+      </c>
+      <c r="C16">
+        <v>5.871360266563271</v>
+      </c>
+      <c r="D16">
+        <v>6.497160266563272</v>
+      </c>
+      <c r="E16">
+        <v>-1.6042</v>
+      </c>
+      <c r="F16">
+        <v>0.9758000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.35</v>
+      </c>
+      <c r="H16">
+        <v>4.39</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.05</v>
+      </c>
+      <c r="K16">
+        <v>0.989</v>
+      </c>
+      <c r="L16">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M16">
+        <v>0.23302104</v>
+      </c>
+      <c r="N16">
+        <v>-0.17202104</v>
+      </c>
+      <c r="O16">
+        <v>-0.025803156</v>
+      </c>
+      <c r="P16">
+        <v>-0.146217884</v>
+      </c>
+      <c r="Q16">
+        <v>0.842782116</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1558386947862527</v>
+      </c>
+      <c r="T16">
+        <v>0.6206778897797136</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.03926684045354877</v>
+      </c>
+      <c r="W16">
+        <v>0.2294230784996926</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.2617789363569918</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1681405085061342</v>
+      </c>
+      <c r="C17">
+        <v>5.701194289714958</v>
+      </c>
+      <c r="D17">
+        <v>6.396694289714958</v>
+      </c>
+      <c r="E17">
+        <v>-1.5345</v>
+      </c>
+      <c r="F17">
+        <v>1.0455</v>
+      </c>
+      <c r="G17">
+        <v>0.35</v>
+      </c>
+      <c r="H17">
+        <v>4.39</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.05</v>
+      </c>
+      <c r="K17">
+        <v>0.989</v>
+      </c>
+      <c r="L17">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M17">
+        <v>0.2496654</v>
+      </c>
+      <c r="N17">
+        <v>-0.1886653999999999</v>
+      </c>
+      <c r="O17">
+        <v>-0.02829980999999999</v>
+      </c>
+      <c r="P17">
+        <v>-0.1603655899999999</v>
+      </c>
+      <c r="Q17">
+        <v>0.82863441</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1572156206072674</v>
+      </c>
+      <c r="T17">
+        <v>0.6279799826006514</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.03664905108997887</v>
+      </c>
+      <c r="W17">
+        <v>0.2300482065997131</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.2443270072665258</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1701405085061343</v>
+      </c>
+      <c r="C18">
+        <v>5.534088023172046</v>
+      </c>
+      <c r="D18">
+        <v>6.299288023172046</v>
+      </c>
+      <c r="E18">
+        <v>-1.4648</v>
+      </c>
+      <c r="F18">
+        <v>1.1152</v>
+      </c>
+      <c r="G18">
+        <v>0.35</v>
+      </c>
+      <c r="H18">
+        <v>4.39</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.05</v>
+      </c>
+      <c r="K18">
+        <v>0.989</v>
+      </c>
+      <c r="L18">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M18">
+        <v>0.26630976</v>
+      </c>
+      <c r="N18">
+        <v>-0.20530976</v>
+      </c>
+      <c r="O18">
+        <v>-0.030796464</v>
+      </c>
+      <c r="P18">
+        <v>-0.174513296</v>
+      </c>
+      <c r="Q18">
+        <v>0.814486704</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1586253303764016</v>
+      </c>
+      <c r="T18">
+        <v>0.6354559347744687</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.03435848539685519</v>
+      </c>
+      <c r="W18">
+        <v>0.230595193687231</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.2290565693123678</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1721405085061343</v>
+      </c>
+      <c r="C19">
+        <v>5.369903787379856</v>
+      </c>
+      <c r="D19">
+        <v>6.204803787379856</v>
+      </c>
+      <c r="E19">
+        <v>-1.3951</v>
+      </c>
+      <c r="F19">
+        <v>1.1849</v>
+      </c>
+      <c r="G19">
+        <v>0.35</v>
+      </c>
+      <c r="H19">
+        <v>4.39</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.05</v>
+      </c>
+      <c r="K19">
+        <v>0.989</v>
+      </c>
+      <c r="L19">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M19">
+        <v>0.28295412</v>
+      </c>
+      <c r="N19">
+        <v>-0.22195412</v>
+      </c>
+      <c r="O19">
+        <v>-0.033293118</v>
+      </c>
+      <c r="P19">
+        <v>-0.188661002</v>
+      </c>
+      <c r="Q19">
+        <v>0.800338998</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1600690090556353</v>
+      </c>
+      <c r="T19">
+        <v>0.643112030374161</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.03233739802056958</v>
+      </c>
+      <c r="W19">
+        <v>0.231077829352688</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.2155826534704639</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1741405085061343</v>
+      </c>
+      <c r="C20">
+        <v>5.208512041045112</v>
+      </c>
+      <c r="D20">
+        <v>6.113112041045112</v>
+      </c>
+      <c r="E20">
+        <v>-1.3254</v>
+      </c>
+      <c r="F20">
+        <v>1.2546</v>
+      </c>
+      <c r="G20">
+        <v>0.35</v>
+      </c>
+      <c r="H20">
+        <v>4.39</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.05</v>
+      </c>
+      <c r="K20">
+        <v>0.989</v>
+      </c>
+      <c r="L20">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M20">
+        <v>0.29959848</v>
+      </c>
+      <c r="N20">
+        <v>-0.2385984799999999</v>
+      </c>
+      <c r="O20">
+        <v>-0.035789772</v>
+      </c>
+      <c r="P20">
+        <v>-0.2028087079999999</v>
+      </c>
+      <c r="Q20">
+        <v>0.786191292</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1615478994099723</v>
+      </c>
+      <c r="T20">
+        <v>0.6509548600128703</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.03054087590831572</v>
+      </c>
+      <c r="W20">
+        <v>0.2315068388330942</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.2036058393887714</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1761405085061343</v>
+      </c>
+      <c r="C21">
+        <v>5.049790788575057</v>
+      </c>
+      <c r="D21">
+        <v>6.024090788575058</v>
+      </c>
+      <c r="E21">
+        <v>-1.2557</v>
+      </c>
+      <c r="F21">
+        <v>1.3243</v>
+      </c>
+      <c r="G21">
+        <v>0.35</v>
+      </c>
+      <c r="H21">
+        <v>4.39</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.05</v>
+      </c>
+      <c r="K21">
+        <v>0.989</v>
+      </c>
+      <c r="L21">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M21">
+        <v>0.31624284</v>
+      </c>
+      <c r="N21">
+        <v>-0.25524284</v>
+      </c>
+      <c r="O21">
+        <v>-0.038286426</v>
+      </c>
+      <c r="P21">
+        <v>-0.216956414</v>
+      </c>
+      <c r="Q21">
+        <v>0.772043586</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1630633055755276</v>
+      </c>
+      <c r="T21">
+        <v>0.6589913397661157</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.02893346138682542</v>
+      </c>
+      <c r="W21">
+        <v>0.2318906894208261</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.1928897425788361</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1781405085061343</v>
+      </c>
+      <c r="C22">
+        <v>4.893625038547888</v>
+      </c>
+      <c r="D22">
+        <v>5.937625038547888</v>
+      </c>
+      <c r="E22">
+        <v>-1.186</v>
+      </c>
+      <c r="F22">
+        <v>1.394</v>
+      </c>
+      <c r="G22">
+        <v>0.35</v>
+      </c>
+      <c r="H22">
+        <v>4.39</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.05</v>
+      </c>
+      <c r="K22">
+        <v>0.989</v>
+      </c>
+      <c r="L22">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M22">
+        <v>0.3328872</v>
+      </c>
+      <c r="N22">
+        <v>-0.2718872</v>
+      </c>
+      <c r="O22">
+        <v>-0.04078308000000001</v>
+      </c>
+      <c r="P22">
+        <v>-0.23110412</v>
+      </c>
+      <c r="Q22">
+        <v>0.75789588</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1646165968952217</v>
+      </c>
+      <c r="T22">
+        <v>0.6672287315131922</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.02748678831748415</v>
+      </c>
+      <c r="W22">
+        <v>0.2322361549497848</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.1832452554498942</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1801405085061343</v>
+      </c>
+      <c r="C23">
+        <v>4.739906308159774</v>
+      </c>
+      <c r="D23">
+        <v>5.853606308159774</v>
+      </c>
+      <c r="E23">
+        <v>-1.1163</v>
+      </c>
+      <c r="F23">
+        <v>1.4637</v>
+      </c>
+      <c r="G23">
+        <v>0.35</v>
+      </c>
+      <c r="H23">
+        <v>4.39</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.05</v>
+      </c>
+      <c r="K23">
+        <v>0.989</v>
+      </c>
+      <c r="L23">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M23">
+        <v>0.34953156</v>
+      </c>
+      <c r="N23">
+        <v>-0.28853156</v>
+      </c>
+      <c r="O23">
+        <v>-0.043279734</v>
+      </c>
+      <c r="P23">
+        <v>-0.245251826</v>
+      </c>
+      <c r="Q23">
+        <v>0.743748174</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1662092120457941</v>
+      </c>
+      <c r="T23">
+        <v>0.6756746648234856</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.02617789363569919</v>
+      </c>
+      <c r="W23">
+        <v>0.232548718999795</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.1745192909046612</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1821405085061343</v>
+      </c>
+      <c r="C24">
+        <v>4.588532169157968</v>
+      </c>
+      <c r="D24">
+        <v>5.771932169157969</v>
+      </c>
+      <c r="E24">
+        <v>-1.0466</v>
+      </c>
+      <c r="F24">
+        <v>1.5334</v>
+      </c>
+      <c r="G24">
+        <v>0.35</v>
+      </c>
+      <c r="H24">
+        <v>4.39</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.05</v>
+      </c>
+      <c r="K24">
+        <v>0.989</v>
+      </c>
+      <c r="L24">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M24">
+        <v>0.36617592</v>
+      </c>
+      <c r="N24">
+        <v>-0.3051759199999999</v>
+      </c>
+      <c r="O24">
+        <v>-0.04577638799999999</v>
+      </c>
+      <c r="P24">
+        <v>-0.2593995319999999</v>
+      </c>
+      <c r="Q24">
+        <v>0.7296004680000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1678426634822786</v>
+      </c>
+      <c r="T24">
+        <v>0.6843371605263509</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.02498798937953104</v>
+      </c>
+      <c r="W24">
+        <v>0.232832868136168</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.1665865958635403</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1841405085061343</v>
+      </c>
+      <c r="C25">
+        <v>4.439405831263818</v>
+      </c>
+      <c r="D25">
+        <v>5.692505831263817</v>
+      </c>
+      <c r="E25">
+        <v>-0.9769000000000001</v>
+      </c>
+      <c r="F25">
+        <v>1.6031</v>
+      </c>
+      <c r="G25">
+        <v>0.35</v>
+      </c>
+      <c r="H25">
+        <v>4.39</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.05</v>
+      </c>
+      <c r="K25">
+        <v>0.989</v>
+      </c>
+      <c r="L25">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M25">
+        <v>0.38282028</v>
+      </c>
+      <c r="N25">
+        <v>-0.32182028</v>
+      </c>
+      <c r="O25">
+        <v>-0.048273042</v>
+      </c>
+      <c r="P25">
+        <v>-0.273547238</v>
+      </c>
+      <c r="Q25">
+        <v>0.715452762</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1695185422288017</v>
+      </c>
+      <c r="T25">
+        <v>0.6932246561176023</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.02390155505868187</v>
+      </c>
+      <c r="W25">
+        <v>0.2330923086519868</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.1593437003912125</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1861405085061343</v>
+      </c>
+      <c r="C26">
+        <v>4.292435759523475</v>
+      </c>
+      <c r="D26">
+        <v>5.615235759523475</v>
+      </c>
+      <c r="E26">
+        <v>-0.9072000000000002</v>
+      </c>
+      <c r="F26">
+        <v>1.6728</v>
+      </c>
+      <c r="G26">
+        <v>0.35</v>
+      </c>
+      <c r="H26">
+        <v>4.39</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.05</v>
+      </c>
+      <c r="K26">
+        <v>0.989</v>
+      </c>
+      <c r="L26">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M26">
+        <v>0.39946464</v>
+      </c>
+      <c r="N26">
+        <v>-0.3384646399999999</v>
+      </c>
+      <c r="O26">
+        <v>-0.050769696</v>
+      </c>
+      <c r="P26">
+        <v>-0.287694944</v>
+      </c>
+      <c r="Q26">
+        <v>0.701305056</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1712385230476017</v>
+      </c>
+      <c r="T26">
+        <v>0.7023460331717811</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.02290565693123679</v>
+      </c>
+      <c r="W26">
+        <v>0.2333301291248207</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.1527043795415786</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1881405085061343</v>
+      </c>
+      <c r="C27">
+        <v>4.147535322405734</v>
+      </c>
+      <c r="D27">
+        <v>5.540035322405734</v>
+      </c>
+      <c r="E27">
+        <v>-0.8375000000000001</v>
+      </c>
+      <c r="F27">
+        <v>1.7425</v>
+      </c>
+      <c r="G27">
+        <v>0.35</v>
+      </c>
+      <c r="H27">
+        <v>4.39</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.05</v>
+      </c>
+      <c r="K27">
+        <v>0.989</v>
+      </c>
+      <c r="L27">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M27">
+        <v>0.416109</v>
+      </c>
+      <c r="N27">
+        <v>-0.355109</v>
+      </c>
+      <c r="O27">
+        <v>-0.05326635</v>
+      </c>
+      <c r="P27">
+        <v>-0.3018426499999999</v>
+      </c>
+      <c r="Q27">
+        <v>0.6871573500000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1730043700215698</v>
+      </c>
+      <c r="T27">
+        <v>0.7117106469474049</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.02198943065398732</v>
+      </c>
+      <c r="W27">
+        <v>0.2335489239598278</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.1465962043599154</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1901405085061343</v>
+      </c>
+      <c r="C28">
+        <v>4.004622467802682</v>
+      </c>
+      <c r="D28">
+        <v>5.466822467802682</v>
+      </c>
+      <c r="E28">
+        <v>-0.7678</v>
+      </c>
+      <c r="F28">
+        <v>1.8122</v>
+      </c>
+      <c r="G28">
+        <v>0.35</v>
+      </c>
+      <c r="H28">
+        <v>4.39</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.05</v>
+      </c>
+      <c r="K28">
+        <v>0.989</v>
+      </c>
+      <c r="L28">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M28">
+        <v>0.43275336</v>
+      </c>
+      <c r="N28">
+        <v>-0.37175336</v>
+      </c>
+      <c r="O28">
+        <v>-0.055763004</v>
+      </c>
+      <c r="P28">
+        <v>-0.315990356</v>
+      </c>
+      <c r="Q28">
+        <v>0.673009644</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1748179425894288</v>
+      </c>
+      <c r="T28">
+        <v>0.7213283583926402</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.02114368332114165</v>
+      </c>
+      <c r="W28">
+        <v>0.2337508884229114</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.140957888807611</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1921405085061343</v>
+      </c>
+      <c r="C29">
+        <v>3.863619424385632</v>
+      </c>
+      <c r="D29">
+        <v>5.395519424385633</v>
+      </c>
+      <c r="E29">
+        <v>-0.6980999999999999</v>
+      </c>
+      <c r="F29">
+        <v>1.8819</v>
+      </c>
+      <c r="G29">
+        <v>0.35</v>
+      </c>
+      <c r="H29">
+        <v>4.39</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.05</v>
+      </c>
+      <c r="K29">
+        <v>0.989</v>
+      </c>
+      <c r="L29">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M29">
+        <v>0.4493977200000001</v>
+      </c>
+      <c r="N29">
+        <v>-0.38839772</v>
+      </c>
+      <c r="O29">
+        <v>-0.05825965800000001</v>
+      </c>
+      <c r="P29">
+        <v>-0.330138062</v>
+      </c>
+      <c r="Q29">
+        <v>0.658861938</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1766812020769552</v>
+      </c>
+      <c r="T29">
+        <v>0.7312095687815804</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.02036058393887714</v>
+      </c>
+      <c r="W29">
+        <v>0.2339378925553961</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.1357372262591809</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1941405085061343</v>
+      </c>
+      <c r="C30">
+        <v>3.724452426031206</v>
+      </c>
+      <c r="D30">
+        <v>5.326052426031207</v>
+      </c>
+      <c r="E30">
+        <v>-0.6283999999999998</v>
+      </c>
+      <c r="F30">
+        <v>1.9516</v>
+      </c>
+      <c r="G30">
+        <v>0.35</v>
+      </c>
+      <c r="H30">
+        <v>4.39</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.05</v>
+      </c>
+      <c r="K30">
+        <v>0.989</v>
+      </c>
+      <c r="L30">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M30">
+        <v>0.4660420800000001</v>
+      </c>
+      <c r="N30">
+        <v>-0.40504208</v>
+      </c>
+      <c r="O30">
+        <v>-0.06075631200000001</v>
+      </c>
+      <c r="P30">
+        <v>-0.344285768</v>
+      </c>
+      <c r="Q30">
+        <v>0.644714232</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1785962187724685</v>
+      </c>
+      <c r="T30">
+        <v>0.7413652572368802</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.01963342022677439</v>
+      </c>
+      <c r="W30">
+        <v>0.2341115392498463</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.1308894681784959</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1961405085061343</v>
+      </c>
+      <c r="C31">
+        <v>3.587051457264813</v>
+      </c>
+      <c r="D31">
+        <v>5.258351457264813</v>
+      </c>
+      <c r="E31">
+        <v>-0.5587000000000004</v>
+      </c>
+      <c r="F31">
+        <v>2.0213</v>
+      </c>
+      <c r="G31">
+        <v>0.35</v>
+      </c>
+      <c r="H31">
+        <v>4.39</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.05</v>
+      </c>
+      <c r="K31">
+        <v>0.989</v>
+      </c>
+      <c r="L31">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M31">
+        <v>0.4826864399999999</v>
+      </c>
+      <c r="N31">
+        <v>-0.4216864399999999</v>
+      </c>
+      <c r="O31">
+        <v>-0.06325296599999999</v>
+      </c>
+      <c r="P31">
+        <v>-0.3584334739999999</v>
+      </c>
+      <c r="Q31">
+        <v>0.6305665260000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1805651796002498</v>
+      </c>
+      <c r="T31">
+        <v>0.7518070214233151</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.01895640573619597</v>
+      </c>
+      <c r="W31">
+        <v>0.2342732103101964</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.1263760382413064</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1981405085061343</v>
+      </c>
+      <c r="C32">
+        <v>3.451350017874874</v>
+      </c>
+      <c r="D32">
+        <v>5.192350017874874</v>
+      </c>
+      <c r="E32">
+        <v>-0.4890000000000003</v>
+      </c>
+      <c r="F32">
+        <v>2.091</v>
+      </c>
+      <c r="G32">
+        <v>0.35</v>
+      </c>
+      <c r="H32">
+        <v>4.39</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.05</v>
+      </c>
+      <c r="K32">
+        <v>0.989</v>
+      </c>
+      <c r="L32">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M32">
+        <v>0.4993308</v>
+      </c>
+      <c r="N32">
+        <v>-0.4383307999999999</v>
+      </c>
+      <c r="O32">
+        <v>-0.06574961999999999</v>
+      </c>
+      <c r="P32">
+        <v>-0.3725811799999999</v>
+      </c>
+      <c r="Q32">
+        <v>0.61641882</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1825903964516819</v>
+      </c>
+      <c r="T32">
+        <v>0.7625471217293625</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.01832452554498943</v>
+      </c>
+      <c r="W32">
+        <v>0.2344241032998566</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.1221635036332629</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2001405085061342</v>
+      </c>
+      <c r="C33">
+        <v>3.317284905034322</v>
+      </c>
+      <c r="D33">
+        <v>5.127984905034322</v>
+      </c>
+      <c r="E33">
+        <v>-0.4193000000000002</v>
+      </c>
+      <c r="F33">
+        <v>2.1607</v>
+      </c>
+      <c r="G33">
+        <v>0.35</v>
+      </c>
+      <c r="H33">
+        <v>4.39</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.05</v>
+      </c>
+      <c r="K33">
+        <v>0.989</v>
+      </c>
+      <c r="L33">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M33">
+        <v>0.51597516</v>
+      </c>
+      <c r="N33">
+        <v>-0.4549751599999999</v>
+      </c>
+      <c r="O33">
+        <v>-0.068246274</v>
+      </c>
+      <c r="P33">
+        <v>-0.3867288859999999</v>
+      </c>
+      <c r="Q33">
+        <v>0.6022711140000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1846743152408367</v>
+      </c>
+      <c r="T33">
+        <v>0.7735985292906575</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.01773341181773171</v>
+      </c>
+      <c r="W33">
+        <v>0.2345652612579257</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.1182227454515448</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2021405085061343</v>
+      </c>
+      <c r="C34">
+        <v>3.184796011428765</v>
+      </c>
+      <c r="D34">
+        <v>5.065196011428766</v>
+      </c>
+      <c r="E34">
+        <v>-0.3496000000000001</v>
+      </c>
+      <c r="F34">
+        <v>2.2304</v>
+      </c>
+      <c r="G34">
+        <v>0.35</v>
+      </c>
+      <c r="H34">
+        <v>4.39</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.05</v>
+      </c>
+      <c r="K34">
+        <v>0.989</v>
+      </c>
+      <c r="L34">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M34">
+        <v>0.53261952</v>
+      </c>
+      <c r="N34">
+        <v>-0.47161952</v>
+      </c>
+      <c r="O34">
+        <v>-0.07074292800000001</v>
+      </c>
+      <c r="P34">
+        <v>-0.4008765919999999</v>
+      </c>
+      <c r="Q34">
+        <v>0.5881234080000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1868195257590843</v>
+      </c>
+      <c r="T34">
+        <v>0.7849749782508143</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.01717924269842759</v>
+      </c>
+      <c r="W34">
+        <v>0.2346975968436155</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.1145282846561839</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2041405085061342</v>
+      </c>
+      <c r="C35">
+        <v>3.053826138036054</v>
+      </c>
+      <c r="D35">
+        <v>5.003926138036054</v>
+      </c>
+      <c r="E35">
+        <v>-0.2799</v>
+      </c>
+      <c r="F35">
+        <v>2.3001</v>
+      </c>
+      <c r="G35">
+        <v>0.35</v>
+      </c>
+      <c r="H35">
+        <v>4.39</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.05</v>
+      </c>
+      <c r="K35">
+        <v>0.989</v>
+      </c>
+      <c r="L35">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M35">
+        <v>0.54926388</v>
+      </c>
+      <c r="N35">
+        <v>-0.48826388</v>
+      </c>
+      <c r="O35">
+        <v>-0.07323958200000001</v>
+      </c>
+      <c r="P35">
+        <v>-0.415024298</v>
+      </c>
+      <c r="Q35">
+        <v>0.573975702</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1890287724122049</v>
+      </c>
+      <c r="T35">
+        <v>0.796691022702319</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.01665865958635403</v>
+      </c>
+      <c r="W35">
+        <v>0.2348219120907787</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.1110577305756935</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2061405085061342</v>
+      </c>
+      <c r="C36">
+        <v>2.924320820331375</v>
+      </c>
+      <c r="D36">
+        <v>4.944120820331375</v>
+      </c>
+      <c r="E36">
+        <v>-0.2101999999999999</v>
+      </c>
+      <c r="F36">
+        <v>2.3698</v>
+      </c>
+      <c r="G36">
+        <v>0.35</v>
+      </c>
+      <c r="H36">
+        <v>4.39</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.05</v>
+      </c>
+      <c r="K36">
+        <v>0.989</v>
+      </c>
+      <c r="L36">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M36">
+        <v>0.5659082400000001</v>
+      </c>
+      <c r="N36">
+        <v>-0.50490824</v>
+      </c>
+      <c r="O36">
+        <v>-0.07573623600000001</v>
+      </c>
+      <c r="P36">
+        <v>-0.429172004</v>
+      </c>
+      <c r="Q36">
+        <v>0.559827996</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.191304965933602</v>
+      </c>
+      <c r="T36">
+        <v>0.8087620988038692</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.01616869901028479</v>
+      </c>
+      <c r="W36">
+        <v>0.234938914676344</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.107791326735232</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2081405085061343</v>
+      </c>
+      <c r="C37">
+        <v>2.796228166808045</v>
+      </c>
+      <c r="D37">
+        <v>4.885728166808046</v>
+      </c>
+      <c r="E37">
+        <v>-0.1404999999999998</v>
+      </c>
+      <c r="F37">
+        <v>2.4395</v>
+      </c>
+      <c r="G37">
+        <v>0.35</v>
+      </c>
+      <c r="H37">
+        <v>4.39</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.05</v>
+      </c>
+      <c r="K37">
+        <v>0.989</v>
+      </c>
+      <c r="L37">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M37">
+        <v>0.5825526000000001</v>
+      </c>
+      <c r="N37">
+        <v>-0.5215526</v>
+      </c>
+      <c r="O37">
+        <v>-0.07823289000000001</v>
+      </c>
+      <c r="P37">
+        <v>-0.44331971</v>
+      </c>
+      <c r="Q37">
+        <v>0.54568029</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1936511961787344</v>
+      </c>
+      <c r="T37">
+        <v>0.8212045926316212</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.01570673618141951</v>
+      </c>
+      <c r="W37">
+        <v>0.235049231399877</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1047115745427968</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2101405085061343</v>
+      </c>
+      <c r="C38">
+        <v>2.669498708807655</v>
+      </c>
+      <c r="D38">
+        <v>4.828698708807655</v>
+      </c>
+      <c r="E38">
+        <v>-0.0708000000000002</v>
+      </c>
+      <c r="F38">
+        <v>2.5092</v>
+      </c>
+      <c r="G38">
+        <v>0.35</v>
+      </c>
+      <c r="H38">
+        <v>4.39</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.05</v>
+      </c>
+      <c r="K38">
+        <v>0.989</v>
+      </c>
+      <c r="L38">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M38">
+        <v>0.59919696</v>
+      </c>
+      <c r="N38">
+        <v>-0.5381969599999999</v>
+      </c>
+      <c r="O38">
+        <v>-0.080729544</v>
+      </c>
+      <c r="P38">
+        <v>-0.457467416</v>
+      </c>
+      <c r="Q38">
+        <v>0.531532584</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1960707461190271</v>
+      </c>
+      <c r="T38">
+        <v>0.8340359143914902</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.01527043795415786</v>
+      </c>
+      <c r="W38">
+        <v>0.2351534194165471</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1018029196943857</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2121405085061343</v>
+      </c>
+      <c r="C39">
+        <v>2.544085260746128</v>
+      </c>
+      <c r="D39">
+        <v>4.772985260746128</v>
+      </c>
+      <c r="E39">
+        <v>-0.001100000000000101</v>
+      </c>
+      <c r="F39">
+        <v>2.5789</v>
+      </c>
+      <c r="G39">
+        <v>0.35</v>
+      </c>
+      <c r="H39">
+        <v>4.39</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.05</v>
+      </c>
+      <c r="K39">
+        <v>0.989</v>
+      </c>
+      <c r="L39">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M39">
+        <v>0.61584132</v>
+      </c>
+      <c r="N39">
+        <v>-0.55484132</v>
+      </c>
+      <c r="O39">
+        <v>-0.083226198</v>
+      </c>
+      <c r="P39">
+        <v>-0.471615122</v>
+      </c>
+      <c r="Q39">
+        <v>0.517384878</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1985671071685354</v>
+      </c>
+      <c r="T39">
+        <v>0.8472745796992917</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.0148577234148563</v>
+      </c>
+      <c r="W39">
+        <v>0.2352519756485323</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.09905148943237529</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2141405085061343</v>
+      </c>
+      <c r="C40">
+        <v>2.419942789905694</v>
+      </c>
+      <c r="D40">
+        <v>4.718542789905694</v>
+      </c>
+      <c r="E40">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="F40">
+        <v>2.6486</v>
+      </c>
+      <c r="G40">
+        <v>0.35</v>
+      </c>
+      <c r="H40">
+        <v>4.39</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.05</v>
+      </c>
+      <c r="K40">
+        <v>0.989</v>
+      </c>
+      <c r="L40">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M40">
+        <v>0.6324856800000001</v>
+      </c>
+      <c r="N40">
+        <v>-0.57148568</v>
+      </c>
+      <c r="O40">
+        <v>-0.08572285200000002</v>
+      </c>
+      <c r="P40">
+        <v>-0.485762828</v>
+      </c>
+      <c r="Q40">
+        <v>0.503237172</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2011439959938344</v>
+      </c>
+      <c r="T40">
+        <v>0.8609402987266994</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.01446673069341271</v>
+      </c>
+      <c r="W40">
+        <v>0.235345344710413</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.09644487128941803</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2161405085061343</v>
+      </c>
+      <c r="C41">
+        <v>2.297028295037562</v>
+      </c>
+      <c r="D41">
+        <v>4.665328295037563</v>
+      </c>
+      <c r="E41">
+        <v>0.1383000000000001</v>
+      </c>
+      <c r="F41">
+        <v>2.7183</v>
+      </c>
+      <c r="G41">
+        <v>0.35</v>
+      </c>
+      <c r="H41">
+        <v>4.39</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.05</v>
+      </c>
+      <c r="K41">
+        <v>0.989</v>
+      </c>
+      <c r="L41">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M41">
+        <v>0.6491300400000001</v>
+      </c>
+      <c r="N41">
+        <v>-0.58813004</v>
+      </c>
+      <c r="O41">
+        <v>-0.08821950600000002</v>
+      </c>
+      <c r="P41">
+        <v>-0.499910534</v>
+      </c>
+      <c r="Q41">
+        <v>0.489089466</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2038053729773399</v>
+      </c>
+      <c r="T41">
+        <v>0.8750540741156618</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.0140957888807611</v>
+      </c>
+      <c r="W41">
+        <v>0.2354339256152743</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.09397192587174064</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
         <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2181405085061343</v>
+      </c>
+      <c r="C42">
+        <v>2.17530069308752</v>
+      </c>
+      <c r="D42">
+        <v>4.61330069308752</v>
+      </c>
+      <c r="E42">
+        <v>0.2080000000000002</v>
+      </c>
+      <c r="F42">
+        <v>2.788</v>
+      </c>
+      <c r="G42">
+        <v>0.35</v>
+      </c>
+      <c r="H42">
+        <v>4.39</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.05</v>
+      </c>
+      <c r="K42">
+        <v>0.989</v>
+      </c>
+      <c r="L42">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M42">
+        <v>0.6657744000000001</v>
+      </c>
+      <c r="N42">
+        <v>-0.6047744</v>
+      </c>
+      <c r="O42">
+        <v>-0.09071616000000002</v>
+      </c>
+      <c r="P42">
+        <v>-0.51405824</v>
+      </c>
+      <c r="Q42">
+        <v>0.47494176</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2065554625269622</v>
+      </c>
+      <c r="T42">
+        <v>0.8896383086842563</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.01374339415874207</v>
+      </c>
+      <c r="W42">
+        <v>0.2355180774748924</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.09162262772494711</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2201405085061343</v>
+      </c>
+      <c r="C43">
+        <v>2.054720713417326</v>
+      </c>
+      <c r="D43">
+        <v>4.562420713417326</v>
+      </c>
+      <c r="E43">
+        <v>0.2776999999999998</v>
+      </c>
+      <c r="F43">
+        <v>2.8577</v>
+      </c>
+      <c r="G43">
+        <v>0.35</v>
+      </c>
+      <c r="H43">
+        <v>4.39</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.05</v>
+      </c>
+      <c r="K43">
+        <v>0.989</v>
+      </c>
+      <c r="L43">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M43">
+        <v>0.68241876</v>
+      </c>
+      <c r="N43">
+        <v>-0.62141876</v>
+      </c>
+      <c r="O43">
+        <v>-0.093212814</v>
+      </c>
+      <c r="P43">
+        <v>-0.5282059459999999</v>
+      </c>
+      <c r="Q43">
+        <v>0.4607940540000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.209398775451148</v>
+      </c>
+      <c r="T43">
+        <v>0.9047169240856843</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.013408189423163</v>
+      </c>
+      <c r="W43">
+        <v>0.2355981243657487</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.08938792948775331</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2221405085061343</v>
+      </c>
+      <c r="C44">
+        <v>1.935250798949518</v>
+      </c>
+      <c r="D44">
+        <v>4.512650798949519</v>
+      </c>
+      <c r="E44">
+        <v>0.3473999999999999</v>
+      </c>
+      <c r="F44">
+        <v>2.9274</v>
+      </c>
+      <c r="G44">
+        <v>0.35</v>
+      </c>
+      <c r="H44">
+        <v>4.39</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.05</v>
+      </c>
+      <c r="K44">
+        <v>0.989</v>
+      </c>
+      <c r="L44">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M44">
+        <v>0.69906312</v>
+      </c>
+      <c r="N44">
+        <v>-0.63806312</v>
+      </c>
+      <c r="O44">
+        <v>-0.09570946800000001</v>
+      </c>
+      <c r="P44">
+        <v>-0.542353652</v>
+      </c>
+      <c r="Q44">
+        <v>0.446646348</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2123401336485816</v>
+      </c>
+      <c r="T44">
+        <v>0.9203154917423338</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.01308894681784959</v>
+      </c>
+      <c r="W44">
+        <v>0.2356743594998975</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.08725964545233067</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2241405085061343</v>
+      </c>
+      <c r="C45">
+        <v>1.816855013712693</v>
+      </c>
+      <c r="D45">
+        <v>4.463955013712693</v>
+      </c>
+      <c r="E45">
+        <v>0.4170999999999996</v>
+      </c>
+      <c r="F45">
+        <v>2.9971</v>
+      </c>
+      <c r="G45">
+        <v>0.35</v>
+      </c>
+      <c r="H45">
+        <v>4.39</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.05</v>
+      </c>
+      <c r="K45">
+        <v>0.989</v>
+      </c>
+      <c r="L45">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M45">
+        <v>0.71570748</v>
+      </c>
+      <c r="N45">
+        <v>-0.6547074799999999</v>
+      </c>
+      <c r="O45">
+        <v>-0.09820612199999999</v>
+      </c>
+      <c r="P45">
+        <v>-0.5565013579999999</v>
+      </c>
+      <c r="Q45">
+        <v>0.4324986420000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2153846973968023</v>
+      </c>
+      <c r="T45">
+        <v>0.9364613775623748</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.01278455270580658</v>
+      </c>
+      <c r="W45">
+        <v>0.2357470488138534</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.08523035137204382</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2261405085061343</v>
+      </c>
+      <c r="C46">
+        <v>1.699498956308892</v>
+      </c>
+      <c r="D46">
+        <v>4.416298956308892</v>
+      </c>
+      <c r="E46">
+        <v>0.4867999999999997</v>
+      </c>
+      <c r="F46">
+        <v>3.0668</v>
+      </c>
+      <c r="G46">
+        <v>0.35</v>
+      </c>
+      <c r="H46">
+        <v>4.39</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.05</v>
+      </c>
+      <c r="K46">
+        <v>0.989</v>
+      </c>
+      <c r="L46">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M46">
+        <v>0.73235184</v>
+      </c>
+      <c r="N46">
+        <v>-0.6713518399999999</v>
+      </c>
+      <c r="O46">
+        <v>-0.100702776</v>
+      </c>
+      <c r="P46">
+        <v>-0.5706490639999999</v>
+      </c>
+      <c r="Q46">
+        <v>0.4183509360000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2185379955646023</v>
+      </c>
+      <c r="T46">
+        <v>0.953183902161703</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.01249399468976552</v>
+      </c>
+      <c r="W46">
+        <v>0.235816434068084</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.08329329793177009</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2281405085061343</v>
+      </c>
+      <c r="C47">
+        <v>1.583149678865276</v>
+      </c>
+      <c r="D47">
+        <v>4.369649678865276</v>
+      </c>
+      <c r="E47">
+        <v>0.5564999999999998</v>
+      </c>
+      <c r="F47">
+        <v>3.1365</v>
+      </c>
+      <c r="G47">
+        <v>0.35</v>
+      </c>
+      <c r="H47">
+        <v>4.39</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.05</v>
+      </c>
+      <c r="K47">
+        <v>0.989</v>
+      </c>
+      <c r="L47">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M47">
+        <v>0.7489962</v>
+      </c>
+      <c r="N47">
+        <v>-0.6879961999999999</v>
+      </c>
+      <c r="O47">
+        <v>-0.10319943</v>
+      </c>
+      <c r="P47">
+        <v>-0.58479677</v>
+      </c>
+      <c r="Q47">
+        <v>0.40420323</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2218059591203224</v>
+      </c>
+      <c r="T47">
+        <v>0.9705145185646431</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.01221635036332629</v>
+      </c>
+      <c r="W47">
+        <v>0.2358827355332377</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.08144233575550863</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2301405085061343</v>
+      </c>
+      <c r="C48">
+        <v>1.467775611068753</v>
+      </c>
+      <c r="D48">
+        <v>4.323975611068753</v>
+      </c>
+      <c r="E48">
+        <v>0.6261999999999999</v>
+      </c>
+      <c r="F48">
+        <v>3.2062</v>
+      </c>
+      <c r="G48">
+        <v>0.35</v>
+      </c>
+      <c r="H48">
+        <v>4.39</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.05</v>
+      </c>
+      <c r="K48">
+        <v>0.989</v>
+      </c>
+      <c r="L48">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M48">
+        <v>0.76564056</v>
+      </c>
+      <c r="N48">
+        <v>-0.70464056</v>
+      </c>
+      <c r="O48">
+        <v>-0.105696084</v>
+      </c>
+      <c r="P48">
+        <v>-0.598944476</v>
+      </c>
+      <c r="Q48">
+        <v>0.390055524</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2251949583632913</v>
+      </c>
+      <c r="T48">
+        <v>0.9884870096491735</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.01195077752934093</v>
+      </c>
+      <c r="W48">
+        <v>0.2359461543259934</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.07967185019560619</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2321405085061343</v>
+      </c>
+      <c r="C49">
+        <v>1.353346488915527</v>
+      </c>
+      <c r="D49">
+        <v>4.279246488915527</v>
+      </c>
+      <c r="E49">
+        <v>0.6959</v>
+      </c>
+      <c r="F49">
+        <v>3.2759</v>
+      </c>
+      <c r="G49">
+        <v>0.35</v>
+      </c>
+      <c r="H49">
+        <v>4.39</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.05</v>
+      </c>
+      <c r="K49">
+        <v>0.989</v>
+      </c>
+      <c r="L49">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M49">
+        <v>0.7822849200000001</v>
+      </c>
+      <c r="N49">
+        <v>-0.72128492</v>
+      </c>
+      <c r="O49">
+        <v>-0.108192738</v>
+      </c>
+      <c r="P49">
+        <v>-0.6130921819999999</v>
+      </c>
+      <c r="Q49">
+        <v>0.3759078180000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2287118443701459</v>
+      </c>
+      <c r="T49">
+        <v>1.007137707944441</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.01169650566701453</v>
+      </c>
+      <c r="W49">
+        <v>0.2360068744467169</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.07797670444676352</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2341405085061343</v>
+      </c>
+      <c r="C50">
+        <v>1.239833287837666</v>
+      </c>
+      <c r="D50">
+        <v>4.235433287837666</v>
+      </c>
+      <c r="E50">
+        <v>0.7655999999999996</v>
+      </c>
+      <c r="F50">
+        <v>3.3456</v>
+      </c>
+      <c r="G50">
+        <v>0.35</v>
+      </c>
+      <c r="H50">
+        <v>4.39</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.05</v>
+      </c>
+      <c r="K50">
+        <v>0.989</v>
+      </c>
+      <c r="L50">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M50">
+        <v>0.79892928</v>
+      </c>
+      <c r="N50">
+        <v>-0.7379292799999999</v>
+      </c>
+      <c r="O50">
+        <v>-0.110689392</v>
+      </c>
+      <c r="P50">
+        <v>-0.6272398879999999</v>
+      </c>
+      <c r="Q50">
+        <v>0.3617601120000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2323639952234179</v>
+      </c>
+      <c r="T50">
+        <v>1.026505740789526</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.0114528284656184</v>
+      </c>
+      <c r="W50">
+        <v>0.2360650645624104</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.07635218977078928</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2361405085061343</v>
+      </c>
+      <c r="C51">
+        <v>1.127208159896121</v>
+      </c>
+      <c r="D51">
+        <v>4.192508159896121</v>
+      </c>
+      <c r="E51">
+        <v>0.8352999999999997</v>
+      </c>
+      <c r="F51">
+        <v>3.4153</v>
+      </c>
+      <c r="G51">
+        <v>0.35</v>
+      </c>
+      <c r="H51">
+        <v>4.39</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.05</v>
+      </c>
+      <c r="K51">
+        <v>0.989</v>
+      </c>
+      <c r="L51">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M51">
+        <v>0.81557364</v>
+      </c>
+      <c r="N51">
+        <v>-0.7545736399999999</v>
+      </c>
+      <c r="O51">
+        <v>-0.113186046</v>
+      </c>
+      <c r="P51">
+        <v>-0.6413875939999999</v>
+      </c>
+      <c r="Q51">
+        <v>0.3476124060000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.236159367678779</v>
+      </c>
+      <c r="T51">
+        <v>1.046633304334419</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.01121909727244251</v>
+      </c>
+      <c r="W51">
+        <v>0.2361208795713407</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.07479398181628338</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2381405085061343</v>
+      </c>
+      <c r="C52">
+        <v>1.015444374754657</v>
+      </c>
+      <c r="D52">
+        <v>4.150444374754657</v>
+      </c>
+      <c r="E52">
+        <v>0.9049999999999998</v>
+      </c>
+      <c r="F52">
+        <v>3.485</v>
+      </c>
+      <c r="G52">
+        <v>0.35</v>
+      </c>
+      <c r="H52">
+        <v>4.39</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.05</v>
+      </c>
+      <c r="K52">
+        <v>0.989</v>
+      </c>
+      <c r="L52">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M52">
+        <v>0.832218</v>
+      </c>
+      <c r="N52">
+        <v>-0.771218</v>
+      </c>
+      <c r="O52">
+        <v>-0.1156827</v>
+      </c>
+      <c r="P52">
+        <v>-0.6555352999999999</v>
+      </c>
+      <c r="Q52">
+        <v>0.3334647000000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2401065550323546</v>
+      </c>
+      <c r="T52">
+        <v>1.067565970421107</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.01099471532699366</v>
+      </c>
+      <c r="W52">
+        <v>0.2361744619799139</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.07329810217995769</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2401405085061343</v>
+      </c>
+      <c r="C53">
+        <v>0.9045162641717517</v>
+      </c>
+      <c r="D53">
+        <v>4.109216264171752</v>
+      </c>
+      <c r="E53">
+        <v>0.9746999999999999</v>
+      </c>
+      <c r="F53">
+        <v>3.5547</v>
+      </c>
+      <c r="G53">
+        <v>0.35</v>
+      </c>
+      <c r="H53">
+        <v>4.39</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.05</v>
+      </c>
+      <c r="K53">
+        <v>0.989</v>
+      </c>
+      <c r="L53">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M53">
+        <v>0.84886236</v>
+      </c>
+      <c r="N53">
+        <v>-0.78786236</v>
+      </c>
+      <c r="O53">
+        <v>-0.118179354</v>
+      </c>
+      <c r="P53">
+        <v>-0.669683006</v>
+      </c>
+      <c r="Q53">
+        <v>0.319316994</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2442148520738313</v>
+      </c>
+      <c r="T53">
+        <v>1.089353031041946</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.0107791326735232</v>
+      </c>
+      <c r="W53">
+        <v>0.2362259431175627</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.0718608844901546</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2421405085061343</v>
+      </c>
+      <c r="C54">
+        <v>0.794399169768274</v>
+      </c>
+      <c r="D54">
+        <v>4.068799169768274</v>
+      </c>
+      <c r="E54">
+        <v>1.0444</v>
+      </c>
+      <c r="F54">
+        <v>3.6244</v>
+      </c>
+      <c r="G54">
+        <v>0.35</v>
+      </c>
+      <c r="H54">
+        <v>4.39</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.05</v>
+      </c>
+      <c r="K54">
+        <v>0.989</v>
+      </c>
+      <c r="L54">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M54">
+        <v>0.8655067200000001</v>
+      </c>
+      <c r="N54">
+        <v>-0.80450672</v>
+      </c>
+      <c r="O54">
+        <v>-0.120676008</v>
+      </c>
+      <c r="P54">
+        <v>-0.683830712</v>
+      </c>
+      <c r="Q54">
+        <v>0.305169288</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2484943281587027</v>
+      </c>
+      <c r="T54">
+        <v>1.11204788585532</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.01057184166057083</v>
+      </c>
+      <c r="W54">
+        <v>0.2362754442114557</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.07047894440380553</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2441405085061343</v>
+      </c>
+      <c r="C55">
+        <v>0.6850693938475936</v>
+      </c>
+      <c r="D55">
+        <v>4.029169393847594</v>
+      </c>
+      <c r="E55">
+        <v>1.1141</v>
+      </c>
+      <c r="F55">
+        <v>3.6941</v>
+      </c>
+      <c r="G55">
+        <v>0.35</v>
+      </c>
+      <c r="H55">
+        <v>4.39</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.05</v>
+      </c>
+      <c r="K55">
+        <v>0.989</v>
+      </c>
+      <c r="L55">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M55">
+        <v>0.8821510800000001</v>
+      </c>
+      <c r="N55">
+        <v>-0.82115108</v>
+      </c>
+      <c r="O55">
+        <v>-0.123172662</v>
+      </c>
+      <c r="P55">
+        <v>-0.697978418</v>
+      </c>
+      <c r="Q55">
+        <v>0.2910215819999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2529559096088879</v>
+      </c>
+      <c r="T55">
+        <v>1.135708479171391</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.01037237294999402</v>
+      </c>
+      <c r="W55">
+        <v>0.2363230773395414</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.06914915299996016</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2461405085061343</v>
+      </c>
+      <c r="C56">
+        <v>0.5765041530620159</v>
+      </c>
+      <c r="D56">
+        <v>3.990304153062016</v>
+      </c>
+      <c r="E56">
+        <v>1.1838</v>
+      </c>
+      <c r="F56">
+        <v>3.7638</v>
+      </c>
+      <c r="G56">
+        <v>0.35</v>
+      </c>
+      <c r="H56">
+        <v>4.39</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.05</v>
+      </c>
+      <c r="K56">
+        <v>0.989</v>
+      </c>
+      <c r="L56">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M56">
+        <v>0.8987954400000001</v>
+      </c>
+      <c r="N56">
+        <v>-0.8377954400000001</v>
+      </c>
+      <c r="O56">
+        <v>-0.125669316</v>
+      </c>
+      <c r="P56">
+        <v>-0.7121261240000001</v>
+      </c>
+      <c r="Q56">
+        <v>0.2768738759999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.257611472861255</v>
+      </c>
+      <c r="T56">
+        <v>1.160397793935986</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.01018029196943857</v>
+      </c>
+      <c r="W56">
+        <v>0.2363689462776981</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.06786861312959047</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2481405085061343</v>
+      </c>
+      <c r="C57">
+        <v>0.4686815347351856</v>
+      </c>
+      <c r="D57">
+        <v>3.952181534735186</v>
+      </c>
+      <c r="E57">
+        <v>1.2535</v>
+      </c>
+      <c r="F57">
+        <v>3.8335</v>
+      </c>
+      <c r="G57">
+        <v>0.35</v>
+      </c>
+      <c r="H57">
+        <v>4.39</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.05</v>
+      </c>
+      <c r="K57">
+        <v>0.989</v>
+      </c>
+      <c r="L57">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M57">
+        <v>0.9154398000000001</v>
+      </c>
+      <c r="N57">
+        <v>-0.8544398000000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.12816597</v>
+      </c>
+      <c r="P57">
+        <v>-0.72627383</v>
+      </c>
+      <c r="Q57">
+        <v>0.26272617</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2624739500359495</v>
+      </c>
+      <c r="T57">
+        <v>1.186184411579008</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.009995195751812416</v>
+      </c>
+      <c r="W57">
+        <v>0.2364131472544672</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.06663463834541605</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2501405085061343</v>
+      </c>
+      <c r="C58">
+        <v>0.3615804556645297</v>
+      </c>
+      <c r="D58">
+        <v>3.91478045566453</v>
+      </c>
+      <c r="E58">
+        <v>1.3232</v>
+      </c>
+      <c r="F58">
+        <v>3.9032</v>
+      </c>
+      <c r="G58">
+        <v>0.35</v>
+      </c>
+      <c r="H58">
+        <v>4.39</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.05</v>
+      </c>
+      <c r="K58">
+        <v>0.989</v>
+      </c>
+      <c r="L58">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M58">
+        <v>0.9320841600000002</v>
+      </c>
+      <c r="N58">
+        <v>-0.8710841600000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.130662624</v>
+      </c>
+      <c r="P58">
+        <v>-0.740421536</v>
+      </c>
+      <c r="Q58">
+        <v>0.2485784639999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.267557448900403</v>
+      </c>
+      <c r="T58">
+        <v>1.213143148205804</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.009816710113387193</v>
+      </c>
+      <c r="W58">
+        <v>0.2364557696249232</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.065444734089248</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2521405085061343</v>
+      </c>
+      <c r="C59">
+        <v>0.2551806232409843</v>
+      </c>
+      <c r="D59">
+        <v>3.878080623240984</v>
+      </c>
+      <c r="E59">
+        <v>1.3929</v>
+      </c>
+      <c r="F59">
+        <v>3.9729</v>
+      </c>
+      <c r="G59">
+        <v>0.35</v>
+      </c>
+      <c r="H59">
+        <v>4.39</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.05</v>
+      </c>
+      <c r="K59">
+        <v>0.989</v>
+      </c>
+      <c r="L59">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M59">
+        <v>0.9487285200000001</v>
+      </c>
+      <c r="N59">
+        <v>-0.88772852</v>
+      </c>
+      <c r="O59">
+        <v>-0.133159278</v>
+      </c>
+      <c r="P59">
+        <v>-0.754569242</v>
+      </c>
+      <c r="Q59">
+        <v>0.234430758</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2728773895725054</v>
+      </c>
+      <c r="T59">
+        <v>1.241355779559427</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.009644487128941805</v>
+      </c>
+      <c r="W59">
+        <v>0.2364968964736087</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.06429658085961198</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2541405085061342</v>
+      </c>
+      <c r="C60">
+        <v>0.1494624987353461</v>
+      </c>
+      <c r="D60">
+        <v>3.842062498735345</v>
+      </c>
+      <c r="E60">
+        <v>1.462599999999999</v>
+      </c>
+      <c r="F60">
+        <v>4.042599999999999</v>
+      </c>
+      <c r="G60">
+        <v>0.35</v>
+      </c>
+      <c r="H60">
+        <v>4.39</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.05</v>
+      </c>
+      <c r="K60">
+        <v>0.989</v>
+      </c>
+      <c r="L60">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M60">
+        <v>0.9653728799999999</v>
+      </c>
+      <c r="N60">
+        <v>-0.9043728799999998</v>
+      </c>
+      <c r="O60">
+        <v>-0.135655932</v>
+      </c>
+      <c r="P60">
+        <v>-0.7687169479999998</v>
+      </c>
+      <c r="Q60">
+        <v>0.2202830520000002</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2784506607528031</v>
+      </c>
+      <c r="T60">
+        <v>1.270911869548937</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.009478202868097984</v>
+      </c>
+      <c r="W60">
+        <v>0.2365366051550982</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.06318801912065319</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2561405085061342</v>
+      </c>
+      <c r="C61">
+        <v>0.04440726261168493</v>
+      </c>
+      <c r="D61">
+        <v>3.806707262611685</v>
+      </c>
+      <c r="E61">
+        <v>1.532299999999999</v>
+      </c>
+      <c r="F61">
+        <v>4.112299999999999</v>
+      </c>
+      <c r="G61">
+        <v>0.35</v>
+      </c>
+      <c r="H61">
+        <v>4.39</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.05</v>
+      </c>
+      <c r="K61">
+        <v>0.989</v>
+      </c>
+      <c r="L61">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M61">
+        <v>0.9820172399999999</v>
+      </c>
+      <c r="N61">
+        <v>-0.9210172399999998</v>
+      </c>
+      <c r="O61">
+        <v>-0.138152586</v>
+      </c>
+      <c r="P61">
+        <v>-0.7828646539999998</v>
+      </c>
+      <c r="Q61">
+        <v>0.2061353460000002</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2842957988199447</v>
+      </c>
+      <c r="T61">
+        <v>1.301909720025741</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.009317555361859036</v>
+      </c>
+      <c r="W61">
+        <v>0.2365749677795881</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.06211703574572691</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2581405085061342</v>
+      </c>
+      <c r="C62">
+        <v>-0.06000321826152888</v>
+      </c>
+      <c r="D62">
+        <v>3.771996781738471</v>
+      </c>
+      <c r="E62">
+        <v>1.601999999999999</v>
+      </c>
+      <c r="F62">
+        <v>4.181999999999999</v>
+      </c>
+      <c r="G62">
+        <v>0.35</v>
+      </c>
+      <c r="H62">
+        <v>4.39</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.05</v>
+      </c>
+      <c r="K62">
+        <v>0.989</v>
+      </c>
+      <c r="L62">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M62">
+        <v>0.9986615999999999</v>
+      </c>
+      <c r="N62">
+        <v>-0.9376615999999999</v>
+      </c>
+      <c r="O62">
+        <v>-0.14064924</v>
+      </c>
+      <c r="P62">
+        <v>-0.7970123599999999</v>
+      </c>
+      <c r="Q62">
+        <v>0.1919876400000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2904331937904432</v>
+      </c>
+      <c r="T62">
+        <v>1.334457463026384</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.009162262772494717</v>
+      </c>
+      <c r="W62">
+        <v>0.2366120516499283</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.06108175181663145</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2601405085061343</v>
+      </c>
+      <c r="C63">
+        <v>-0.1637864216226896</v>
+      </c>
+      <c r="D63">
+        <v>3.73791357837731</v>
+      </c>
+      <c r="E63">
+        <v>1.6717</v>
+      </c>
+      <c r="F63">
+        <v>4.2517</v>
+      </c>
+      <c r="G63">
+        <v>0.35</v>
+      </c>
+      <c r="H63">
+        <v>4.39</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.05</v>
+      </c>
+      <c r="K63">
+        <v>0.989</v>
+      </c>
+      <c r="L63">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M63">
+        <v>1.01530596</v>
+      </c>
+      <c r="N63">
+        <v>-0.95430596</v>
+      </c>
+      <c r="O63">
+        <v>-0.143145894</v>
+      </c>
+      <c r="P63">
+        <v>-0.811160066</v>
+      </c>
+      <c r="Q63">
+        <v>0.177839934</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2968853269645572</v>
+      </c>
+      <c r="T63">
+        <v>1.368674321052702</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.009012061743437426</v>
+      </c>
+      <c r="W63">
+        <v>0.2366479196556672</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.06008041162291611</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2621405085061343</v>
+      </c>
+      <c r="C64">
+        <v>-0.2669591991620557</v>
+      </c>
+      <c r="D64">
+        <v>3.704440800837944</v>
+      </c>
+      <c r="E64">
+        <v>1.7414</v>
+      </c>
+      <c r="F64">
+        <v>4.3214</v>
+      </c>
+      <c r="G64">
+        <v>0.35</v>
+      </c>
+      <c r="H64">
+        <v>4.39</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.05</v>
+      </c>
+      <c r="K64">
+        <v>0.989</v>
+      </c>
+      <c r="L64">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M64">
+        <v>1.03195032</v>
+      </c>
+      <c r="N64">
+        <v>-0.9709503199999999</v>
+      </c>
+      <c r="O64">
+        <v>-0.145642548</v>
+      </c>
+      <c r="P64">
+        <v>-0.8253077719999999</v>
+      </c>
+      <c r="Q64">
+        <v>0.1636922280000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3036770460952035</v>
+      </c>
+      <c r="T64">
+        <v>1.404692066343562</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.008866705908865855</v>
+      </c>
+      <c r="W64">
+        <v>0.2366826306289629</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.05911137272577238</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2641405085061342</v>
+      </c>
+      <c r="C65">
+        <v>-0.3695378043040787</v>
+      </c>
+      <c r="D65">
+        <v>3.671562195695921</v>
+      </c>
+      <c r="E65">
+        <v>1.8111</v>
+      </c>
+      <c r="F65">
+        <v>4.3911</v>
+      </c>
+      <c r="G65">
+        <v>0.35</v>
+      </c>
+      <c r="H65">
+        <v>4.39</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.05</v>
+      </c>
+      <c r="K65">
+        <v>0.989</v>
+      </c>
+      <c r="L65">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M65">
+        <v>1.04859468</v>
+      </c>
+      <c r="N65">
+        <v>-0.9875946800000001</v>
+      </c>
+      <c r="O65">
+        <v>-0.148139202</v>
+      </c>
+      <c r="P65">
+        <v>-0.8394554780000001</v>
+      </c>
+      <c r="Q65">
+        <v>0.1495445219999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3108358851788576</v>
+      </c>
+      <c r="T65">
+        <v>1.44265671678528</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.008725964545233063</v>
+      </c>
+      <c r="W65">
+        <v>0.2367162396665984</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.05817309696822037</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2661405085061343</v>
+      </c>
+      <c r="C66">
+        <v>-0.4715379185232469</v>
+      </c>
+      <c r="D66">
+        <v>3.639262081476753</v>
+      </c>
+      <c r="E66">
+        <v>1.8808</v>
+      </c>
+      <c r="F66">
+        <v>4.4608</v>
+      </c>
+      <c r="G66">
+        <v>0.35</v>
+      </c>
+      <c r="H66">
+        <v>4.39</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.05</v>
+      </c>
+      <c r="K66">
+        <v>0.989</v>
+      </c>
+      <c r="L66">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M66">
+        <v>1.06523904</v>
+      </c>
+      <c r="N66">
+        <v>-1.00423904</v>
+      </c>
+      <c r="O66">
+        <v>-0.150635856</v>
+      </c>
+      <c r="P66">
+        <v>-0.8536031839999998</v>
+      </c>
+      <c r="Q66">
+        <v>0.1353968160000002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.318392437544937</v>
+      </c>
+      <c r="T66">
+        <v>1.48273051447376</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.008589621349213797</v>
+      </c>
+      <c r="W66">
+        <v>0.2367487984218078</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.05726414232809207</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2681405085061342</v>
+      </c>
+      <c r="C67">
+        <v>-0.5729746762829802</v>
+      </c>
+      <c r="D67">
+        <v>3.60752532371702</v>
+      </c>
+      <c r="E67">
+        <v>1.9505</v>
+      </c>
+      <c r="F67">
+        <v>4.5305</v>
+      </c>
+      <c r="G67">
+        <v>0.35</v>
+      </c>
+      <c r="H67">
+        <v>4.39</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.05</v>
+      </c>
+      <c r="K67">
+        <v>0.989</v>
+      </c>
+      <c r="L67">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M67">
+        <v>1.0818834</v>
+      </c>
+      <c r="N67">
+        <v>-1.0208834</v>
+      </c>
+      <c r="O67">
+        <v>-0.15313251</v>
+      </c>
+      <c r="P67">
+        <v>-0.8677508899999997</v>
+      </c>
+      <c r="Q67">
+        <v>0.1212491100000003</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3263807929033638</v>
+      </c>
+      <c r="T67">
+        <v>1.525094243458725</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.008457473328456661</v>
+      </c>
+      <c r="W67">
+        <v>0.2367803553691646</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.05638315552304451</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2701405085061343</v>
+      </c>
+      <c r="C68">
+        <v>-0.6738626886809165</v>
+      </c>
+      <c r="D68">
+        <v>3.576337311319084</v>
+      </c>
+      <c r="E68">
+        <v>2.0202</v>
+      </c>
+      <c r="F68">
+        <v>4.6002</v>
+      </c>
+      <c r="G68">
+        <v>0.35</v>
+      </c>
+      <c r="H68">
+        <v>4.39</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.05</v>
+      </c>
+      <c r="K68">
+        <v>0.989</v>
+      </c>
+      <c r="L68">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M68">
+        <v>1.09852776</v>
+      </c>
+      <c r="N68">
+        <v>-1.03752776</v>
+      </c>
+      <c r="O68">
+        <v>-0.155629164</v>
+      </c>
+      <c r="P68">
+        <v>-0.8818985960000001</v>
+      </c>
+      <c r="Q68">
+        <v>0.1071014039999999</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3348390515181686</v>
+      </c>
+      <c r="T68">
+        <v>1.569949956501629</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.008329329793177015</v>
+      </c>
+      <c r="W68">
+        <v>0.2368109560453893</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.05552886528784662</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2721405085061343</v>
+      </c>
+      <c r="C69">
+        <v>-0.7742160658781732</v>
+      </c>
+      <c r="D69">
+        <v>3.545683934121827</v>
+      </c>
+      <c r="E69">
+        <v>2.0899</v>
+      </c>
+      <c r="F69">
+        <v>4.6699</v>
+      </c>
+      <c r="G69">
+        <v>0.35</v>
+      </c>
+      <c r="H69">
+        <v>4.39</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.05</v>
+      </c>
+      <c r="K69">
+        <v>0.989</v>
+      </c>
+      <c r="L69">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M69">
+        <v>1.11517212</v>
+      </c>
+      <c r="N69">
+        <v>-1.05417212</v>
+      </c>
+      <c r="O69">
+        <v>-0.158125818</v>
+      </c>
+      <c r="P69">
+        <v>-0.896046302</v>
+      </c>
+      <c r="Q69">
+        <v>0.09295369799999997</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.343809931867204</v>
+      </c>
+      <c r="T69">
+        <v>1.617524197607739</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.008205011438054971</v>
+      </c>
+      <c r="W69">
+        <v>0.2368406432685925</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.05470007625369966</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2741405085061343</v>
+      </c>
+      <c r="C70">
+        <v>-0.8740484383849609</v>
+      </c>
+      <c r="D70">
+        <v>3.515551561615039</v>
+      </c>
+      <c r="E70">
+        <v>2.1596</v>
+      </c>
+      <c r="F70">
+        <v>4.7396</v>
+      </c>
+      <c r="G70">
+        <v>0.35</v>
+      </c>
+      <c r="H70">
+        <v>4.39</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.05</v>
+      </c>
+      <c r="K70">
+        <v>0.989</v>
+      </c>
+      <c r="L70">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M70">
+        <v>1.13181648</v>
+      </c>
+      <c r="N70">
+        <v>-1.07081648</v>
+      </c>
+      <c r="O70">
+        <v>-0.160622472</v>
+      </c>
+      <c r="P70">
+        <v>-0.9101940079999999</v>
+      </c>
+      <c r="Q70">
+        <v>0.07880599200000005</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3533414922380542</v>
+      </c>
+      <c r="T70">
+        <v>1.668071828782981</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.008084349505142396</v>
+      </c>
+      <c r="W70">
+        <v>0.236869457338172</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.05389566336761609</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2761405085061343</v>
+      </c>
+      <c r="C71">
+        <v>-0.9733729772699795</v>
+      </c>
+      <c r="D71">
+        <v>3.485927022730021</v>
+      </c>
+      <c r="E71">
+        <v>2.2293</v>
+      </c>
+      <c r="F71">
+        <v>4.8093</v>
+      </c>
+      <c r="G71">
+        <v>0.35</v>
+      </c>
+      <c r="H71">
+        <v>4.39</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.05</v>
+      </c>
+      <c r="K71">
+        <v>0.989</v>
+      </c>
+      <c r="L71">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M71">
+        <v>1.14846084</v>
+      </c>
+      <c r="N71">
+        <v>-1.08746084</v>
+      </c>
+      <c r="O71">
+        <v>-0.163119126</v>
+      </c>
+      <c r="P71">
+        <v>-0.9243417139999999</v>
+      </c>
+      <c r="Q71">
+        <v>0.06465828600000012</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3634879919876688</v>
+      </c>
+      <c r="T71">
+        <v>1.721880597453399</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.007967185019560622</v>
+      </c>
+      <c r="W71">
+        <v>0.2368974362173289</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.05311456679707094</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2781405085061343</v>
+      </c>
+      <c r="C72">
+        <v>-1.072202413356564</v>
+      </c>
+      <c r="D72">
+        <v>3.456797586643437</v>
+      </c>
+      <c r="E72">
+        <v>2.299</v>
+      </c>
+      <c r="F72">
+        <v>4.879</v>
+      </c>
+      <c r="G72">
+        <v>0.35</v>
+      </c>
+      <c r="H72">
+        <v>4.39</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.05</v>
+      </c>
+      <c r="K72">
+        <v>0.989</v>
+      </c>
+      <c r="L72">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M72">
+        <v>1.1651052</v>
+      </c>
+      <c r="N72">
+        <v>-1.1041052</v>
+      </c>
+      <c r="O72">
+        <v>-0.16561578</v>
+      </c>
+      <c r="P72">
+        <v>-0.9384894200000002</v>
+      </c>
+      <c r="Q72">
+        <v>0.05051057999999975</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3743109250539244</v>
+      </c>
+      <c r="T72">
+        <v>1.779276617368513</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.007853368090709755</v>
+      </c>
+      <c r="W72">
+        <v>0.2369246156999385</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.05235578727139822</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2801405085061343</v>
+      </c>
+      <c r="C73">
+        <v>-1.170549055464351</v>
+      </c>
+      <c r="D73">
+        <v>3.428150944535648</v>
+      </c>
+      <c r="E73">
+        <v>2.3687</v>
+      </c>
+      <c r="F73">
+        <v>4.9487</v>
+      </c>
+      <c r="G73">
+        <v>0.35</v>
+      </c>
+      <c r="H73">
+        <v>4.39</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.05</v>
+      </c>
+      <c r="K73">
+        <v>0.989</v>
+      </c>
+      <c r="L73">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M73">
+        <v>1.18174956</v>
+      </c>
+      <c r="N73">
+        <v>-1.12074956</v>
+      </c>
+      <c r="O73">
+        <v>-0.168112434</v>
+      </c>
+      <c r="P73">
+        <v>-0.9526371260000002</v>
+      </c>
+      <c r="Q73">
+        <v>0.03636287399999982</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3858802672971631</v>
+      </c>
+      <c r="T73">
+        <v>1.840630983484668</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.007742757272530746</v>
+      </c>
+      <c r="W73">
+        <v>0.2369510295633197</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.05161838181687151</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2821405085061343</v>
+      </c>
+      <c r="C74">
+        <v>-1.268424807751392</v>
+      </c>
+      <c r="D74">
+        <v>3.399975192248608</v>
+      </c>
+      <c r="E74">
+        <v>2.4384</v>
+      </c>
+      <c r="F74">
+        <v>5.0184</v>
+      </c>
+      <c r="G74">
+        <v>0.35</v>
+      </c>
+      <c r="H74">
+        <v>4.39</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.05</v>
+      </c>
+      <c r="K74">
+        <v>0.989</v>
+      </c>
+      <c r="L74">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M74">
+        <v>1.19839392</v>
+      </c>
+      <c r="N74">
+        <v>-1.13739392</v>
+      </c>
+      <c r="O74">
+        <v>-0.170609088</v>
+      </c>
+      <c r="P74">
+        <v>-0.966784832</v>
+      </c>
+      <c r="Q74">
+        <v>0.02221516800000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3982759911292046</v>
+      </c>
+      <c r="T74">
+        <v>1.906367804323406</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.00763521897707893</v>
+      </c>
+      <c r="W74">
+        <v>0.2369767097082736</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.05090145984719274</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2841405085061343</v>
+      </c>
+      <c r="C75">
+        <v>-1.365841186208019</v>
+      </c>
+      <c r="D75">
+        <v>3.372258813791981</v>
+      </c>
+      <c r="E75">
+        <v>2.5081</v>
+      </c>
+      <c r="F75">
+        <v>5.0881</v>
+      </c>
+      <c r="G75">
+        <v>0.35</v>
+      </c>
+      <c r="H75">
+        <v>4.39</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.05</v>
+      </c>
+      <c r="K75">
+        <v>0.989</v>
+      </c>
+      <c r="L75">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M75">
+        <v>1.21503828</v>
+      </c>
+      <c r="N75">
+        <v>-1.15403828</v>
+      </c>
+      <c r="O75">
+        <v>-0.173105742</v>
+      </c>
+      <c r="P75">
+        <v>-0.9809325379999999</v>
+      </c>
+      <c r="Q75">
+        <v>0.008067462000000081</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4115899167265826</v>
+      </c>
+      <c r="T75">
+        <v>1.976974019298347</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.007530626936297028</v>
+      </c>
+      <c r="W75">
+        <v>0.2370016862876123</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.05020417957531342</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2861405085061343</v>
+      </c>
+      <c r="C76">
+        <v>-1.462809334350508</v>
+      </c>
+      <c r="D76">
+        <v>3.344990665649492</v>
+      </c>
+      <c r="E76">
+        <v>2.5778</v>
+      </c>
+      <c r="F76">
+        <v>5.1578</v>
+      </c>
+      <c r="G76">
+        <v>0.35</v>
+      </c>
+      <c r="H76">
+        <v>4.39</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.05</v>
+      </c>
+      <c r="K76">
+        <v>0.989</v>
+      </c>
+      <c r="L76">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M76">
+        <v>1.23168264</v>
+      </c>
+      <c r="N76">
+        <v>-1.17068264</v>
+      </c>
+      <c r="O76">
+        <v>-0.175602396</v>
+      </c>
+      <c r="P76">
+        <v>-0.9950802439999998</v>
+      </c>
+      <c r="Q76">
+        <v>-0.006080243999999846</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4259279904468358</v>
+      </c>
+      <c r="T76">
+        <v>2.053011481579052</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.007428861707428148</v>
+      </c>
+      <c r="W76">
+        <v>0.2370259878242661</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.04952574471618776</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2881405085061343</v>
+      </c>
+      <c r="C77">
+        <v>-1.55934003815945</v>
+      </c>
+      <c r="D77">
+        <v>3.31815996184055</v>
+      </c>
+      <c r="E77">
+        <v>2.6475</v>
+      </c>
+      <c r="F77">
+        <v>5.2275</v>
+      </c>
+      <c r="G77">
+        <v>0.35</v>
+      </c>
+      <c r="H77">
+        <v>4.39</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.05</v>
+      </c>
+      <c r="K77">
+        <v>0.989</v>
+      </c>
+      <c r="L77">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M77">
+        <v>1.248327</v>
+      </c>
+      <c r="N77">
+        <v>-1.187327</v>
+      </c>
+      <c r="O77">
+        <v>-0.17809905</v>
+      </c>
+      <c r="P77">
+        <v>-1.00922795</v>
+      </c>
+      <c r="Q77">
+        <v>-0.02022794999999988</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4414131100647092</v>
+      </c>
+      <c r="T77">
+        <v>2.135131940842215</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.007329810217995773</v>
+      </c>
+      <c r="W77">
+        <v>0.2370496413199426</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.0488654014533052</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2901405085061343</v>
+      </c>
+      <c r="C78">
+        <v>-1.655443740304896</v>
+      </c>
+      <c r="D78">
+        <v>3.291756259695104</v>
+      </c>
+      <c r="E78">
+        <v>2.7172</v>
+      </c>
+      <c r="F78">
+        <v>5.2972</v>
+      </c>
+      <c r="G78">
+        <v>0.35</v>
+      </c>
+      <c r="H78">
+        <v>4.39</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.05</v>
+      </c>
+      <c r="K78">
+        <v>0.989</v>
+      </c>
+      <c r="L78">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M78">
+        <v>1.26497136</v>
+      </c>
+      <c r="N78">
+        <v>-1.20397136</v>
+      </c>
+      <c r="O78">
+        <v>-0.1805957040000001</v>
+      </c>
+      <c r="P78">
+        <v>-1.023375656</v>
+      </c>
+      <c r="Q78">
+        <v>-0.03437565600000003</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4581886563174055</v>
+      </c>
+      <c r="T78">
+        <v>2.22409577171064</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.007233365346706355</v>
+      </c>
+      <c r="W78">
+        <v>0.2370726723552065</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.04822243564470896</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2921405085061343</v>
+      </c>
+      <c r="C79">
+        <v>-1.751130553697713</v>
+      </c>
+      <c r="D79">
+        <v>3.265769446302287</v>
+      </c>
+      <c r="E79">
+        <v>2.7869</v>
+      </c>
+      <c r="F79">
+        <v>5.3669</v>
+      </c>
+      <c r="G79">
+        <v>0.35</v>
+      </c>
+      <c r="H79">
+        <v>4.39</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.05</v>
+      </c>
+      <c r="K79">
+        <v>0.989</v>
+      </c>
+      <c r="L79">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M79">
+        <v>1.28161572</v>
+      </c>
+      <c r="N79">
+        <v>-1.22061572</v>
+      </c>
+      <c r="O79">
+        <v>-0.183092358</v>
+      </c>
+      <c r="P79">
+        <v>-1.037523362</v>
+      </c>
+      <c r="Q79">
+        <v>-0.04852336199999996</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4764229457225101</v>
+      </c>
+      <c r="T79">
+        <v>2.320795587871973</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.00713942553700887</v>
+      </c>
+      <c r="W79">
+        <v>0.2370951051817623</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.04759617024672569</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2941405085061343</v>
+      </c>
+      <c r="C80">
+        <v>-1.846410274404064</v>
+      </c>
+      <c r="D80">
+        <v>3.240189725595936</v>
+      </c>
+      <c r="E80">
+        <v>2.8566</v>
+      </c>
+      <c r="F80">
+        <v>5.4366</v>
+      </c>
+      <c r="G80">
+        <v>0.35</v>
+      </c>
+      <c r="H80">
+        <v>4.39</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.05</v>
+      </c>
+      <c r="K80">
+        <v>0.989</v>
+      </c>
+      <c r="L80">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M80">
+        <v>1.29826008</v>
+      </c>
+      <c r="N80">
+        <v>-1.23726008</v>
+      </c>
+      <c r="O80">
+        <v>-0.185589012</v>
+      </c>
+      <c r="P80">
+        <v>-1.051671068</v>
+      </c>
+      <c r="Q80">
+        <v>-0.06267106799999989</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.496314897800806</v>
+      </c>
+      <c r="T80">
+        <v>2.426286296411608</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.00704789444038055</v>
+      </c>
+      <c r="W80">
+        <v>0.2371169628076371</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.04698596293587043</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2961405085061343</v>
+      </c>
+      <c r="C81">
+        <v>-1.941292393957689</v>
+      </c>
+      <c r="D81">
+        <v>3.215007606042311</v>
+      </c>
+      <c r="E81">
+        <v>2.9263</v>
+      </c>
+      <c r="F81">
+        <v>5.5063</v>
+      </c>
+      <c r="G81">
+        <v>0.35</v>
+      </c>
+      <c r="H81">
+        <v>4.39</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.05</v>
+      </c>
+      <c r="K81">
+        <v>0.989</v>
+      </c>
+      <c r="L81">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M81">
+        <v>1.31490444</v>
+      </c>
+      <c r="N81">
+        <v>-1.25390444</v>
+      </c>
+      <c r="O81">
+        <v>-0.188085666</v>
+      </c>
+      <c r="P81">
+        <v>-1.065818774</v>
+      </c>
+      <c r="Q81">
+        <v>-0.07681877399999981</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5181013215056064</v>
+      </c>
+      <c r="T81">
+        <v>2.541823739097875</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.006958680586704847</v>
+      </c>
+      <c r="W81">
+        <v>0.2371382670758949</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.04639120391136575</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2981405085061343</v>
+      </c>
+      <c r="C82">
+        <v>-2.03578611110247</v>
+      </c>
+      <c r="D82">
+        <v>3.190213888897531</v>
+      </c>
+      <c r="E82">
+        <v>2.996</v>
+      </c>
+      <c r="F82">
+        <v>5.576000000000001</v>
+      </c>
+      <c r="G82">
+        <v>0.35</v>
+      </c>
+      <c r="H82">
+        <v>4.39</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.05</v>
+      </c>
+      <c r="K82">
+        <v>0.989</v>
+      </c>
+      <c r="L82">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M82">
+        <v>1.3315488</v>
+      </c>
+      <c r="N82">
+        <v>-1.2705488</v>
+      </c>
+      <c r="O82">
+        <v>-0.1905823200000001</v>
+      </c>
+      <c r="P82">
+        <v>-1.07996648</v>
+      </c>
+      <c r="Q82">
+        <v>-0.09096648000000018</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5420663875808867</v>
+      </c>
+      <c r="T82">
+        <v>2.668914926052769</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.006871697079371037</v>
+      </c>
+      <c r="W82">
+        <v>0.2371590387374462</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.0458113138624735</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3001405085061343</v>
+      </c>
+      <c r="C83">
+        <v>-2.12990034299582</v>
+      </c>
+      <c r="D83">
+        <v>3.16579965700418</v>
+      </c>
+      <c r="E83">
+        <v>3.065700000000001</v>
+      </c>
+      <c r="F83">
+        <v>5.645700000000001</v>
+      </c>
+      <c r="G83">
+        <v>0.35</v>
+      </c>
+      <c r="H83">
+        <v>4.39</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.05</v>
+      </c>
+      <c r="K83">
+        <v>0.989</v>
+      </c>
+      <c r="L83">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M83">
+        <v>1.34819316</v>
+      </c>
+      <c r="N83">
+        <v>-1.28719316</v>
+      </c>
+      <c r="O83">
+        <v>-0.193078974</v>
+      </c>
+      <c r="P83">
+        <v>-1.094114186</v>
+      </c>
+      <c r="Q83">
+        <v>-0.1051141860000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5685540921904071</v>
+      </c>
+      <c r="T83">
+        <v>2.809384132687125</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.006786861312959048</v>
+      </c>
+      <c r="W83">
+        <v>0.2371792975184654</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.04524574208639354</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3021405085061343</v>
+      </c>
+      <c r="C84">
+        <v>-2.223643735901552</v>
+      </c>
+      <c r="D84">
+        <v>3.141756264098448</v>
+      </c>
+      <c r="E84">
+        <v>3.1354</v>
+      </c>
+      <c r="F84">
+        <v>5.7154</v>
+      </c>
+      <c r="G84">
+        <v>0.35</v>
+      </c>
+      <c r="H84">
+        <v>4.39</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.05</v>
+      </c>
+      <c r="K84">
+        <v>0.989</v>
+      </c>
+      <c r="L84">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M84">
+        <v>1.36483752</v>
+      </c>
+      <c r="N84">
+        <v>-1.30383752</v>
+      </c>
+      <c r="O84">
+        <v>-0.195575628</v>
+      </c>
+      <c r="P84">
+        <v>-1.108261892</v>
+      </c>
+      <c r="Q84">
+        <v>-0.119261892</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5979848750898742</v>
+      </c>
+      <c r="T84">
+        <v>2.965461028947521</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.006704094711581499</v>
+      </c>
+      <c r="W84">
+        <v>0.2371990621828743</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.04469396474387655</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3041405085061343</v>
+      </c>
+      <c r="C85">
+        <v>-2.317024675399155</v>
+      </c>
+      <c r="D85">
+        <v>3.118075324600845</v>
+      </c>
+      <c r="E85">
+        <v>3.2051</v>
+      </c>
+      <c r="F85">
+        <v>5.7851</v>
+      </c>
+      <c r="G85">
+        <v>0.35</v>
+      </c>
+      <c r="H85">
+        <v>4.39</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.05</v>
+      </c>
+      <c r="K85">
+        <v>0.989</v>
+      </c>
+      <c r="L85">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M85">
+        <v>1.38148188</v>
+      </c>
+      <c r="N85">
+        <v>-1.32048188</v>
+      </c>
+      <c r="O85">
+        <v>-0.198072282</v>
+      </c>
+      <c r="P85">
+        <v>-1.122409598</v>
+      </c>
+      <c r="Q85">
+        <v>-0.133409598</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6308781030363373</v>
+      </c>
+      <c r="T85">
+        <v>3.139899913003258</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.00662332248614076</v>
+      </c>
+      <c r="W85">
+        <v>0.2372183505903096</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.04415548324093832</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3061405085061343</v>
+      </c>
+      <c r="C86">
+        <v>-2.410051296134817</v>
+      </c>
+      <c r="D86">
+        <v>3.094748703865183</v>
+      </c>
+      <c r="E86">
+        <v>3.2748</v>
+      </c>
+      <c r="F86">
+        <v>5.8548</v>
+      </c>
+      <c r="G86">
+        <v>0.35</v>
+      </c>
+      <c r="H86">
+        <v>4.39</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.05</v>
+      </c>
+      <c r="K86">
+        <v>0.989</v>
+      </c>
+      <c r="L86">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M86">
+        <v>1.39812624</v>
+      </c>
+      <c r="N86">
+        <v>-1.33712624</v>
+      </c>
+      <c r="O86">
+        <v>-0.200568936</v>
+      </c>
+      <c r="P86">
+        <v>-1.136557304</v>
+      </c>
+      <c r="Q86">
+        <v>-0.1475573039999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6678829844761081</v>
+      </c>
+      <c r="T86">
+        <v>3.33614365756596</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.006544473408924797</v>
+      </c>
+      <c r="W86">
+        <v>0.2372371797499488</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.04362982272616533</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3081405085061343</v>
+      </c>
+      <c r="C87">
+        <v>-2.502731491138011</v>
+      </c>
+      <c r="D87">
+        <v>3.071768508861988</v>
+      </c>
+      <c r="E87">
+        <v>3.344499999999999</v>
+      </c>
+      <c r="F87">
+        <v>5.924499999999999</v>
+      </c>
+      <c r="G87">
+        <v>0.35</v>
+      </c>
+      <c r="H87">
+        <v>4.39</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.05</v>
+      </c>
+      <c r="K87">
+        <v>0.989</v>
+      </c>
+      <c r="L87">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M87">
+        <v>1.4147706</v>
+      </c>
+      <c r="N87">
+        <v>-1.3537706</v>
+      </c>
+      <c r="O87">
+        <v>-0.20306559</v>
+      </c>
+      <c r="P87">
+        <v>-1.15070501</v>
+      </c>
+      <c r="Q87">
+        <v>-0.1617050099999998</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.7098218501078488</v>
+      </c>
+      <c r="T87">
+        <v>3.558553234737025</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.006467479604113918</v>
+      </c>
+      <c r="W87">
+        <v>0.2372555658705376</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.04311653069409283</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3101405085061343</v>
+      </c>
+      <c r="C88">
+        <v>-2.595072920726049</v>
+      </c>
+      <c r="D88">
+        <v>3.04912707927395</v>
+      </c>
+      <c r="E88">
+        <v>3.414199999999999</v>
+      </c>
+      <c r="F88">
+        <v>5.994199999999999</v>
+      </c>
+      <c r="G88">
+        <v>0.35</v>
+      </c>
+      <c r="H88">
+        <v>4.39</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.05</v>
+      </c>
+      <c r="K88">
+        <v>0.989</v>
+      </c>
+      <c r="L88">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M88">
+        <v>1.43141496</v>
+      </c>
+      <c r="N88">
+        <v>-1.37041496</v>
+      </c>
+      <c r="O88">
+        <v>-0.205562244</v>
+      </c>
+      <c r="P88">
+        <v>-1.164852716</v>
+      </c>
+      <c r="Q88">
+        <v>-0.1758527159999997</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7577519822584093</v>
+      </c>
+      <c r="T88">
+        <v>3.812735608646812</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.00639227635290329</v>
+      </c>
+      <c r="W88">
+        <v>0.2372735244069267</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.04261517568602202</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3121405085061343</v>
+      </c>
+      <c r="C89">
+        <v>-2.687083021017719</v>
+      </c>
+      <c r="D89">
+        <v>3.026816978982281</v>
+      </c>
+      <c r="E89">
+        <v>3.483899999999999</v>
+      </c>
+      <c r="F89">
+        <v>6.063899999999999</v>
+      </c>
+      <c r="G89">
+        <v>0.35</v>
+      </c>
+      <c r="H89">
+        <v>4.39</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.05</v>
+      </c>
+      <c r="K89">
+        <v>0.989</v>
+      </c>
+      <c r="L89">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M89">
+        <v>1.44805932</v>
+      </c>
+      <c r="N89">
+        <v>-1.38705932</v>
+      </c>
+      <c r="O89">
+        <v>-0.208058898</v>
+      </c>
+      <c r="P89">
+        <v>-1.179000422</v>
+      </c>
+      <c r="Q89">
+        <v>-0.1900004220000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8130559808936715</v>
+      </c>
+      <c r="T89">
+        <v>4.106022963158105</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.006318801912065321</v>
+      </c>
+      <c r="W89">
+        <v>0.2372910701033988</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.04212534608043539</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3141405085061343</v>
+      </c>
+      <c r="C90">
+        <v>-2.778769012075877</v>
+      </c>
+      <c r="D90">
+        <v>3.004830987924123</v>
+      </c>
+      <c r="E90">
+        <v>3.553599999999999</v>
+      </c>
+      <c r="F90">
+        <v>6.133599999999999</v>
+      </c>
+      <c r="G90">
+        <v>0.35</v>
+      </c>
+      <c r="H90">
+        <v>4.39</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.05</v>
+      </c>
+      <c r="K90">
+        <v>0.989</v>
+      </c>
+      <c r="L90">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M90">
+        <v>1.46470368</v>
+      </c>
+      <c r="N90">
+        <v>-1.40370368</v>
+      </c>
+      <c r="O90">
+        <v>-0.210555552</v>
+      </c>
+      <c r="P90">
+        <v>-1.193148128</v>
+      </c>
+      <c r="Q90">
+        <v>-0.204148128</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.877577312634811</v>
+      </c>
+      <c r="T90">
+        <v>4.448191543421281</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.006246997344882761</v>
+      </c>
+      <c r="W90">
+        <v>0.237308217034042</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.04164664896588499</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3161405085061343</v>
+      </c>
+      <c r="C91">
+        <v>-2.870137905697723</v>
+      </c>
+      <c r="D91">
+        <v>2.983162094302276</v>
+      </c>
+      <c r="E91">
+        <v>3.6233</v>
+      </c>
+      <c r="F91">
+        <v>6.2033</v>
+      </c>
+      <c r="G91">
+        <v>0.35</v>
+      </c>
+      <c r="H91">
+        <v>4.39</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.05</v>
+      </c>
+      <c r="K91">
+        <v>0.989</v>
+      </c>
+      <c r="L91">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M91">
+        <v>1.48134804</v>
+      </c>
+      <c r="N91">
+        <v>-1.42034804</v>
+      </c>
+      <c r="O91">
+        <v>-0.213052206</v>
+      </c>
+      <c r="P91">
+        <v>-1.207295834</v>
+      </c>
+      <c r="Q91">
+        <v>-0.218295834</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.953829795601612</v>
+      </c>
+      <c r="T91">
+        <v>4.852572592823216</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.006176806363479584</v>
+      </c>
+      <c r="W91">
+        <v>0.2373249786404011</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.04117870908986399</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3181405085061342</v>
+      </c>
+      <c r="C92">
+        <v>-2.961196512870422</v>
+      </c>
+      <c r="D92">
+        <v>2.961803487129578</v>
+      </c>
+      <c r="E92">
+        <v>3.693</v>
+      </c>
+      <c r="F92">
+        <v>6.273</v>
+      </c>
+      <c r="G92">
+        <v>0.35</v>
+      </c>
+      <c r="H92">
+        <v>4.39</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.05</v>
+      </c>
+      <c r="K92">
+        <v>0.989</v>
+      </c>
+      <c r="L92">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M92">
+        <v>1.4979924</v>
+      </c>
+      <c r="N92">
+        <v>-1.4369924</v>
+      </c>
+      <c r="O92">
+        <v>-0.21554886</v>
+      </c>
+      <c r="P92">
+        <v>-1.22144354</v>
+      </c>
+      <c r="Q92">
+        <v>-0.2324435399999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.045332775161773</v>
+      </c>
+      <c r="T92">
+        <v>5.337829852105537</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.006108175181663144</v>
+      </c>
+      <c r="W92">
+        <v>0.2373413677666188</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.04072116787775437</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3201405085061343</v>
+      </c>
+      <c r="C93">
+        <v>-3.051951450908718</v>
+      </c>
+      <c r="D93">
+        <v>2.940748549091282</v>
+      </c>
+      <c r="E93">
+        <v>3.7627</v>
+      </c>
+      <c r="F93">
+        <v>6.3427</v>
+      </c>
+      <c r="G93">
+        <v>0.35</v>
+      </c>
+      <c r="H93">
+        <v>4.39</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.05</v>
+      </c>
+      <c r="K93">
+        <v>0.989</v>
+      </c>
+      <c r="L93">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M93">
+        <v>1.51463676</v>
+      </c>
+      <c r="N93">
+        <v>-1.45363676</v>
+      </c>
+      <c r="O93">
+        <v>-0.218045514</v>
+      </c>
+      <c r="P93">
+        <v>-1.235591246</v>
+      </c>
+      <c r="Q93">
+        <v>-0.2465912459999998</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.157169750179748</v>
+      </c>
+      <c r="T93">
+        <v>5.930922057895042</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.006041052377469045</v>
+      </c>
+      <c r="W93">
+        <v>0.2373573966922604</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.04027368251646035</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3221405085061343</v>
+      </c>
+      <c r="C94">
+        <v>-3.142409150290256</v>
+      </c>
+      <c r="D94">
+        <v>2.919990849709743</v>
+      </c>
+      <c r="E94">
+        <v>3.8324</v>
+      </c>
+      <c r="F94">
+        <v>6.4124</v>
+      </c>
+      <c r="G94">
+        <v>0.35</v>
+      </c>
+      <c r="H94">
+        <v>4.39</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.05</v>
+      </c>
+      <c r="K94">
+        <v>0.989</v>
+      </c>
+      <c r="L94">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M94">
+        <v>1.53128112</v>
+      </c>
+      <c r="N94">
+        <v>-1.47028112</v>
+      </c>
+      <c r="O94">
+        <v>-0.220542168</v>
+      </c>
+      <c r="P94">
+        <v>-1.249738952</v>
+      </c>
+      <c r="Q94">
+        <v>-0.260738952</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.296965968952217</v>
+      </c>
+      <c r="T94">
+        <v>6.672287315131925</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.005975388764670467</v>
+      </c>
+      <c r="W94">
+        <v>0.2373730771629967</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.03983592509780298</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3241405085061343</v>
+      </c>
+      <c r="C95">
+        <v>-3.232575861203453</v>
+      </c>
+      <c r="D95">
+        <v>2.899524138796547</v>
+      </c>
+      <c r="E95">
+        <v>3.9021</v>
+      </c>
+      <c r="F95">
+        <v>6.4821</v>
+      </c>
+      <c r="G95">
+        <v>0.35</v>
+      </c>
+      <c r="H95">
+        <v>4.39</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.05</v>
+      </c>
+      <c r="K95">
+        <v>0.989</v>
+      </c>
+      <c r="L95">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M95">
+        <v>1.54792548</v>
+      </c>
+      <c r="N95">
+        <v>-1.48692548</v>
+      </c>
+      <c r="O95">
+        <v>-0.223038822</v>
+      </c>
+      <c r="P95">
+        <v>-1.263886658</v>
+      </c>
+      <c r="Q95">
+        <v>-0.2748866580000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.47670396451682</v>
+      </c>
+      <c r="T95">
+        <v>7.62547121729363</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.005911137272577236</v>
+      </c>
+      <c r="W95">
+        <v>0.2373884204193086</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.03940758181718151</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3261405085061342</v>
+      </c>
+      <c r="C96">
+        <v>-3.3224576598219</v>
+      </c>
+      <c r="D96">
+        <v>2.8793423401781</v>
+      </c>
+      <c r="E96">
+        <v>3.9718</v>
+      </c>
+      <c r="F96">
+        <v>6.5518</v>
+      </c>
+      <c r="G96">
+        <v>0.35</v>
+      </c>
+      <c r="H96">
+        <v>4.39</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.05</v>
+      </c>
+      <c r="K96">
+        <v>0.989</v>
+      </c>
+      <c r="L96">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M96">
+        <v>1.56456984</v>
+      </c>
+      <c r="N96">
+        <v>-1.50356984</v>
+      </c>
+      <c r="O96">
+        <v>-0.225535476</v>
+      </c>
+      <c r="P96">
+        <v>-1.278034364</v>
+      </c>
+      <c r="Q96">
+        <v>-0.2890343639999998</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.716354625269623</v>
+      </c>
+      <c r="T96">
+        <v>8.896383086842569</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.005848252833507265</v>
+      </c>
+      <c r="W96">
+        <v>0.2374034372233585</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.03898835222338182</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3281405085061343</v>
+      </c>
+      <c r="C97">
+        <v>-3.412060454318559</v>
+      </c>
+      <c r="D97">
+        <v>2.859439545681441</v>
+      </c>
+      <c r="E97">
+        <v>4.0415</v>
+      </c>
+      <c r="F97">
+        <v>6.6215</v>
+      </c>
+      <c r="G97">
+        <v>0.35</v>
+      </c>
+      <c r="H97">
+        <v>4.39</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.05</v>
+      </c>
+      <c r="K97">
+        <v>0.989</v>
+      </c>
+      <c r="L97">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M97">
+        <v>1.5812142</v>
+      </c>
+      <c r="N97">
+        <v>-1.5202142</v>
+      </c>
+      <c r="O97">
+        <v>-0.22803213</v>
+      </c>
+      <c r="P97">
+        <v>-1.29218207</v>
+      </c>
+      <c r="Q97">
+        <v>-0.30318207</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.051865550323549</v>
+      </c>
+      <c r="T97">
+        <v>10.67565970421109</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.005786692277365084</v>
+      </c>
+      <c r="W97">
+        <v>0.2374181378841652</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.03857794851576735</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3301405085061343</v>
+      </c>
+      <c r="C98">
+        <v>-3.501389990632223</v>
+      </c>
+      <c r="D98">
+        <v>2.839810009367776</v>
+      </c>
+      <c r="E98">
+        <v>4.111199999999999</v>
+      </c>
+      <c r="F98">
+        <v>6.691199999999999</v>
+      </c>
+      <c r="G98">
+        <v>0.35</v>
+      </c>
+      <c r="H98">
+        <v>4.39</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.05</v>
+      </c>
+      <c r="K98">
+        <v>0.989</v>
+      </c>
+      <c r="L98">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M98">
+        <v>1.59785856</v>
+      </c>
+      <c r="N98">
+        <v>-1.53685856</v>
+      </c>
+      <c r="O98">
+        <v>-0.230528784</v>
+      </c>
+      <c r="P98">
+        <v>-1.306329776</v>
+      </c>
+      <c r="Q98">
+        <v>-0.3173297759999997</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.555131937904431</v>
+      </c>
+      <c r="T98">
+        <v>13.34457463026383</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.005726414232809198</v>
+      </c>
+      <c r="W98">
+        <v>0.2374325322812052</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.03817609488539475</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3321405085061343</v>
+      </c>
+      <c r="C99">
+        <v>-3.590451857998103</v>
+      </c>
+      <c r="D99">
+        <v>2.820448142001896</v>
+      </c>
+      <c r="E99">
+        <v>4.180899999999999</v>
+      </c>
+      <c r="F99">
+        <v>6.760899999999999</v>
+      </c>
+      <c r="G99">
+        <v>0.35</v>
+      </c>
+      <c r="H99">
+        <v>4.39</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.05</v>
+      </c>
+      <c r="K99">
+        <v>0.989</v>
+      </c>
+      <c r="L99">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M99">
+        <v>1.61450292</v>
+      </c>
+      <c r="N99">
+        <v>-1.55350292</v>
+      </c>
+      <c r="O99">
+        <v>-0.2330254380000001</v>
+      </c>
+      <c r="P99">
+        <v>-1.320477482</v>
+      </c>
+      <c r="Q99">
+        <v>-0.331477482</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.393909250539241</v>
+      </c>
+      <c r="T99">
+        <v>17.79276617368511</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.005667379034532814</v>
+      </c>
+      <c r="W99">
+        <v>0.2374466298865536</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.03778252689688533</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3341405085061343</v>
+      </c>
+      <c r="C100">
+        <v>-3.679251494253679</v>
+      </c>
+      <c r="D100">
+        <v>2.801348505746321</v>
+      </c>
+      <c r="E100">
+        <v>4.250599999999999</v>
+      </c>
+      <c r="F100">
+        <v>6.8306</v>
+      </c>
+      <c r="G100">
+        <v>0.35</v>
+      </c>
+      <c r="H100">
+        <v>4.39</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.05</v>
+      </c>
+      <c r="K100">
+        <v>0.989</v>
+      </c>
+      <c r="L100">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M100">
+        <v>1.63114728</v>
+      </c>
+      <c r="N100">
+        <v>-1.57014728</v>
+      </c>
+      <c r="O100">
+        <v>-0.235522092</v>
+      </c>
+      <c r="P100">
+        <v>-1.334625188</v>
+      </c>
+      <c r="Q100">
+        <v>-0.345625188</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.071463875808861</v>
+      </c>
+      <c r="T100">
+        <v>26.68914926052766</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.005609548636221254</v>
+      </c>
+      <c r="W100">
+        <v>0.2374604397856704</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.03739699090814164</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3361405085061343</v>
+      </c>
+      <c r="C101">
+        <v>-3.767794190930431</v>
+      </c>
+      <c r="D101">
+        <v>2.782505809069568</v>
+      </c>
+      <c r="E101">
+        <v>4.3203</v>
+      </c>
+      <c r="F101">
+        <v>6.9003</v>
+      </c>
+      <c r="G101">
+        <v>0.35</v>
+      </c>
+      <c r="H101">
+        <v>4.39</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.05</v>
+      </c>
+      <c r="K101">
+        <v>0.989</v>
+      </c>
+      <c r="L101">
+        <v>0.06100000000000005</v>
+      </c>
+      <c r="M101">
+        <v>1.64779164</v>
+      </c>
+      <c r="N101">
+        <v>-1.58679164</v>
+      </c>
+      <c r="O101">
+        <v>-0.238018746</v>
+      </c>
+      <c r="P101">
+        <v>-1.348772894</v>
+      </c>
+      <c r="Q101">
+        <v>-0.3597728939999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>10.10412775161772</v>
+      </c>
+      <c r="T101">
+        <v>53.37829852105532</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.005552886528784677</v>
+      </c>
+      <c r="W101">
+        <v>0.2374739706969262</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.03701924352523123</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/tunisia/tunisia_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_telecom_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1329091592290287</v>
+        <v>0.1327480454901851</v>
       </c>
       <c r="C2">
-        <v>15.76751931586301</v>
+        <v>15.64985910185209</v>
       </c>
       <c r="D2">
-        <v>15.31851931586301</v>
+        <v>15.33915910185208</v>
       </c>
       <c r="E2">
-        <v>-3.629999999999999</v>
+        <v>-3.491699999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1383</v>
       </c>
       <c r="G2">
         <v>0.449</v>
@@ -1451,28 +1451,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006956489999999998</v>
       </c>
       <c r="N2">
-        <v>2.293499999999999</v>
+        <v>2.28654351</v>
       </c>
       <c r="O2">
-        <v>0.3440249999999999</v>
+        <v>0.3429815264999999</v>
       </c>
       <c r="P2">
-        <v>1.949475</v>
+        <v>1.9435619835</v>
       </c>
       <c r="Q2">
-        <v>2.868475</v>
+        <v>2.8625619835</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1329091592290287</v>
+        <v>0.1336570661517021</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.537322879721409</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>329.6921292203396</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1327480454901851</v>
+        <v>0.1325869317513416</v>
       </c>
       <c r="C3">
-        <v>15.64985910185209</v>
+        <v>15.53225458193456</v>
       </c>
       <c r="D3">
-        <v>15.33915910185208</v>
+        <v>15.35985458193456</v>
       </c>
       <c r="E3">
-        <v>-3.491699999999999</v>
+        <v>-3.3534</v>
       </c>
       <c r="F3">
-        <v>0.1383</v>
+        <v>0.2766</v>
       </c>
       <c r="G3">
         <v>0.449</v>
@@ -1533,28 +1533,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M3">
-        <v>0.006956489999999998</v>
+        <v>0.01391298</v>
       </c>
       <c r="N3">
-        <v>2.28654351</v>
+        <v>2.279587019999999</v>
       </c>
       <c r="O3">
-        <v>0.3429815264999999</v>
+        <v>0.3419380529999999</v>
       </c>
       <c r="P3">
-        <v>1.9435619835</v>
+        <v>1.937648966999999</v>
       </c>
       <c r="Q3">
-        <v>2.8625619835</v>
+        <v>2.856648966999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1336570661517021</v>
+        <v>0.1344202364809608</v>
       </c>
       <c r="T3">
-        <v>0.537322879721409</v>
+        <v>0.5419903344521092</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>329.6921292203396</v>
+        <v>164.8460646101698</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1325869317513416</v>
+        <v>0.1324258180124981</v>
       </c>
       <c r="C4">
-        <v>15.53225458193456</v>
+        <v>15.41470598184116</v>
       </c>
       <c r="D4">
-        <v>15.35985458193456</v>
+        <v>15.38060598184116</v>
       </c>
       <c r="E4">
-        <v>-3.3534</v>
+        <v>-3.2151</v>
       </c>
       <c r="F4">
-        <v>0.2766</v>
+        <v>0.4148999999999999</v>
       </c>
       <c r="G4">
         <v>0.449</v>
@@ -1615,28 +1615,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M4">
-        <v>0.01391298</v>
+        <v>0.02086946999999999</v>
       </c>
       <c r="N4">
-        <v>2.279587019999999</v>
+        <v>2.272630529999999</v>
       </c>
       <c r="O4">
-        <v>0.3419380529999999</v>
+        <v>0.3408945794999999</v>
       </c>
       <c r="P4">
-        <v>1.937648966999999</v>
+        <v>1.931735950499999</v>
       </c>
       <c r="Q4">
-        <v>2.856648966999999</v>
+        <v>2.850735950499999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1344202364809608</v>
+        <v>0.1351991422809258</v>
       </c>
       <c r="T4">
-        <v>0.5419903344521092</v>
+        <v>0.5467540253628237</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>164.8460646101698</v>
+        <v>109.8973764067799</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1324258180124981</v>
+        <v>0.1322647042736545</v>
       </c>
       <c r="C5">
-        <v>15.41470598184116</v>
+        <v>15.29721352852414</v>
       </c>
       <c r="D5">
-        <v>15.38060598184116</v>
+        <v>15.40141352852414</v>
       </c>
       <c r="E5">
-        <v>-3.2151</v>
+        <v>-3.0768</v>
       </c>
       <c r="F5">
-        <v>0.4148999999999999</v>
+        <v>0.5531999999999999</v>
       </c>
       <c r="G5">
         <v>0.449</v>
@@ -1697,28 +1697,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M5">
-        <v>0.02086946999999999</v>
+        <v>0.02782595999999999</v>
       </c>
       <c r="N5">
-        <v>2.272630529999999</v>
+        <v>2.26567404</v>
       </c>
       <c r="O5">
-        <v>0.3408945794999999</v>
+        <v>0.3398511059999999</v>
       </c>
       <c r="P5">
-        <v>1.931735950499999</v>
+        <v>1.925822934</v>
       </c>
       <c r="Q5">
-        <v>2.850735950499999</v>
+        <v>2.844822934</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1351991422809258</v>
+        <v>0.1359942752850568</v>
       </c>
       <c r="T5">
-        <v>0.5467540253628237</v>
+        <v>0.5516169598341781</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>109.8973764067799</v>
+        <v>82.42303230508489</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1322647042736545</v>
+        <v>0.1321035905348109</v>
       </c>
       <c r="C6">
-        <v>15.29721352852414</v>
+        <v>15.17977745016553</v>
       </c>
       <c r="D6">
-        <v>15.40141352852414</v>
+        <v>15.42227745016553</v>
       </c>
       <c r="E6">
-        <v>-3.0768</v>
+        <v>-2.938499999999999</v>
       </c>
       <c r="F6">
-        <v>0.5531999999999999</v>
+        <v>0.6915</v>
       </c>
       <c r="G6">
         <v>0.449</v>
@@ -1779,28 +1779,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M6">
-        <v>0.02782595999999999</v>
+        <v>0.03478245</v>
       </c>
       <c r="N6">
-        <v>2.26567404</v>
+        <v>2.25871755</v>
       </c>
       <c r="O6">
-        <v>0.3398511059999999</v>
+        <v>0.3388076325</v>
       </c>
       <c r="P6">
-        <v>1.925822934</v>
+        <v>1.9199099175</v>
       </c>
       <c r="Q6">
-        <v>2.844822934</v>
+        <v>2.8389099175</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1359942752850568</v>
+        <v>0.13680614793138</v>
       </c>
       <c r="T6">
-        <v>0.5516169598341781</v>
+        <v>0.5565822718733505</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>82.42303230508489</v>
+        <v>65.93842584406791</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1321035905348109</v>
+        <v>0.1319424767959674</v>
       </c>
       <c r="C7">
-        <v>15.17977745016553</v>
+        <v>15.06239797618549</v>
       </c>
       <c r="D7">
-        <v>15.42227745016553</v>
+        <v>15.44319797618549</v>
       </c>
       <c r="E7">
-        <v>-2.938499999999999</v>
+        <v>-2.800199999999999</v>
       </c>
       <c r="F7">
-        <v>0.6915</v>
+        <v>0.8298</v>
       </c>
       <c r="G7">
         <v>0.449</v>
@@ -1861,28 +1861,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M7">
-        <v>0.03478245</v>
+        <v>0.04173894</v>
       </c>
       <c r="N7">
-        <v>2.25871755</v>
+        <v>2.251761059999999</v>
       </c>
       <c r="O7">
-        <v>0.3388076325</v>
+        <v>0.3377641589999999</v>
       </c>
       <c r="P7">
-        <v>1.9199099175</v>
+        <v>1.913996901</v>
       </c>
       <c r="Q7">
-        <v>2.8389099175</v>
+        <v>2.832996901</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.13680614793138</v>
+        <v>0.1376352944637951</v>
       </c>
       <c r="T7">
-        <v>0.5565822718733505</v>
+        <v>0.5616532288495266</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>65.93842584406791</v>
+        <v>54.94868820338992</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1319424767959674</v>
+        <v>0.1317813630571239</v>
       </c>
       <c r="C8">
-        <v>15.06239797618549</v>
+        <v>14.9450753372507</v>
       </c>
       <c r="D8">
-        <v>15.44319797618549</v>
+        <v>15.4641753372507</v>
       </c>
       <c r="E8">
-        <v>-2.800199999999999</v>
+        <v>-2.6619</v>
       </c>
       <c r="F8">
-        <v>0.8297999999999999</v>
+        <v>0.9680999999999997</v>
       </c>
       <c r="G8">
         <v>0.449</v>
@@ -1943,28 +1943,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M8">
-        <v>0.04173893999999999</v>
+        <v>0.04869542999999998</v>
       </c>
       <c r="N8">
-        <v>2.251761059999999</v>
+        <v>2.244804569999999</v>
       </c>
       <c r="O8">
-        <v>0.3377641589999999</v>
+        <v>0.3367206854999999</v>
       </c>
       <c r="P8">
-        <v>1.913996901</v>
+        <v>1.908083884499999</v>
       </c>
       <c r="Q8">
-        <v>2.832996901</v>
+        <v>2.827083884499999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1376352944637951</v>
+        <v>0.1384822721044343</v>
       </c>
       <c r="T8">
-        <v>0.5616532288495266</v>
+        <v>0.5668332386639</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.94868820338993</v>
+        <v>47.09887560290566</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1317813630571239</v>
+        <v>0.1316202493182803</v>
       </c>
       <c r="C9">
-        <v>14.9450753372507</v>
+        <v>14.82780976528289</v>
       </c>
       <c r="D9">
-        <v>15.4641753372507</v>
+        <v>15.48520976528289</v>
       </c>
       <c r="E9">
-        <v>-2.661899999999999</v>
+        <v>-2.5236</v>
       </c>
       <c r="F9">
-        <v>0.9681</v>
+        <v>1.1064</v>
       </c>
       <c r="G9">
         <v>0.449</v>
@@ -2025,28 +2025,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M9">
-        <v>0.04869543</v>
+        <v>0.05565191999999999</v>
       </c>
       <c r="N9">
-        <v>2.244804569999999</v>
+        <v>2.23784808</v>
       </c>
       <c r="O9">
-        <v>0.3367206854999999</v>
+        <v>0.3356772119999999</v>
       </c>
       <c r="P9">
-        <v>1.908083884499999</v>
+        <v>1.902170868</v>
       </c>
       <c r="Q9">
-        <v>2.827083884499999</v>
+        <v>2.821170867999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1384822721044343</v>
+        <v>0.1393476623024786</v>
       </c>
       <c r="T9">
-        <v>0.5668332386639</v>
+        <v>0.5721258573872816</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>47.09887560290564</v>
+        <v>41.21151615254245</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1316202493182803</v>
+        <v>0.1314591355794368</v>
       </c>
       <c r="C10">
-        <v>14.82780976528289</v>
+        <v>14.71060149346734</v>
       </c>
       <c r="D10">
-        <v>15.48520976528289</v>
+        <v>15.50630149346734</v>
       </c>
       <c r="E10">
-        <v>-2.5236</v>
+        <v>-2.3853</v>
       </c>
       <c r="F10">
-        <v>1.1064</v>
+        <v>1.2447</v>
       </c>
       <c r="G10">
         <v>0.449</v>
@@ -2107,28 +2107,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M10">
-        <v>0.05565191999999999</v>
+        <v>0.06260840999999998</v>
       </c>
       <c r="N10">
-        <v>2.23784808</v>
+        <v>2.230891589999999</v>
       </c>
       <c r="O10">
-        <v>0.3356772119999999</v>
+        <v>0.3346337384999999</v>
       </c>
       <c r="P10">
-        <v>1.902170868</v>
+        <v>1.896257851499999</v>
       </c>
       <c r="Q10">
-        <v>2.821170867999999</v>
+        <v>2.815257851499999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1393476623024786</v>
+        <v>0.1402320720653152</v>
       </c>
       <c r="T10">
-        <v>0.5721258573872816</v>
+        <v>0.5775347974012869</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.21151615254245</v>
+        <v>36.63245880225995</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1314591355794368</v>
+        <v>0.1312980218405932</v>
       </c>
       <c r="C11">
-        <v>14.71060149346734</v>
+        <v>14.59345075626148</v>
       </c>
       <c r="D11">
-        <v>15.50630149346734</v>
+        <v>15.52745075626148</v>
       </c>
       <c r="E11">
-        <v>-2.3853</v>
+        <v>-2.247</v>
       </c>
       <c r="F11">
-        <v>1.2447</v>
+        <v>1.383</v>
       </c>
       <c r="G11">
         <v>0.449</v>
@@ -2189,28 +2189,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M11">
-        <v>0.06260840999999998</v>
+        <v>0.06956489999999999</v>
       </c>
       <c r="N11">
-        <v>2.230891589999999</v>
+        <v>2.223935099999999</v>
       </c>
       <c r="O11">
-        <v>0.3346337384999999</v>
+        <v>0.3335902649999999</v>
       </c>
       <c r="P11">
-        <v>1.896257851499999</v>
+        <v>1.890344835</v>
       </c>
       <c r="Q11">
-        <v>2.815257851499999</v>
+        <v>2.809344835</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1402320720653152</v>
+        <v>0.1411361353784369</v>
       </c>
       <c r="T11">
-        <v>0.5775347974012869</v>
+        <v>0.5830639360822701</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.63245880225995</v>
+        <v>32.96921292203395</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1312980218405932</v>
+        <v>0.1311369081017497</v>
       </c>
       <c r="C12">
-        <v>14.59345075626148</v>
+        <v>14.47635778940364</v>
       </c>
       <c r="D12">
-        <v>15.52745075626148</v>
+        <v>15.54865778940364</v>
       </c>
       <c r="E12">
-        <v>-2.246999999999999</v>
+        <v>-2.1087</v>
       </c>
       <c r="F12">
-        <v>1.383</v>
+        <v>1.5213</v>
       </c>
       <c r="G12">
         <v>0.449</v>
@@ -2271,28 +2271,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M12">
-        <v>0.0695649</v>
+        <v>0.07652138999999999</v>
       </c>
       <c r="N12">
-        <v>2.223935099999999</v>
+        <v>2.21697861</v>
       </c>
       <c r="O12">
-        <v>0.3335902649999999</v>
+        <v>0.3325467914999999</v>
       </c>
       <c r="P12">
-        <v>1.890344835</v>
+        <v>1.8844318185</v>
       </c>
       <c r="Q12">
-        <v>2.809344835</v>
+        <v>2.8034318185</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1411361353784369</v>
+        <v>0.1420605147210671</v>
       </c>
       <c r="T12">
-        <v>0.5830639360822701</v>
+        <v>0.5887173250706912</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.96921292203395</v>
+        <v>29.97201174730359</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1311369081017497</v>
+        <v>0.1309757943629062</v>
       </c>
       <c r="C13">
-        <v>14.47635778940364</v>
+        <v>14.35932282992175</v>
       </c>
       <c r="D13">
-        <v>15.54865778940364</v>
+        <v>15.56992282992175</v>
       </c>
       <c r="E13">
-        <v>-2.1087</v>
+        <v>-1.9704</v>
       </c>
       <c r="F13">
-        <v>1.5213</v>
+        <v>1.6596</v>
       </c>
       <c r="G13">
         <v>0.449</v>
@@ -2353,28 +2353,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M13">
-        <v>0.07652138999999999</v>
+        <v>0.08347787999999998</v>
       </c>
       <c r="N13">
-        <v>2.21697861</v>
+        <v>2.21002212</v>
       </c>
       <c r="O13">
-        <v>0.3325467914999999</v>
+        <v>0.3315033179999999</v>
       </c>
       <c r="P13">
-        <v>1.8844318185</v>
+        <v>1.878518802</v>
       </c>
       <c r="Q13">
-        <v>2.8034318185</v>
+        <v>2.797518802</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1420605147210671</v>
+        <v>0.1430059026851206</v>
       </c>
       <c r="T13">
-        <v>0.5887173250706912</v>
+        <v>0.5944992001724854</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.97201174730359</v>
+        <v>27.47434410169497</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1309757943629062</v>
+        <v>0.1308146806240626</v>
       </c>
       <c r="C14">
-        <v>14.35932282992175</v>
+        <v>14.24234611614223</v>
       </c>
       <c r="D14">
-        <v>15.56992282992175</v>
+        <v>15.59124611614223</v>
       </c>
       <c r="E14">
-        <v>-1.9704</v>
+        <v>-1.8321</v>
       </c>
       <c r="F14">
-        <v>1.6596</v>
+        <v>1.7979</v>
       </c>
       <c r="G14">
         <v>0.449</v>
@@ -2435,28 +2435,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M14">
-        <v>0.08347787999999998</v>
+        <v>0.09043436999999999</v>
       </c>
       <c r="N14">
-        <v>2.21002212</v>
+        <v>2.203065629999999</v>
       </c>
       <c r="O14">
-        <v>0.3315033179999999</v>
+        <v>0.3304598444999999</v>
       </c>
       <c r="P14">
-        <v>1.878518802</v>
+        <v>1.872605785499999</v>
       </c>
       <c r="Q14">
-        <v>2.797518802</v>
+        <v>2.791605785499999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1430059026851206</v>
+        <v>0.1439730237058191</v>
       </c>
       <c r="T14">
-        <v>0.5944992001724854</v>
+        <v>0.6004139919432864</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.47434410169497</v>
+        <v>25.36093301694919</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1308146806240626</v>
+        <v>0.1306535668852191</v>
       </c>
       <c r="C15">
-        <v>14.24234611614223</v>
+        <v>14.12542788769883</v>
       </c>
       <c r="D15">
-        <v>15.59124611614223</v>
+        <v>15.61262788769883</v>
       </c>
       <c r="E15">
-        <v>-1.8321</v>
+        <v>-1.6938</v>
       </c>
       <c r="F15">
-        <v>1.7979</v>
+        <v>1.9362</v>
       </c>
       <c r="G15">
         <v>0.449</v>
@@ -2517,28 +2517,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M15">
-        <v>0.09043436999999999</v>
+        <v>0.09739086</v>
       </c>
       <c r="N15">
-        <v>2.203065629999999</v>
+        <v>2.196109139999999</v>
       </c>
       <c r="O15">
-        <v>0.3304598444999999</v>
+        <v>0.3294163709999999</v>
       </c>
       <c r="P15">
-        <v>1.872605785499999</v>
+        <v>1.866692768999999</v>
       </c>
       <c r="Q15">
-        <v>2.791605785499999</v>
+        <v>2.785692769</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1439730237058191</v>
+        <v>0.1449626359130454</v>
       </c>
       <c r="T15">
-        <v>0.6004139919432864</v>
+        <v>0.6064663370110827</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.36093301694919</v>
+        <v>23.54943780145282</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1306535668852191</v>
+        <v>0.1304924531463755</v>
       </c>
       <c r="C16">
-        <v>14.12542788769883</v>
+        <v>14.00856838554164</v>
       </c>
       <c r="D16">
-        <v>15.61262788769883</v>
+        <v>15.63406838554164</v>
       </c>
       <c r="E16">
-        <v>-1.6938</v>
+        <v>-1.555499999999999</v>
       </c>
       <c r="F16">
-        <v>1.9362</v>
+        <v>2.0745</v>
       </c>
       <c r="G16">
         <v>0.449</v>
@@ -2599,28 +2599,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M16">
-        <v>0.09739086</v>
+        <v>0.10434735</v>
       </c>
       <c r="N16">
-        <v>2.196109139999999</v>
+        <v>2.18915265</v>
       </c>
       <c r="O16">
-        <v>0.3294163709999999</v>
+        <v>0.3283728974999999</v>
       </c>
       <c r="P16">
-        <v>1.866692768999999</v>
+        <v>1.8607797525</v>
       </c>
       <c r="Q16">
-        <v>2.785692769</v>
+        <v>2.7797797525</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1449626359130454</v>
+        <v>0.145975533113383</v>
       </c>
       <c r="T16">
-        <v>0.6064663370110827</v>
+        <v>0.6126610901981213</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.54943780145282</v>
+        <v>21.97947528135597</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1304924531463755</v>
+        <v>0.130331339407532</v>
       </c>
       <c r="C17">
-        <v>14.00856838554164</v>
+        <v>13.89176785194614</v>
       </c>
       <c r="D17">
-        <v>15.63406838554164</v>
+        <v>15.65556785194614</v>
       </c>
       <c r="E17">
-        <v>-1.5555</v>
+        <v>-1.4172</v>
       </c>
       <c r="F17">
-        <v>2.0745</v>
+        <v>2.2128</v>
       </c>
       <c r="G17">
         <v>0.449</v>
@@ -2681,28 +2681,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M17">
-        <v>0.10434735</v>
+        <v>0.11130384</v>
       </c>
       <c r="N17">
-        <v>2.18915265</v>
+        <v>2.182196159999999</v>
       </c>
       <c r="O17">
-        <v>0.3283728974999999</v>
+        <v>0.3273294239999999</v>
       </c>
       <c r="P17">
-        <v>1.8607797525</v>
+        <v>1.854866736</v>
       </c>
       <c r="Q17">
-        <v>2.7797797525</v>
+        <v>2.773866736</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.145975533113383</v>
+        <v>0.1470125469137286</v>
       </c>
       <c r="T17">
-        <v>0.6126610901981213</v>
+        <v>0.619003337508661</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.97947528135597</v>
+        <v>20.60575807627122</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.130331339407532</v>
+        <v>0.1301702256686884</v>
       </c>
       <c r="C18">
-        <v>13.89176785194614</v>
+        <v>13.77502653052234</v>
       </c>
       <c r="D18">
-        <v>15.65556785194614</v>
+        <v>15.67712653052234</v>
       </c>
       <c r="E18">
-        <v>-1.4172</v>
+        <v>-1.2789</v>
       </c>
       <c r="F18">
-        <v>2.2128</v>
+        <v>2.3511</v>
       </c>
       <c r="G18">
         <v>0.449</v>
@@ -2763,28 +2763,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M18">
-        <v>0.11130384</v>
+        <v>0.11826033</v>
       </c>
       <c r="N18">
-        <v>2.182196159999999</v>
+        <v>2.175239669999999</v>
       </c>
       <c r="O18">
-        <v>0.3273294239999999</v>
+        <v>0.3262859504999999</v>
       </c>
       <c r="P18">
-        <v>1.854866736</v>
+        <v>1.848953719499999</v>
       </c>
       <c r="Q18">
-        <v>2.773866736</v>
+        <v>2.767953719499999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1470125469137286</v>
+        <v>0.1480745489984198</v>
       </c>
       <c r="T18">
-        <v>0.619003337508661</v>
+        <v>0.625498410055599</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.60575807627122</v>
+        <v>19.39365466001997</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1301702256686884</v>
+        <v>0.1300091119298449</v>
       </c>
       <c r="C19">
-        <v>13.77502653052234</v>
+        <v>13.65834466622393</v>
       </c>
       <c r="D19">
-        <v>15.67712653052234</v>
+        <v>15.69874466622393</v>
       </c>
       <c r="E19">
-        <v>-1.2789</v>
+        <v>-1.1406</v>
       </c>
       <c r="F19">
-        <v>2.3511</v>
+        <v>2.4894</v>
       </c>
       <c r="G19">
         <v>0.449</v>
@@ -2845,28 +2845,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M19">
-        <v>0.11826033</v>
+        <v>0.12521682</v>
       </c>
       <c r="N19">
-        <v>2.175239669999999</v>
+        <v>2.16828318</v>
       </c>
       <c r="O19">
-        <v>0.3262859504999999</v>
+        <v>0.3252424769999999</v>
       </c>
       <c r="P19">
-        <v>1.848953719499999</v>
+        <v>1.843040703</v>
       </c>
       <c r="Q19">
-        <v>2.767953719499999</v>
+        <v>2.762040702999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1480745489984198</v>
+        <v>0.1491624535729816</v>
       </c>
       <c r="T19">
-        <v>0.625498410055599</v>
+        <v>0.632151899006121</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.39365466001997</v>
+        <v>18.31622940112997</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1300091119298449</v>
+        <v>0.1298479981910014</v>
       </c>
       <c r="C20">
-        <v>13.65834466622393</v>
+        <v>13.54172250535762</v>
       </c>
       <c r="D20">
-        <v>15.69874466622393</v>
+        <v>15.72042250535762</v>
       </c>
       <c r="E20">
-        <v>-1.1406</v>
+        <v>-1.0023</v>
       </c>
       <c r="F20">
-        <v>2.489399999999999</v>
+        <v>2.6277</v>
       </c>
       <c r="G20">
         <v>0.449</v>
@@ -2927,28 +2927,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M20">
-        <v>0.12521682</v>
+        <v>0.13217331</v>
       </c>
       <c r="N20">
-        <v>2.16828318</v>
+        <v>2.161326689999999</v>
       </c>
       <c r="O20">
-        <v>0.3252424769999999</v>
+        <v>0.3241990034999999</v>
       </c>
       <c r="P20">
-        <v>1.843040703</v>
+        <v>1.837127686499999</v>
       </c>
       <c r="Q20">
-        <v>2.762040702999999</v>
+        <v>2.756127686499999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1491624535729816</v>
+        <v>0.1502772199888906</v>
       </c>
       <c r="T20">
-        <v>0.632151899006121</v>
+        <v>0.6389696716344336</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.31622940112998</v>
+        <v>17.35221732738629</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1298479981910014</v>
+        <v>0.1296868844521578</v>
       </c>
       <c r="C21">
-        <v>13.54172250535762</v>
+        <v>13.42516029559246</v>
       </c>
       <c r="D21">
-        <v>15.72042250535762</v>
+        <v>15.74216029559246</v>
       </c>
       <c r="E21">
-        <v>-1.0023</v>
+        <v>-0.8639999999999994</v>
       </c>
       <c r="F21">
-        <v>2.6277</v>
+        <v>2.766</v>
       </c>
       <c r="G21">
         <v>0.449</v>
@@ -3009,28 +3009,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M21">
-        <v>0.13217331</v>
+        <v>0.1391298</v>
       </c>
       <c r="N21">
-        <v>2.161326689999999</v>
+        <v>2.154370199999999</v>
       </c>
       <c r="O21">
-        <v>0.3241990034999999</v>
+        <v>0.3231555299999999</v>
       </c>
       <c r="P21">
-        <v>1.837127686499999</v>
+        <v>1.831214669999999</v>
       </c>
       <c r="Q21">
-        <v>2.756127686499999</v>
+        <v>2.750214669999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1502772199888906</v>
+        <v>0.1514198555651973</v>
       </c>
       <c r="T21">
-        <v>0.6389696716344336</v>
+        <v>0.645957888578454</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.35221732738629</v>
+        <v>16.48460646101697</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1296868844521578</v>
+        <v>0.1295257707133143</v>
       </c>
       <c r="C22">
-        <v>13.42516029559246</v>
+        <v>13.30865828596926</v>
       </c>
       <c r="D22">
-        <v>15.74216029559246</v>
+        <v>15.76395828596926</v>
       </c>
       <c r="E22">
-        <v>-0.8639999999999994</v>
+        <v>-0.7256999999999993</v>
       </c>
       <c r="F22">
-        <v>2.766</v>
+        <v>2.9043</v>
       </c>
       <c r="G22">
         <v>0.449</v>
@@ -3091,28 +3091,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M22">
-        <v>0.1391298</v>
+        <v>0.14608629</v>
       </c>
       <c r="N22">
-        <v>2.154370199999999</v>
+        <v>2.147413709999999</v>
       </c>
       <c r="O22">
-        <v>0.3231555299999999</v>
+        <v>0.3221120564999999</v>
       </c>
       <c r="P22">
-        <v>1.831214669999999</v>
+        <v>1.8253016535</v>
       </c>
       <c r="Q22">
-        <v>2.750214669999999</v>
+        <v>2.7443016535</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1514198555651973</v>
+        <v>0.1525914186244484</v>
       </c>
       <c r="T22">
-        <v>0.645957888578454</v>
+        <v>0.6531230224071333</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.48460646101697</v>
+        <v>15.69962520096855</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1295257707133143</v>
+        <v>0.1293646569744707</v>
       </c>
       <c r="C23">
-        <v>13.30865828596926</v>
+        <v>13.19221672691016</v>
       </c>
       <c r="D23">
-        <v>15.76395828596926</v>
+        <v>15.78581672691016</v>
       </c>
       <c r="E23">
-        <v>-0.7256999999999998</v>
+        <v>-0.5873999999999997</v>
       </c>
       <c r="F23">
-        <v>2.9043</v>
+        <v>3.0426</v>
       </c>
       <c r="G23">
         <v>0.449</v>
@@ -3173,28 +3173,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M23">
-        <v>0.14608629</v>
+        <v>0.15304278</v>
       </c>
       <c r="N23">
-        <v>2.147413709999999</v>
+        <v>2.14045722</v>
       </c>
       <c r="O23">
-        <v>0.3221120564999999</v>
+        <v>0.3210685829999999</v>
       </c>
       <c r="P23">
-        <v>1.8253016535</v>
+        <v>1.819388637</v>
       </c>
       <c r="Q23">
-        <v>2.7443016535</v>
+        <v>2.738388637</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1525914186244484</v>
+        <v>0.153793021762142</v>
       </c>
       <c r="T23">
-        <v>0.6531230224071332</v>
+        <v>0.660471877616035</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.69962520096855</v>
+        <v>14.9860058736518</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1293646569744707</v>
+        <v>0.1292035432356272</v>
       </c>
       <c r="C24">
-        <v>13.19221672691016</v>
+        <v>13.07583587022812</v>
       </c>
       <c r="D24">
-        <v>15.78581672691016</v>
+        <v>15.80773587022812</v>
       </c>
       <c r="E24">
-        <v>-0.5873999999999997</v>
+        <v>-0.4490999999999996</v>
       </c>
       <c r="F24">
-        <v>3.0426</v>
+        <v>3.1809</v>
       </c>
       <c r="G24">
         <v>0.449</v>
@@ -3255,28 +3255,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M24">
-        <v>0.15304278</v>
+        <v>0.15999927</v>
       </c>
       <c r="N24">
-        <v>2.14045722</v>
+        <v>2.133500729999999</v>
       </c>
       <c r="O24">
-        <v>0.3210685829999999</v>
+        <v>0.3200251094999999</v>
       </c>
       <c r="P24">
-        <v>1.819388637</v>
+        <v>1.813475620499999</v>
       </c>
       <c r="Q24">
-        <v>2.738388637</v>
+        <v>2.732475620499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.153793021762142</v>
+        <v>0.1550258353709444</v>
       </c>
       <c r="T24">
-        <v>0.660471877616035</v>
+        <v>0.668011612181012</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.9860058736518</v>
+        <v>14.33444040088433</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1292035432356272</v>
+        <v>0.1290424294967837</v>
       </c>
       <c r="C25">
-        <v>13.07583587022812</v>
+        <v>12.95951596913669</v>
       </c>
       <c r="D25">
-        <v>15.80773587022812</v>
+        <v>15.82971596913669</v>
       </c>
       <c r="E25">
-        <v>-0.4490999999999996</v>
+        <v>-0.3107999999999995</v>
       </c>
       <c r="F25">
-        <v>3.1809</v>
+        <v>3.3192</v>
       </c>
       <c r="G25">
         <v>0.449</v>
@@ -3337,28 +3337,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M25">
-        <v>0.15999927</v>
+        <v>0.16695576</v>
       </c>
       <c r="N25">
-        <v>2.133500729999999</v>
+        <v>2.126544239999999</v>
       </c>
       <c r="O25">
-        <v>0.3200251094999999</v>
+        <v>0.3189816359999999</v>
       </c>
       <c r="P25">
-        <v>1.813475620499999</v>
+        <v>1.807562603999999</v>
       </c>
       <c r="Q25">
-        <v>2.732475620499999</v>
+        <v>2.726562604</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1550258353709444</v>
+        <v>0.1562910914431364</v>
       </c>
       <c r="T25">
-        <v>0.668011612181012</v>
+        <v>0.6757497608134886</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.33444040088433</v>
+        <v>13.73717205084748</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1290424294967837</v>
+        <v>0.1288813157579401</v>
       </c>
       <c r="C26">
-        <v>12.9595159691367</v>
+        <v>12.84325727825973</v>
       </c>
       <c r="D26">
-        <v>15.82971596913669</v>
+        <v>15.85175727825973</v>
       </c>
       <c r="E26">
-        <v>-0.3108</v>
+        <v>-0.1724999999999999</v>
       </c>
       <c r="F26">
-        <v>3.319199999999999</v>
+        <v>3.4575</v>
       </c>
       <c r="G26">
         <v>0.449</v>
@@ -3419,28 +3419,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M26">
-        <v>0.16695576</v>
+        <v>0.17391225</v>
       </c>
       <c r="N26">
-        <v>2.126544239999999</v>
+        <v>2.11958775</v>
       </c>
       <c r="O26">
-        <v>0.3189816359999999</v>
+        <v>0.3179381624999999</v>
       </c>
       <c r="P26">
-        <v>1.807562603999999</v>
+        <v>1.8016495875</v>
       </c>
       <c r="Q26">
-        <v>2.726562604</v>
+        <v>2.7206495875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1562910914431364</v>
+        <v>0.1575900876772535</v>
       </c>
       <c r="T26">
-        <v>0.6757497608134886</v>
+        <v>0.6836942600761644</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.73717205084748</v>
+        <v>13.18768516881358</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1288813157579401</v>
+        <v>0.1290517020190965</v>
       </c>
       <c r="C27">
-        <v>12.84325727825973</v>
+        <v>12.68164929864881</v>
       </c>
       <c r="D27">
-        <v>15.85175727825973</v>
+        <v>15.82844929864881</v>
       </c>
       <c r="E27">
-        <v>-0.1724999999999999</v>
+        <v>-0.03419999999999979</v>
       </c>
       <c r="F27">
-        <v>3.4575</v>
+        <v>3.5958</v>
       </c>
       <c r="G27">
         <v>0.449</v>
@@ -3501,45 +3501,45 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M27">
-        <v>0.17391225</v>
+        <v>0.18626244</v>
       </c>
       <c r="N27">
-        <v>2.11958775</v>
+        <v>2.107237559999999</v>
       </c>
       <c r="O27">
-        <v>0.3179381624999999</v>
+        <v>0.3160856339999999</v>
       </c>
       <c r="P27">
-        <v>1.8016495875</v>
+        <v>1.791151926</v>
       </c>
       <c r="Q27">
-        <v>2.7206495875</v>
+        <v>2.710151926</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1575900876772535</v>
+        <v>0.158924191917698</v>
       </c>
       <c r="T27">
-        <v>0.6836942600761644</v>
+        <v>0.6918534755351289</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.18768516881358</v>
+        <v>12.31327153236047</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1290517020190965</v>
+        <v>0.128903338280253</v>
       </c>
       <c r="C28">
-        <v>12.68164929864881</v>
+        <v>12.56364084646643</v>
       </c>
       <c r="D28">
-        <v>15.82844929864881</v>
+        <v>15.84874084646642</v>
       </c>
       <c r="E28">
-        <v>-0.03419999999999979</v>
+        <v>0.1041000000000003</v>
       </c>
       <c r="F28">
-        <v>3.5958</v>
+        <v>3.7341</v>
       </c>
       <c r="G28">
         <v>0.449</v>
@@ -3583,28 +3583,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M28">
-        <v>0.18626244</v>
+        <v>0.19342638</v>
       </c>
       <c r="N28">
-        <v>2.107237559999999</v>
+        <v>2.100073619999999</v>
       </c>
       <c r="O28">
-        <v>0.3160856339999999</v>
+        <v>0.3150110429999999</v>
       </c>
       <c r="P28">
-        <v>1.791151926</v>
+        <v>1.785062576999999</v>
       </c>
       <c r="Q28">
-        <v>2.710151926</v>
+        <v>2.704062576999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.158924191917698</v>
+        <v>0.1602948469592507</v>
       </c>
       <c r="T28">
-        <v>0.6918534755351289</v>
+        <v>0.700236231143654</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.31327153236047</v>
+        <v>11.85722443856934</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.128903338280253</v>
+        <v>0.1287549745414095</v>
       </c>
       <c r="C29">
-        <v>12.56364084646643</v>
+        <v>12.44568448725013</v>
       </c>
       <c r="D29">
-        <v>15.84874084646642</v>
+        <v>15.86908448725013</v>
       </c>
       <c r="E29">
-        <v>0.1041000000000003</v>
+        <v>0.2424000000000004</v>
       </c>
       <c r="F29">
-        <v>3.7341</v>
+        <v>3.8724</v>
       </c>
       <c r="G29">
         <v>0.449</v>
@@ -3665,28 +3665,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M29">
-        <v>0.19342638</v>
+        <v>0.20059032</v>
       </c>
       <c r="N29">
-        <v>2.100073619999999</v>
+        <v>2.09290968</v>
       </c>
       <c r="O29">
-        <v>0.3150110429999999</v>
+        <v>0.3139364519999999</v>
       </c>
       <c r="P29">
-        <v>1.785062576999999</v>
+        <v>1.778973228</v>
       </c>
       <c r="Q29">
-        <v>2.704062576999999</v>
+        <v>2.697973228</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1602948469592507</v>
+        <v>0.1617035757519576</v>
       </c>
       <c r="T29">
-        <v>0.700236231143654</v>
+        <v>0.7088518410746382</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.85722443856934</v>
+        <v>11.43375213719186</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1287549745414095</v>
+        <v>0.1286066108025659</v>
       </c>
       <c r="C30">
-        <v>12.44568448725013</v>
+        <v>12.32778042185929</v>
       </c>
       <c r="D30">
-        <v>15.86908448725013</v>
+        <v>15.88948042185929</v>
       </c>
       <c r="E30">
-        <v>0.2424000000000004</v>
+        <v>0.3807000000000005</v>
       </c>
       <c r="F30">
-        <v>3.8724</v>
+        <v>4.0107</v>
       </c>
       <c r="G30">
         <v>0.449</v>
@@ -3747,28 +3747,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M30">
-        <v>0.20059032</v>
+        <v>0.20775426</v>
       </c>
       <c r="N30">
-        <v>2.09290968</v>
+        <v>2.085745739999999</v>
       </c>
       <c r="O30">
-        <v>0.3139364519999999</v>
+        <v>0.3128618609999999</v>
       </c>
       <c r="P30">
-        <v>1.778973228</v>
+        <v>1.772883878999999</v>
       </c>
       <c r="Q30">
-        <v>2.697973228</v>
+        <v>2.691883879</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1617035757519576</v>
+        <v>0.1631519870458675</v>
       </c>
       <c r="T30">
-        <v>0.7088518410746382</v>
+        <v>0.7177101442431147</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.43375213719186</v>
+        <v>11.03948482211628</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1286066108025659</v>
+        <v>0.1284582470637224</v>
       </c>
       <c r="C31">
-        <v>12.32778042185929</v>
+        <v>12.20992885218722</v>
       </c>
       <c r="D31">
-        <v>15.88948042185929</v>
+        <v>15.90992885218722</v>
       </c>
       <c r="E31">
-        <v>0.3806999999999996</v>
+        <v>0.5189999999999997</v>
       </c>
       <c r="F31">
-        <v>4.010699999999999</v>
+        <v>4.148999999999999</v>
       </c>
       <c r="G31">
         <v>0.449</v>
@@ -3829,28 +3829,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M31">
-        <v>0.2077542599999999</v>
+        <v>0.2149181999999999</v>
       </c>
       <c r="N31">
-        <v>2.08574574</v>
+        <v>2.078581799999999</v>
       </c>
       <c r="O31">
-        <v>0.312861861</v>
+        <v>0.3117872699999999</v>
       </c>
       <c r="P31">
-        <v>1.772883879</v>
+        <v>1.766794529999999</v>
       </c>
       <c r="Q31">
-        <v>2.691883879</v>
+        <v>2.685794529999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1631519870458675</v>
+        <v>0.1646417815196034</v>
       </c>
       <c r="T31">
-        <v>0.7177101442431147</v>
+        <v>0.7268215417878334</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.03948482211628</v>
+        <v>10.67150199471241</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1284582470637224</v>
+        <v>0.1283098833248788</v>
       </c>
       <c r="C32">
-        <v>12.20992885218722</v>
+        <v>12.09212998116787</v>
       </c>
       <c r="D32">
-        <v>15.90992885218722</v>
+        <v>15.93042998116786</v>
       </c>
       <c r="E32">
-        <v>0.5189999999999997</v>
+        <v>0.6572999999999998</v>
       </c>
       <c r="F32">
-        <v>4.148999999999999</v>
+        <v>4.287299999999999</v>
       </c>
       <c r="G32">
         <v>0.449</v>
@@ -3911,28 +3911,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M32">
-        <v>0.2149181999999999</v>
+        <v>0.22208214</v>
       </c>
       <c r="N32">
-        <v>2.078581799999999</v>
+        <v>2.07141786</v>
       </c>
       <c r="O32">
-        <v>0.3117872699999999</v>
+        <v>0.3107126789999999</v>
       </c>
       <c r="P32">
-        <v>1.766794529999999</v>
+        <v>1.760705181</v>
       </c>
       <c r="Q32">
-        <v>2.685794529999999</v>
+        <v>2.679705181</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1646417815196034</v>
+        <v>0.1661747584418534</v>
       </c>
       <c r="T32">
-        <v>0.7268215417878334</v>
+        <v>0.7361970378121093</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.67150199471241</v>
+        <v>10.32725999488297</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1283098833248788</v>
+        <v>0.1281615195860353</v>
       </c>
       <c r="C33">
-        <v>12.09212998116787</v>
+        <v>11.97438401278248</v>
       </c>
       <c r="D33">
-        <v>15.93042998116786</v>
+        <v>15.95098401278248</v>
       </c>
       <c r="E33">
-        <v>0.6572999999999998</v>
+        <v>0.7955999999999999</v>
       </c>
       <c r="F33">
-        <v>4.287299999999999</v>
+        <v>4.425599999999999</v>
       </c>
       <c r="G33">
         <v>0.449</v>
@@ -3993,28 +3993,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M33">
-        <v>0.22208214</v>
+        <v>0.22924608</v>
       </c>
       <c r="N33">
-        <v>2.07141786</v>
+        <v>2.06425392</v>
       </c>
       <c r="O33">
-        <v>0.3107126789999999</v>
+        <v>0.3096380879999999</v>
       </c>
       <c r="P33">
-        <v>1.760705181</v>
+        <v>1.754615832</v>
       </c>
       <c r="Q33">
-        <v>2.679705181</v>
+        <v>2.673615832</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1661747584418534</v>
+        <v>0.1677528229206401</v>
       </c>
       <c r="T33">
-        <v>0.7361970378121093</v>
+        <v>0.7458482837194521</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.32725999488297</v>
+        <v>10.00453312004288</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1281615195860353</v>
+        <v>0.1284900058471918</v>
       </c>
       <c r="C34">
-        <v>11.97438401278248</v>
+        <v>11.79064722942056</v>
       </c>
       <c r="D34">
-        <v>15.95098401278248</v>
+        <v>15.90554722942056</v>
       </c>
       <c r="E34">
-        <v>0.7955999999999999</v>
+        <v>0.9339</v>
       </c>
       <c r="F34">
-        <v>4.425599999999999</v>
+        <v>4.563899999999999</v>
       </c>
       <c r="G34">
         <v>0.449</v>
@@ -4075,45 +4075,45 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M34">
-        <v>0.22924608</v>
+        <v>0.24416865</v>
       </c>
       <c r="N34">
-        <v>2.06425392</v>
+        <v>2.04933135</v>
       </c>
       <c r="O34">
-        <v>0.3096380879999999</v>
+        <v>0.3073997024999999</v>
       </c>
       <c r="P34">
-        <v>1.754615832</v>
+        <v>1.7419316475</v>
       </c>
       <c r="Q34">
-        <v>2.673615832</v>
+        <v>2.6609316475</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1677528229206401</v>
+        <v>0.1693779938017788</v>
       </c>
       <c r="T34">
-        <v>0.7458482837194521</v>
+        <v>0.7557876265195514</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>10.00453312004288</v>
+        <v>9.393097762550598</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1284900058471918</v>
+        <v>0.1283560921083482</v>
       </c>
       <c r="C35">
-        <v>11.79064722942056</v>
+        <v>11.67083911766322</v>
       </c>
       <c r="D35">
-        <v>15.90554722942056</v>
+        <v>15.92403911766322</v>
       </c>
       <c r="E35">
-        <v>0.9339</v>
+        <v>1.0722</v>
       </c>
       <c r="F35">
-        <v>4.563899999999999</v>
+        <v>4.702199999999999</v>
       </c>
       <c r="G35">
         <v>0.449</v>
@@ -4157,28 +4157,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M35">
-        <v>0.24416865</v>
+        <v>0.2515676999999999</v>
       </c>
       <c r="N35">
-        <v>2.04933135</v>
+        <v>2.0419323</v>
       </c>
       <c r="O35">
-        <v>0.3073997024999999</v>
+        <v>0.3062898449999999</v>
       </c>
       <c r="P35">
-        <v>1.7419316475</v>
+        <v>1.735642455</v>
       </c>
       <c r="Q35">
-        <v>2.6609316475</v>
+        <v>2.654642454999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1693779938017788</v>
+        <v>0.1710524122853761</v>
       </c>
       <c r="T35">
-        <v>0.7557876265195514</v>
+        <v>0.7660281615257144</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.393097762550598</v>
+        <v>9.116830181299109</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1283560921083482</v>
+        <v>0.1282221783695047</v>
       </c>
       <c r="C36">
-        <v>11.67083911766322</v>
+        <v>11.55107405352211</v>
       </c>
       <c r="D36">
-        <v>15.92403911766322</v>
+        <v>15.94257405352211</v>
       </c>
       <c r="E36">
-        <v>1.0722</v>
+        <v>1.2105</v>
       </c>
       <c r="F36">
-        <v>4.702199999999999</v>
+        <v>4.8405</v>
       </c>
       <c r="G36">
         <v>0.449</v>
@@ -4239,28 +4239,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M36">
-        <v>0.2515676999999999</v>
+        <v>0.25896675</v>
       </c>
       <c r="N36">
-        <v>2.0419323</v>
+        <v>2.03453325</v>
       </c>
       <c r="O36">
-        <v>0.3062898449999999</v>
+        <v>0.3051799874999999</v>
       </c>
       <c r="P36">
-        <v>1.735642455</v>
+        <v>1.7293532625</v>
       </c>
       <c r="Q36">
-        <v>2.654642454999999</v>
+        <v>2.6483532625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1710524122853761</v>
+        <v>0.1727783513376995</v>
       </c>
       <c r="T36">
-        <v>0.7660281615257144</v>
+        <v>0.7765837899166824</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.116830181299109</v>
+        <v>8.856349318976278</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1282221783695047</v>
+        <v>0.1280882646306611</v>
       </c>
       <c r="C37">
-        <v>11.55107405352211</v>
+        <v>11.43135218748945</v>
       </c>
       <c r="D37">
-        <v>15.94257405352211</v>
+        <v>15.96115218748945</v>
       </c>
       <c r="E37">
-        <v>1.2105</v>
+        <v>1.3488</v>
       </c>
       <c r="F37">
-        <v>4.8405</v>
+        <v>4.9788</v>
       </c>
       <c r="G37">
         <v>0.449</v>
@@ -4321,28 +4321,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M37">
-        <v>0.25896675</v>
+        <v>0.2663658</v>
       </c>
       <c r="N37">
-        <v>2.03453325</v>
+        <v>2.027134199999999</v>
       </c>
       <c r="O37">
-        <v>0.3051799874999999</v>
+        <v>0.3040701299999999</v>
       </c>
       <c r="P37">
-        <v>1.7293532625</v>
+        <v>1.72306407</v>
       </c>
       <c r="Q37">
-        <v>2.6483532625</v>
+        <v>2.64206407</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1727783513376995</v>
+        <v>0.174558225985408</v>
       </c>
       <c r="T37">
-        <v>0.7765837899166824</v>
+        <v>0.7874692816948681</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.856349318976278</v>
+        <v>8.610339615671379</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1280882646306611</v>
+        <v>0.1279543508918176</v>
       </c>
       <c r="C38">
-        <v>11.43135218748945</v>
+        <v>11.31167367075976</v>
       </c>
       <c r="D38">
-        <v>15.96115218748945</v>
+        <v>15.97977367075976</v>
       </c>
       <c r="E38">
-        <v>1.348799999999999</v>
+        <v>1.487099999999999</v>
       </c>
       <c r="F38">
-        <v>4.978799999999999</v>
+        <v>5.117099999999999</v>
       </c>
       <c r="G38">
         <v>0.449</v>
@@ -4403,28 +4403,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M38">
-        <v>0.2663657999999999</v>
+        <v>0.2737648499999999</v>
       </c>
       <c r="N38">
-        <v>2.027134199999999</v>
+        <v>2.019735149999999</v>
       </c>
       <c r="O38">
-        <v>0.3040701299999999</v>
+        <v>0.3029602724999999</v>
       </c>
       <c r="P38">
-        <v>1.72306407</v>
+        <v>1.716774877499999</v>
       </c>
       <c r="Q38">
-        <v>2.64206407</v>
+        <v>2.635774877499999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.174558225985408</v>
+        <v>0.1763946045901867</v>
       </c>
       <c r="T38">
-        <v>0.787469281694868</v>
+        <v>0.7987003446406151</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.610339615671382</v>
+        <v>8.377627734166747</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1279543508918176</v>
+        <v>0.127820437152974</v>
       </c>
       <c r="C39">
-        <v>11.31167367075976</v>
+        <v>11.19203865523393</v>
       </c>
       <c r="D39">
-        <v>15.97977367075976</v>
+        <v>15.99843865523393</v>
       </c>
       <c r="E39">
-        <v>1.487099999999999</v>
+        <v>1.6254</v>
       </c>
       <c r="F39">
-        <v>5.117099999999999</v>
+        <v>5.2554</v>
       </c>
       <c r="G39">
         <v>0.449</v>
@@ -4485,28 +4485,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M39">
-        <v>0.2737648499999999</v>
+        <v>0.2811639</v>
       </c>
       <c r="N39">
-        <v>2.019735149999999</v>
+        <v>2.012336099999999</v>
       </c>
       <c r="O39">
-        <v>0.3029602724999999</v>
+        <v>0.3018504149999999</v>
       </c>
       <c r="P39">
-        <v>1.716774877499999</v>
+        <v>1.710485684999999</v>
       </c>
       <c r="Q39">
-        <v>2.635774877499999</v>
+        <v>2.629485685</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1763946045901867</v>
+        <v>0.1782902212144743</v>
       </c>
       <c r="T39">
-        <v>0.7987003446406151</v>
+        <v>0.8102936999394509</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.377627734166747</v>
+        <v>8.157163846425519</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.127820437152974</v>
+        <v>0.1276865234141305</v>
       </c>
       <c r="C40">
-        <v>11.19203865523393</v>
+        <v>11.07244729352342</v>
       </c>
       <c r="D40">
-        <v>15.99843865523393</v>
+        <v>16.01714729352341</v>
       </c>
       <c r="E40">
-        <v>1.6254</v>
+        <v>1.7637</v>
       </c>
       <c r="F40">
-        <v>5.2554</v>
+        <v>5.3937</v>
       </c>
       <c r="G40">
         <v>0.449</v>
@@ -4567,28 +4567,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M40">
-        <v>0.2811639</v>
+        <v>0.28856295</v>
       </c>
       <c r="N40">
-        <v>2.012336099999999</v>
+        <v>2.00493705</v>
       </c>
       <c r="O40">
-        <v>0.3018504149999999</v>
+        <v>0.3007405574999999</v>
       </c>
       <c r="P40">
-        <v>1.710485684999999</v>
+        <v>1.7041964925</v>
       </c>
       <c r="Q40">
-        <v>2.629485685</v>
+        <v>2.6231964925</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1782902212144743</v>
+        <v>0.1802479892034926</v>
       </c>
       <c r="T40">
-        <v>0.8102936999394509</v>
+        <v>0.8222671652480845</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.157163846425519</v>
+        <v>7.948005799081274</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1276865234141305</v>
+        <v>0.127552609675287</v>
       </c>
       <c r="C41">
-        <v>11.07244729352342</v>
+        <v>10.95289973895436</v>
       </c>
       <c r="D41">
-        <v>16.01714729352341</v>
+        <v>16.03589973895436</v>
       </c>
       <c r="E41">
-        <v>1.7637</v>
+        <v>1.902000000000001</v>
       </c>
       <c r="F41">
-        <v>5.3937</v>
+        <v>5.532</v>
       </c>
       <c r="G41">
         <v>0.449</v>
@@ -4649,28 +4649,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M41">
-        <v>0.28856295</v>
+        <v>0.295962</v>
       </c>
       <c r="N41">
-        <v>2.00493705</v>
+        <v>1.997537999999999</v>
       </c>
       <c r="O41">
-        <v>0.3007405574999999</v>
+        <v>0.2996306999999999</v>
       </c>
       <c r="P41">
-        <v>1.7041964925</v>
+        <v>1.697907299999999</v>
       </c>
       <c r="Q41">
-        <v>2.6231964925</v>
+        <v>2.616907299999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1802479892034926</v>
+        <v>0.1822710161254783</v>
       </c>
       <c r="T41">
-        <v>0.8222671652480845</v>
+        <v>0.8346397460670061</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.948005799081274</v>
+        <v>7.749305654104241</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.127552609675287</v>
+        <v>0.1276974959364434</v>
       </c>
       <c r="C42">
-        <v>10.95289973895436</v>
+        <v>10.79431271373686</v>
       </c>
       <c r="D42">
-        <v>16.03589973895436</v>
+        <v>16.01561271373686</v>
       </c>
       <c r="E42">
-        <v>1.902000000000001</v>
+        <v>2.040300000000001</v>
       </c>
       <c r="F42">
-        <v>5.532</v>
+        <v>5.6703</v>
       </c>
       <c r="G42">
         <v>0.449</v>
@@ -4731,45 +4731,45 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M42">
-        <v>0.295962</v>
+        <v>0.30789729</v>
       </c>
       <c r="N42">
-        <v>1.997537999999999</v>
+        <v>1.985602709999999</v>
       </c>
       <c r="O42">
-        <v>0.2996306999999999</v>
+        <v>0.2978404064999999</v>
       </c>
       <c r="P42">
-        <v>1.697907299999999</v>
+        <v>1.6877623035</v>
       </c>
       <c r="Q42">
-        <v>2.616907299999999</v>
+        <v>2.6067623035</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1822710161254783</v>
+        <v>0.18436262023126</v>
       </c>
       <c r="T42">
-        <v>0.8346397460670061</v>
+        <v>0.8474317364052129</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.749305654104241</v>
+        <v>7.448912590299186</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1276974959364434</v>
+        <v>0.1275703821975999</v>
       </c>
       <c r="C43">
-        <v>10.79431271373686</v>
+        <v>10.6738084590199</v>
       </c>
       <c r="D43">
-        <v>16.01561271373686</v>
+        <v>16.0334084590199</v>
       </c>
       <c r="E43">
-        <v>2.040300000000001</v>
+        <v>2.178600000000001</v>
       </c>
       <c r="F43">
-        <v>5.6703</v>
+        <v>5.8086</v>
       </c>
       <c r="G43">
         <v>0.449</v>
@@ -4813,28 +4813,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M43">
-        <v>0.30789729</v>
+        <v>0.31540698</v>
       </c>
       <c r="N43">
-        <v>1.985602709999999</v>
+        <v>1.978093019999999</v>
       </c>
       <c r="O43">
-        <v>0.2978404064999999</v>
+        <v>0.2967139529999999</v>
       </c>
       <c r="P43">
-        <v>1.6877623035</v>
+        <v>1.681379067</v>
       </c>
       <c r="Q43">
-        <v>2.6067623035</v>
+        <v>2.600379067</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.18436262023126</v>
+        <v>0.1865263486165515</v>
       </c>
       <c r="T43">
-        <v>0.8474317364052129</v>
+        <v>0.8606648298585304</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.448912590299186</v>
+        <v>7.271557528625395</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1275703821975999</v>
+        <v>0.1274432684587563</v>
       </c>
       <c r="C44">
-        <v>10.6738084590199</v>
+        <v>10.55334379577356</v>
       </c>
       <c r="D44">
-        <v>16.0334084590199</v>
+        <v>16.05124379577356</v>
       </c>
       <c r="E44">
-        <v>2.1786</v>
+        <v>2.3169</v>
       </c>
       <c r="F44">
-        <v>5.808599999999999</v>
+        <v>5.946899999999999</v>
       </c>
       <c r="G44">
         <v>0.449</v>
@@ -4895,28 +4895,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M44">
-        <v>0.3154069799999999</v>
+        <v>0.32291667</v>
       </c>
       <c r="N44">
-        <v>1.97809302</v>
+        <v>1.97058333</v>
       </c>
       <c r="O44">
-        <v>0.2967139529999999</v>
+        <v>0.2955874994999999</v>
       </c>
       <c r="P44">
-        <v>1.681379067</v>
+        <v>1.6749958305</v>
       </c>
       <c r="Q44">
-        <v>2.600379067</v>
+        <v>2.5939958305</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1865263486165515</v>
+        <v>0.1887659972960637</v>
       </c>
       <c r="T44">
-        <v>0.8606648298585303</v>
+        <v>0.8743622423803853</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.271557528625396</v>
+        <v>7.102451539587596</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1274432684587563</v>
+        <v>0.1273161547199128</v>
       </c>
       <c r="C45">
-        <v>10.55334379577356</v>
+        <v>10.43291885626794</v>
       </c>
       <c r="D45">
-        <v>16.05124379577356</v>
+        <v>16.06911885626794</v>
       </c>
       <c r="E45">
-        <v>2.3169</v>
+        <v>2.4552</v>
       </c>
       <c r="F45">
-        <v>5.946899999999999</v>
+        <v>6.085199999999999</v>
       </c>
       <c r="G45">
         <v>0.449</v>
@@ -4977,28 +4977,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M45">
-        <v>0.32291667</v>
+        <v>0.33042636</v>
       </c>
       <c r="N45">
-        <v>1.97058333</v>
+        <v>1.96307364</v>
       </c>
       <c r="O45">
-        <v>0.2955874994999999</v>
+        <v>0.2944610459999999</v>
       </c>
       <c r="P45">
-        <v>1.6749958305</v>
+        <v>1.668612594</v>
       </c>
       <c r="Q45">
-        <v>2.5939958305</v>
+        <v>2.587612593999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1887659972960637</v>
+        <v>0.1910856334284157</v>
       </c>
       <c r="T45">
-        <v>0.8743622423803853</v>
+        <v>0.8885488482065921</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.102451539587596</v>
+        <v>6.941032186415151</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1273161547199128</v>
+        <v>0.1271890409810692</v>
       </c>
       <c r="C46">
-        <v>10.43291885626794</v>
+        <v>10.31253377336301</v>
       </c>
       <c r="D46">
-        <v>16.06911885626794</v>
+        <v>16.087033773363</v>
       </c>
       <c r="E46">
-        <v>2.4552</v>
+        <v>2.5935</v>
       </c>
       <c r="F46">
-        <v>6.085199999999999</v>
+        <v>6.2235</v>
       </c>
       <c r="G46">
         <v>0.449</v>
@@ -5059,28 +5059,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M46">
-        <v>0.33042636</v>
+        <v>0.33793605</v>
       </c>
       <c r="N46">
-        <v>1.96307364</v>
+        <v>1.955563949999999</v>
       </c>
       <c r="O46">
-        <v>0.2944610459999999</v>
+        <v>0.2933345924999999</v>
       </c>
       <c r="P46">
-        <v>1.668612594</v>
+        <v>1.6622293575</v>
       </c>
       <c r="Q46">
-        <v>2.587612593999999</v>
+        <v>2.5812293575</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1910856334284157</v>
+        <v>0.1934896199655804</v>
       </c>
       <c r="T46">
-        <v>0.8885488482065921</v>
+        <v>0.9032513306082974</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.941032186415151</v>
+        <v>6.786787026717036</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1271890409810692</v>
+        <v>0.1270619272422257</v>
       </c>
       <c r="C47">
-        <v>10.31253377336301</v>
+        <v>10.19218868051187</v>
       </c>
       <c r="D47">
-        <v>16.087033773363</v>
+        <v>16.10498868051186</v>
       </c>
       <c r="E47">
-        <v>2.5935</v>
+        <v>2.7318</v>
       </c>
       <c r="F47">
-        <v>6.2235</v>
+        <v>6.3618</v>
       </c>
       <c r="G47">
         <v>0.449</v>
@@ -5141,28 +5141,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M47">
-        <v>0.33793605</v>
+        <v>0.34544574</v>
       </c>
       <c r="N47">
-        <v>1.955563949999999</v>
+        <v>1.948054259999999</v>
       </c>
       <c r="O47">
-        <v>0.2933345924999999</v>
+        <v>0.2922081389999999</v>
       </c>
       <c r="P47">
-        <v>1.6622293575</v>
+        <v>1.655846121</v>
       </c>
       <c r="Q47">
-        <v>2.5812293575</v>
+        <v>2.574846120999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1934896199655804</v>
+        <v>0.1959826430411587</v>
       </c>
       <c r="T47">
-        <v>0.9032513306082974</v>
+        <v>0.9184983493952512</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.786787026717036</v>
+        <v>6.639248178310144</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1270619272422257</v>
+        <v>0.1269348135033822</v>
       </c>
       <c r="C48">
-        <v>10.19218868051187</v>
+        <v>10.07188371176409</v>
       </c>
       <c r="D48">
-        <v>16.10498868051186</v>
+        <v>16.12298371176409</v>
       </c>
       <c r="E48">
-        <v>2.7318</v>
+        <v>2.8701</v>
       </c>
       <c r="F48">
-        <v>6.3618</v>
+        <v>6.5001</v>
       </c>
       <c r="G48">
         <v>0.449</v>
@@ -5223,28 +5223,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M48">
-        <v>0.34544574</v>
+        <v>0.35295543</v>
       </c>
       <c r="N48">
-        <v>1.948054259999999</v>
+        <v>1.940544569999999</v>
       </c>
       <c r="O48">
-        <v>0.2922081389999999</v>
+        <v>0.2910816854999999</v>
       </c>
       <c r="P48">
-        <v>1.655846121</v>
+        <v>1.6494628845</v>
       </c>
       <c r="Q48">
-        <v>2.574846120999999</v>
+        <v>2.5684628845</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1959826430411587</v>
+        <v>0.1985697424592116</v>
       </c>
       <c r="T48">
-        <v>0.9184983493952512</v>
+        <v>0.9343207273817126</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.639248178310144</v>
+        <v>6.49798757877163</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1269348135033822</v>
+        <v>0.1268076997645386</v>
       </c>
       <c r="C49">
-        <v>10.07188371176409</v>
+        <v>9.951619001769057</v>
       </c>
       <c r="D49">
-        <v>16.12298371176409</v>
+        <v>16.14101900176906</v>
       </c>
       <c r="E49">
-        <v>2.8701</v>
+        <v>3.0084</v>
       </c>
       <c r="F49">
-        <v>6.5001</v>
+        <v>6.6384</v>
       </c>
       <c r="G49">
         <v>0.449</v>
@@ -5305,28 +5305,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M49">
-        <v>0.35295543</v>
+        <v>0.36046512</v>
       </c>
       <c r="N49">
-        <v>1.940544569999999</v>
+        <v>1.933034879999999</v>
       </c>
       <c r="O49">
-        <v>0.2910816854999999</v>
+        <v>0.2899552319999999</v>
       </c>
       <c r="P49">
-        <v>1.6494628845</v>
+        <v>1.643079648</v>
       </c>
       <c r="Q49">
-        <v>2.5684628845</v>
+        <v>2.562079648</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1985697424592116</v>
+        <v>0.2012563457010358</v>
       </c>
       <c r="T49">
-        <v>0.9343207273817126</v>
+        <v>0.9507516583676532</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.49798757877163</v>
+        <v>6.362612837547221</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1268076997645386</v>
+        <v>0.1266805860256951</v>
       </c>
       <c r="C50">
-        <v>9.951619001769059</v>
+        <v>9.831394685779273</v>
       </c>
       <c r="D50">
-        <v>16.14101900176906</v>
+        <v>16.15909468577927</v>
       </c>
       <c r="E50">
-        <v>3.0084</v>
+        <v>3.1467</v>
       </c>
       <c r="F50">
-        <v>6.638399999999999</v>
+        <v>6.776699999999999</v>
       </c>
       <c r="G50">
         <v>0.449</v>
@@ -5387,28 +5387,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M50">
-        <v>0.36046512</v>
+        <v>0.3679748099999999</v>
       </c>
       <c r="N50">
-        <v>1.933034879999999</v>
+        <v>1.925525189999999</v>
       </c>
       <c r="O50">
-        <v>0.2899552319999999</v>
+        <v>0.2888287784999999</v>
       </c>
       <c r="P50">
-        <v>1.643079648</v>
+        <v>1.6366964115</v>
       </c>
       <c r="Q50">
-        <v>2.562079648</v>
+        <v>2.5556964115</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2012563457010358</v>
+        <v>0.2040483059327354</v>
       </c>
       <c r="T50">
-        <v>0.9507516583676532</v>
+        <v>0.9678269395883365</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.362612837547221</v>
+        <v>6.232763595964625</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1266805860256951</v>
+        <v>0.1269784722868516</v>
       </c>
       <c r="C51">
-        <v>9.831394685779273</v>
+        <v>9.650798563758634</v>
       </c>
       <c r="D51">
-        <v>16.15909468577927</v>
+        <v>16.11679856375863</v>
       </c>
       <c r="E51">
-        <v>3.1467</v>
+        <v>3.285</v>
       </c>
       <c r="F51">
-        <v>6.776699999999999</v>
+        <v>6.914999999999999</v>
       </c>
       <c r="G51">
         <v>0.449</v>
@@ -5469,45 +5469,45 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M51">
-        <v>0.3679748099999999</v>
+        <v>0.3823994999999999</v>
       </c>
       <c r="N51">
-        <v>1.925525189999999</v>
+        <v>1.911100499999999</v>
       </c>
       <c r="O51">
-        <v>0.2888287784999999</v>
+        <v>0.2866650749999999</v>
       </c>
       <c r="P51">
-        <v>1.6366964115</v>
+        <v>1.624435424999999</v>
       </c>
       <c r="Q51">
-        <v>2.5556964115</v>
+        <v>2.543435424999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2040483059327354</v>
+        <v>0.2069519445737031</v>
       </c>
       <c r="T51">
-        <v>0.9678269395883365</v>
+        <v>0.9855852320578475</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.15</v>
       </c>
       <c r="W51">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.232763595964625</v>
+        <v>5.997654285635833</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1269784722868516</v>
+        <v>0.126859858548008</v>
       </c>
       <c r="C52">
-        <v>9.650798563758634</v>
+        <v>9.529313673265463</v>
       </c>
       <c r="D52">
-        <v>16.11679856375863</v>
+        <v>16.13361367326546</v>
       </c>
       <c r="E52">
-        <v>3.285</v>
+        <v>3.4233</v>
       </c>
       <c r="F52">
-        <v>6.914999999999999</v>
+        <v>7.053299999999999</v>
       </c>
       <c r="G52">
         <v>0.449</v>
@@ -5551,28 +5551,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M52">
-        <v>0.3823994999999999</v>
+        <v>0.39004749</v>
       </c>
       <c r="N52">
-        <v>1.911100499999999</v>
+        <v>1.903452509999999</v>
       </c>
       <c r="O52">
-        <v>0.2866650749999999</v>
+        <v>0.2855178764999999</v>
       </c>
       <c r="P52">
-        <v>1.624435424999999</v>
+        <v>1.6179346335</v>
       </c>
       <c r="Q52">
-        <v>2.543435424999999</v>
+        <v>2.5369346335</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2069519445737031</v>
+        <v>0.2099740990775673</v>
       </c>
       <c r="T52">
-        <v>0.9855852320578475</v>
+        <v>1.00406835279142</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.997654285635833</v>
+        <v>5.8800532212116</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.126859858548008</v>
+        <v>0.1267412448091645</v>
       </c>
       <c r="C53">
-        <v>9.529313673265463</v>
+        <v>9.407863906772077</v>
       </c>
       <c r="D53">
-        <v>16.13361367326546</v>
+        <v>16.15046390677207</v>
       </c>
       <c r="E53">
-        <v>3.4233</v>
+        <v>3.5616</v>
       </c>
       <c r="F53">
-        <v>7.053299999999999</v>
+        <v>7.191599999999999</v>
       </c>
       <c r="G53">
         <v>0.449</v>
@@ -5633,28 +5633,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M53">
-        <v>0.39004749</v>
+        <v>0.39769548</v>
       </c>
       <c r="N53">
-        <v>1.903452509999999</v>
+        <v>1.89580452</v>
       </c>
       <c r="O53">
-        <v>0.2855178764999999</v>
+        <v>0.2843706779999999</v>
       </c>
       <c r="P53">
-        <v>1.6179346335</v>
+        <v>1.611433842</v>
       </c>
       <c r="Q53">
-        <v>2.5369346335</v>
+        <v>2.530433842</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2099740990775673</v>
+        <v>0.2131221766857593</v>
       </c>
       <c r="T53">
-        <v>1.00406835279142</v>
+        <v>1.023321603555558</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.8800532212116</v>
+        <v>5.766975274649839</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1267412448091645</v>
+        <v>0.1266226310703209</v>
       </c>
       <c r="C54">
-        <v>9.407863906772077</v>
+        <v>9.286449374445937</v>
       </c>
       <c r="D54">
-        <v>16.15046390677207</v>
+        <v>16.16734937444593</v>
       </c>
       <c r="E54">
-        <v>3.5616</v>
+        <v>3.6999</v>
       </c>
       <c r="F54">
-        <v>7.191599999999999</v>
+        <v>7.329899999999999</v>
       </c>
       <c r="G54">
         <v>0.449</v>
@@ -5715,28 +5715,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M54">
-        <v>0.39769548</v>
+        <v>0.40534347</v>
       </c>
       <c r="N54">
-        <v>1.89580452</v>
+        <v>1.888156529999999</v>
       </c>
       <c r="O54">
-        <v>0.2843706779999999</v>
+        <v>0.2832234794999999</v>
       </c>
       <c r="P54">
-        <v>1.611433842</v>
+        <v>1.604933050499999</v>
       </c>
       <c r="Q54">
-        <v>2.530433842</v>
+        <v>2.523933050499999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2131221766857593</v>
+        <v>0.216404215043236</v>
       </c>
       <c r="T54">
-        <v>1.023321603555558</v>
+        <v>1.043394141586255</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.766975274649839</v>
+        <v>5.658164420411163</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1266226310703209</v>
+        <v>0.1265040173314773</v>
       </c>
       <c r="C55">
-        <v>9.286449374445937</v>
+        <v>9.165070186915699</v>
       </c>
       <c r="D55">
-        <v>16.16734937444593</v>
+        <v>16.1842701869157</v>
       </c>
       <c r="E55">
-        <v>3.6999</v>
+        <v>3.8382</v>
       </c>
       <c r="F55">
-        <v>7.329899999999999</v>
+        <v>7.4682</v>
       </c>
       <c r="G55">
         <v>0.449</v>
@@ -5797,28 +5797,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M55">
-        <v>0.40534347</v>
+        <v>0.41299146</v>
       </c>
       <c r="N55">
-        <v>1.888156529999999</v>
+        <v>1.880508539999999</v>
       </c>
       <c r="O55">
-        <v>0.2832234794999999</v>
+        <v>0.2820762809999999</v>
       </c>
       <c r="P55">
-        <v>1.604933050499999</v>
+        <v>1.598432259</v>
       </c>
       <c r="Q55">
-        <v>2.523933050499999</v>
+        <v>2.517432259</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.216404215043236</v>
+        <v>0.219828950720603</v>
       </c>
       <c r="T55">
-        <v>1.043394141586255</v>
+        <v>1.064339398661765</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.658164420411163</v>
+        <v>5.553383597810956</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1265040173314773</v>
+        <v>0.1263854035926338</v>
       </c>
       <c r="C56">
-        <v>9.165070186915699</v>
+        <v>9.043726455273646</v>
       </c>
       <c r="D56">
-        <v>16.1842701869157</v>
+        <v>16.20122645527364</v>
       </c>
       <c r="E56">
-        <v>3.8382</v>
+        <v>3.9765</v>
       </c>
       <c r="F56">
-        <v>7.4682</v>
+        <v>7.6065</v>
       </c>
       <c r="G56">
         <v>0.449</v>
@@ -5879,28 +5879,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M56">
-        <v>0.41299146</v>
+        <v>0.42063945</v>
       </c>
       <c r="N56">
-        <v>1.880508539999999</v>
+        <v>1.87286055</v>
       </c>
       <c r="O56">
-        <v>0.2820762809999999</v>
+        <v>0.2809290824999999</v>
       </c>
       <c r="P56">
-        <v>1.598432259</v>
+        <v>1.5919314675</v>
       </c>
       <c r="Q56">
-        <v>2.517432259</v>
+        <v>2.5109314675</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.219828950720603</v>
+        <v>0.2234058968725196</v>
       </c>
       <c r="T56">
-        <v>1.064339398661765</v>
+        <v>1.086215556051742</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.553383597810956</v>
+        <v>5.452412986941666</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1263854035926338</v>
+        <v>0.1262667898537903</v>
       </c>
       <c r="C57">
-        <v>9.043726455273646</v>
+        <v>8.922418291078118</v>
       </c>
       <c r="D57">
-        <v>16.20122645527364</v>
+        <v>16.21821829107812</v>
       </c>
       <c r="E57">
-        <v>3.9765</v>
+        <v>4.114800000000001</v>
       </c>
       <c r="F57">
-        <v>7.6065</v>
+        <v>7.7448</v>
       </c>
       <c r="G57">
         <v>0.449</v>
@@ -5961,28 +5961,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M57">
-        <v>0.42063945</v>
+        <v>0.42828744</v>
       </c>
       <c r="N57">
-        <v>1.87286055</v>
+        <v>1.865212559999999</v>
       </c>
       <c r="O57">
-        <v>0.2809290824999999</v>
+        <v>0.2797818839999999</v>
       </c>
       <c r="P57">
-        <v>1.5919314675</v>
+        <v>1.585430675999999</v>
       </c>
       <c r="Q57">
-        <v>2.5109314675</v>
+        <v>2.504430675999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2234058968725196</v>
+        <v>0.227145431485887</v>
       </c>
       <c r="T57">
-        <v>1.086215556051742</v>
+        <v>1.109086084232172</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.452412986941666</v>
+        <v>5.355048469317707</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1262667898537903</v>
+        <v>0.1261481761149467</v>
       </c>
       <c r="C58">
-        <v>8.922418291078118</v>
+        <v>8.801145806355962</v>
       </c>
       <c r="D58">
-        <v>16.21821829107812</v>
+        <v>16.23524580635596</v>
       </c>
       <c r="E58">
-        <v>4.114800000000001</v>
+        <v>4.2531</v>
       </c>
       <c r="F58">
-        <v>7.7448</v>
+        <v>7.8831</v>
       </c>
       <c r="G58">
         <v>0.449</v>
@@ -6043,28 +6043,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M58">
-        <v>0.42828744</v>
+        <v>0.43593543</v>
       </c>
       <c r="N58">
-        <v>1.865212559999999</v>
+        <v>1.857564569999999</v>
       </c>
       <c r="O58">
-        <v>0.2797818839999999</v>
+        <v>0.2786346854999999</v>
       </c>
       <c r="P58">
-        <v>1.585430675999999</v>
+        <v>1.578929884499999</v>
       </c>
       <c r="Q58">
-        <v>2.504430675999999</v>
+        <v>2.4979298845</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.227145431485887</v>
+        <v>0.2310588979417366</v>
       </c>
       <c r="T58">
-        <v>1.109086084232172</v>
+        <v>1.133020357909367</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.355048469317707</v>
+        <v>5.261100250557748</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1261481761149467</v>
+        <v>0.1260295623761032</v>
       </c>
       <c r="C59">
-        <v>8.801145806355962</v>
+        <v>8.67990911360496</v>
       </c>
       <c r="D59">
-        <v>16.23524580635596</v>
+        <v>16.25230911360496</v>
       </c>
       <c r="E59">
-        <v>4.2531</v>
+        <v>4.391400000000001</v>
       </c>
       <c r="F59">
-        <v>7.8831</v>
+        <v>8.0214</v>
       </c>
       <c r="G59">
         <v>0.449</v>
@@ -6125,28 +6125,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M59">
-        <v>0.43593543</v>
+        <v>0.44358342</v>
       </c>
       <c r="N59">
-        <v>1.857564569999999</v>
+        <v>1.849916579999999</v>
       </c>
       <c r="O59">
-        <v>0.2786346854999999</v>
+        <v>0.2774874869999999</v>
       </c>
       <c r="P59">
-        <v>1.578929884499999</v>
+        <v>1.572429093</v>
       </c>
       <c r="Q59">
-        <v>2.4979298845</v>
+        <v>2.491429093</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2310588979417366</v>
+        <v>0.2351587199431029</v>
       </c>
       <c r="T59">
-        <v>1.133020357909367</v>
+        <v>1.158094358904524</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.261100250557748</v>
+        <v>5.170391625548131</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1260295623761032</v>
+        <v>0.1259109486372597</v>
       </c>
       <c r="C60">
-        <v>8.679909113604962</v>
+        <v>8.558708325796369</v>
       </c>
       <c r="D60">
-        <v>16.25230911360496</v>
+        <v>16.26940832579637</v>
       </c>
       <c r="E60">
-        <v>4.391399999999999</v>
+        <v>4.5297</v>
       </c>
       <c r="F60">
-        <v>8.021399999999998</v>
+        <v>8.159699999999999</v>
       </c>
       <c r="G60">
         <v>0.449</v>
@@ -6207,28 +6207,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M60">
-        <v>0.4435834199999999</v>
+        <v>0.4512314099999999</v>
       </c>
       <c r="N60">
-        <v>1.849916579999999</v>
+        <v>1.84226859</v>
       </c>
       <c r="O60">
-        <v>0.2774874869999999</v>
+        <v>0.2763402884999999</v>
       </c>
       <c r="P60">
-        <v>1.572429093</v>
+        <v>1.5659283015</v>
       </c>
       <c r="Q60">
-        <v>2.491429093</v>
+        <v>2.4849283015</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2351587199431028</v>
+        <v>0.2394585332616089</v>
       </c>
       <c r="T60">
-        <v>1.158094358904523</v>
+        <v>1.184391481899443</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.170391625548132</v>
+        <v>5.08275786918291</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1259109486372597</v>
+        <v>0.1257923348984161</v>
       </c>
       <c r="C61">
-        <v>8.558708325796369</v>
+        <v>8.437543556377356</v>
       </c>
       <c r="D61">
-        <v>16.26940832579637</v>
+        <v>16.28654355637735</v>
       </c>
       <c r="E61">
-        <v>4.5297</v>
+        <v>4.667999999999999</v>
       </c>
       <c r="F61">
-        <v>8.159699999999999</v>
+        <v>8.297999999999998</v>
       </c>
       <c r="G61">
         <v>0.449</v>
@@ -6289,28 +6289,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M61">
-        <v>0.4512314099999999</v>
+        <v>0.4588793999999999</v>
       </c>
       <c r="N61">
-        <v>1.84226859</v>
+        <v>1.8346206</v>
       </c>
       <c r="O61">
-        <v>0.2763402884999999</v>
+        <v>0.2751930899999999</v>
       </c>
       <c r="P61">
-        <v>1.5659283015</v>
+        <v>1.55942751</v>
       </c>
       <c r="Q61">
-        <v>2.4849283015</v>
+        <v>2.47842751</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2394585332616089</v>
+        <v>0.2439733372460402</v>
       </c>
       <c r="T61">
-        <v>1.184391481899443</v>
+        <v>1.212003461044109</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.08275786918291</v>
+        <v>4.998045238029861</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1257923348984161</v>
+        <v>0.1256737211595725</v>
       </c>
       <c r="C62">
-        <v>8.437543556377356</v>
+        <v>8.316414919273541</v>
       </c>
       <c r="D62">
-        <v>16.28654355637735</v>
+        <v>16.30371491927354</v>
       </c>
       <c r="E62">
-        <v>4.667999999999999</v>
+        <v>4.8063</v>
       </c>
       <c r="F62">
-        <v>8.297999999999998</v>
+        <v>8.436299999999999</v>
       </c>
       <c r="G62">
         <v>0.449</v>
@@ -6371,28 +6371,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M62">
-        <v>0.4588793999999999</v>
+        <v>0.46652739</v>
       </c>
       <c r="N62">
-        <v>1.8346206</v>
+        <v>1.826972609999999</v>
       </c>
       <c r="O62">
-        <v>0.2751930899999999</v>
+        <v>0.2740458914999999</v>
       </c>
       <c r="P62">
-        <v>1.55942751</v>
+        <v>1.5529267185</v>
       </c>
       <c r="Q62">
-        <v>2.47842751</v>
+        <v>2.4719267185</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2439733372460402</v>
+        <v>0.2487196696399296</v>
       </c>
       <c r="T62">
-        <v>1.212003461044109</v>
+        <v>1.241031439119271</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.998045238029861</v>
+        <v>4.916110070193305</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1256737211595725</v>
+        <v>0.125555107420729</v>
       </c>
       <c r="C63">
-        <v>8.316414919273541</v>
+        <v>8.1953225288915</v>
       </c>
       <c r="D63">
-        <v>16.30371491927354</v>
+        <v>16.3209225288915</v>
       </c>
       <c r="E63">
-        <v>4.8063</v>
+        <v>4.944599999999999</v>
       </c>
       <c r="F63">
-        <v>8.436299999999999</v>
+        <v>8.574599999999998</v>
       </c>
       <c r="G63">
         <v>0.449</v>
@@ -6453,28 +6453,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M63">
-        <v>0.46652739</v>
+        <v>0.4741753799999999</v>
       </c>
       <c r="N63">
-        <v>1.826972609999999</v>
+        <v>1.81932462</v>
       </c>
       <c r="O63">
-        <v>0.2740458914999999</v>
+        <v>0.2728986929999999</v>
       </c>
       <c r="P63">
-        <v>1.5529267185</v>
+        <v>1.546425927</v>
       </c>
       <c r="Q63">
-        <v>2.4719267185</v>
+        <v>2.465425927</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2487196696399296</v>
+        <v>0.2537158090019185</v>
       </c>
       <c r="T63">
-        <v>1.241031439119271</v>
+        <v>1.271587205514179</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.916110070193305</v>
+        <v>4.836817972286962</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.125555107420729</v>
+        <v>0.1254364936818855</v>
       </c>
       <c r="C64">
-        <v>8.1953225288915</v>
+        <v>8.074266500121334</v>
       </c>
       <c r="D64">
-        <v>16.3209225288915</v>
+        <v>16.33816650012133</v>
       </c>
       <c r="E64">
-        <v>4.944599999999999</v>
+        <v>5.0829</v>
       </c>
       <c r="F64">
-        <v>8.574599999999998</v>
+        <v>8.712899999999999</v>
       </c>
       <c r="G64">
         <v>0.449</v>
@@ -6535,28 +6535,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M64">
-        <v>0.4741753799999999</v>
+        <v>0.48182337</v>
       </c>
       <c r="N64">
-        <v>1.81932462</v>
+        <v>1.81167663</v>
       </c>
       <c r="O64">
-        <v>0.2728986929999999</v>
+        <v>0.2717514944999999</v>
       </c>
       <c r="P64">
-        <v>1.546425927</v>
+        <v>1.5399251355</v>
       </c>
       <c r="Q64">
-        <v>2.465425927</v>
+        <v>2.458925135499999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2537158090019185</v>
+        <v>0.2589820099510418</v>
       </c>
       <c r="T64">
-        <v>1.271587205514179</v>
+        <v>1.303794634957459</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.836817972286962</v>
+        <v>4.760043083837962</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1254364936818855</v>
+        <v>0.1253178799430419</v>
       </c>
       <c r="C65">
-        <v>8.074266500121334</v>
+        <v>7.953246948339196</v>
       </c>
       <c r="D65">
-        <v>16.33816650012133</v>
+        <v>16.35544694833919</v>
       </c>
       <c r="E65">
-        <v>5.0829</v>
+        <v>5.2212</v>
       </c>
       <c r="F65">
-        <v>8.712899999999999</v>
+        <v>8.851199999999999</v>
       </c>
       <c r="G65">
         <v>0.449</v>
@@ -6617,28 +6617,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M65">
-        <v>0.48182337</v>
+        <v>0.48947136</v>
       </c>
       <c r="N65">
-        <v>1.81167663</v>
+        <v>1.804028639999999</v>
       </c>
       <c r="O65">
-        <v>0.2717514944999999</v>
+        <v>0.2706042959999999</v>
       </c>
       <c r="P65">
-        <v>1.5399251355</v>
+        <v>1.533424343999999</v>
       </c>
       <c r="Q65">
-        <v>2.458925135499999</v>
+        <v>2.452424344</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2589820099510418</v>
+        <v>0.2645407776195609</v>
       </c>
       <c r="T65">
-        <v>1.303794634957459</v>
+        <v>1.337791366036478</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.760043083837962</v>
+        <v>4.685667410652995</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1253178799430419</v>
+        <v>0.1251992662041984</v>
       </c>
       <c r="C66">
-        <v>7.953246948339196</v>
+        <v>7.832263989409878</v>
       </c>
       <c r="D66">
-        <v>16.35544694833919</v>
+        <v>16.37276398940988</v>
       </c>
       <c r="E66">
-        <v>5.2212</v>
+        <v>5.359500000000001</v>
       </c>
       <c r="F66">
-        <v>8.851199999999999</v>
+        <v>8.9895</v>
       </c>
       <c r="G66">
         <v>0.449</v>
@@ -6699,28 +6699,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M66">
-        <v>0.48947136</v>
+        <v>0.49711935</v>
       </c>
       <c r="N66">
-        <v>1.804028639999999</v>
+        <v>1.796380649999999</v>
       </c>
       <c r="O66">
-        <v>0.2706042959999999</v>
+        <v>0.2694570974999999</v>
       </c>
       <c r="P66">
-        <v>1.533424343999999</v>
+        <v>1.5269235525</v>
       </c>
       <c r="Q66">
-        <v>2.452424344</v>
+        <v>2.4459235525</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2645407776195609</v>
+        <v>0.2704171891548525</v>
       </c>
       <c r="T66">
-        <v>1.337791366036478</v>
+        <v>1.373730767462868</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.685667410652995</v>
+        <v>4.613580219719871</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1251992662041984</v>
+        <v>0.1250806524653549</v>
       </c>
       <c r="C67">
-        <v>7.832263989409878</v>
+        <v>7.711317739689404</v>
       </c>
       <c r="D67">
-        <v>16.37276398940988</v>
+        <v>16.3901177396894</v>
       </c>
       <c r="E67">
-        <v>5.359500000000001</v>
+        <v>5.4978</v>
       </c>
       <c r="F67">
-        <v>8.9895</v>
+        <v>9.127799999999999</v>
       </c>
       <c r="G67">
         <v>0.449</v>
@@ -6781,28 +6781,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M67">
-        <v>0.49711935</v>
+        <v>0.5047673399999999</v>
       </c>
       <c r="N67">
-        <v>1.796380649999999</v>
+        <v>1.78873266</v>
       </c>
       <c r="O67">
-        <v>0.2694570974999999</v>
+        <v>0.2683098989999999</v>
       </c>
       <c r="P67">
-        <v>1.5269235525</v>
+        <v>1.520422761</v>
       </c>
       <c r="Q67">
-        <v>2.4459235525</v>
+        <v>2.439422760999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2704171891548525</v>
+        <v>0.2766392719569261</v>
       </c>
       <c r="T67">
-        <v>1.373730767462868</v>
+        <v>1.411784251326106</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.613580219719871</v>
+        <v>4.543677489118055</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1250806524653549</v>
+        <v>0.1263857887265113</v>
       </c>
       <c r="C68">
-        <v>7.711317739689404</v>
+        <v>7.384071341480391</v>
       </c>
       <c r="D68">
-        <v>16.3901177396894</v>
+        <v>16.20117134148039</v>
       </c>
       <c r="E68">
-        <v>5.4978</v>
+        <v>5.636100000000001</v>
       </c>
       <c r="F68">
-        <v>9.127799999999999</v>
+        <v>9.2661</v>
       </c>
       <c r="G68">
         <v>0.449</v>
@@ -6863,45 +6863,45 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M68">
-        <v>0.5047673399999999</v>
+        <v>0.53558058</v>
       </c>
       <c r="N68">
-        <v>1.78873266</v>
+        <v>1.757919419999999</v>
       </c>
       <c r="O68">
-        <v>0.2683098989999999</v>
+        <v>0.2636879129999999</v>
       </c>
       <c r="P68">
-        <v>1.520422761</v>
+        <v>1.494231507</v>
       </c>
       <c r="Q68">
-        <v>2.439422760999999</v>
+        <v>2.413231507</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2766392719569261</v>
+        <v>0.2832384506863979</v>
       </c>
       <c r="T68">
-        <v>1.411784251326106</v>
+        <v>1.45214400693863</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.15</v>
       </c>
       <c r="W68">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.543677489118055</v>
+        <v>4.282268785772628</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1263857887265113</v>
+        <v>0.1262884249876677</v>
       </c>
       <c r="C69">
-        <v>7.384071341480391</v>
+        <v>7.259716324814502</v>
       </c>
       <c r="D69">
-        <v>16.20117134148039</v>
+        <v>16.2151163248145</v>
       </c>
       <c r="E69">
-        <v>5.636100000000001</v>
+        <v>5.7744</v>
       </c>
       <c r="F69">
-        <v>9.2661</v>
+        <v>9.404399999999999</v>
       </c>
       <c r="G69">
         <v>0.449</v>
@@ -6945,28 +6945,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M69">
-        <v>0.53558058</v>
+        <v>0.5435743199999999</v>
       </c>
       <c r="N69">
-        <v>1.757919419999999</v>
+        <v>1.74992568</v>
       </c>
       <c r="O69">
-        <v>0.2636879129999999</v>
+        <v>0.2624888519999999</v>
       </c>
       <c r="P69">
-        <v>1.494231507</v>
+        <v>1.487436828</v>
       </c>
       <c r="Q69">
-        <v>2.413231507</v>
+        <v>2.406436827999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2832384506863979</v>
+        <v>0.2902500780864617</v>
       </c>
       <c r="T69">
-        <v>1.45214400693863</v>
+        <v>1.495026247276938</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.282268785772628</v>
+        <v>4.219294244805383</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1262884249876677</v>
+        <v>0.1261910612488242</v>
       </c>
       <c r="C70">
-        <v>7.259716324814502</v>
+        <v>7.13538533481703</v>
       </c>
       <c r="D70">
-        <v>16.2151163248145</v>
+        <v>16.22908533481703</v>
       </c>
       <c r="E70">
-        <v>5.7744</v>
+        <v>5.912700000000001</v>
       </c>
       <c r="F70">
-        <v>9.404399999999999</v>
+        <v>9.5427</v>
       </c>
       <c r="G70">
         <v>0.449</v>
@@ -7027,28 +7027,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M70">
-        <v>0.5435743199999999</v>
+        <v>0.55156806</v>
       </c>
       <c r="N70">
-        <v>1.74992568</v>
+        <v>1.741931939999999</v>
       </c>
       <c r="O70">
-        <v>0.2624888519999999</v>
+        <v>0.2612897909999999</v>
       </c>
       <c r="P70">
-        <v>1.487436828</v>
+        <v>1.480642148999999</v>
       </c>
       <c r="Q70">
-        <v>2.406436827999999</v>
+        <v>2.399642149</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2902500780864617</v>
+        <v>0.2977140685445943</v>
       </c>
       <c r="T70">
-        <v>1.495026247276938</v>
+        <v>1.540675083766104</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.219294244805383</v>
+        <v>4.158145052851681</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1261910612488242</v>
+        <v>0.1260936975099807</v>
       </c>
       <c r="C71">
-        <v>7.13538533481703</v>
+        <v>7.011078433637062</v>
       </c>
       <c r="D71">
-        <v>16.22908533481703</v>
+        <v>16.24307843363706</v>
       </c>
       <c r="E71">
-        <v>5.912700000000001</v>
+        <v>6.051</v>
       </c>
       <c r="F71">
-        <v>9.5427</v>
+        <v>9.680999999999999</v>
       </c>
       <c r="G71">
         <v>0.449</v>
@@ -7109,28 +7109,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M71">
-        <v>0.55156806</v>
+        <v>0.5595618</v>
       </c>
       <c r="N71">
-        <v>1.741931939999999</v>
+        <v>1.733938199999999</v>
       </c>
       <c r="O71">
-        <v>0.2612897909999999</v>
+        <v>0.2600907299999999</v>
       </c>
       <c r="P71">
-        <v>1.480642148999999</v>
+        <v>1.473847469999999</v>
       </c>
       <c r="Q71">
-        <v>2.399642149</v>
+        <v>2.39284747</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2977140685445943</v>
+        <v>0.3056756583666023</v>
       </c>
       <c r="T71">
-        <v>1.540675083766104</v>
+        <v>1.589367176021214</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.158145052851681</v>
+        <v>4.098742980668086</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1260936975099807</v>
+        <v>0.1259963337711371</v>
       </c>
       <c r="C72">
-        <v>7.011078433637062</v>
+        <v>6.886795683638193</v>
       </c>
       <c r="D72">
-        <v>16.24307843363706</v>
+        <v>16.25709568363819</v>
       </c>
       <c r="E72">
-        <v>6.051</v>
+        <v>6.189300000000001</v>
       </c>
       <c r="F72">
-        <v>9.680999999999999</v>
+        <v>9.8193</v>
       </c>
       <c r="G72">
         <v>0.449</v>
@@ -7191,28 +7191,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M72">
-        <v>0.5595618</v>
+        <v>0.5675555400000001</v>
       </c>
       <c r="N72">
-        <v>1.733938199999999</v>
+        <v>1.725944459999999</v>
       </c>
       <c r="O72">
-        <v>0.2600907299999999</v>
+        <v>0.2588916689999999</v>
       </c>
       <c r="P72">
-        <v>1.473847469999999</v>
+        <v>1.467052791</v>
       </c>
       <c r="Q72">
-        <v>2.39284747</v>
+        <v>2.386052791</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3056756583666023</v>
+        <v>0.3141863233487489</v>
       </c>
       <c r="T72">
-        <v>1.589367176021214</v>
+        <v>1.641417343604263</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.098742980668086</v>
+        <v>4.041014206292479</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1259963337711371</v>
+        <v>0.1280409700322936</v>
       </c>
       <c r="C73">
-        <v>6.886795683638198</v>
+        <v>6.459123816917048</v>
       </c>
       <c r="D73">
-        <v>16.25709568363819</v>
+        <v>15.96772381691705</v>
       </c>
       <c r="E73">
-        <v>6.189299999999999</v>
+        <v>6.327599999999999</v>
       </c>
       <c r="F73">
-        <v>9.819299999999998</v>
+        <v>9.957599999999998</v>
       </c>
       <c r="G73">
         <v>0.449</v>
@@ -7273,45 +7273,45 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M73">
-        <v>0.56755554</v>
+        <v>0.6104008799999998</v>
       </c>
       <c r="N73">
-        <v>1.72594446</v>
+        <v>1.68309912</v>
       </c>
       <c r="O73">
-        <v>0.2588916689999999</v>
+        <v>0.252464868</v>
       </c>
       <c r="P73">
-        <v>1.467052791</v>
+        <v>1.430634252</v>
       </c>
       <c r="Q73">
-        <v>2.386052791</v>
+        <v>2.349634252</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3141863233487487</v>
+        <v>0.3233048929724771</v>
       </c>
       <c r="T73">
-        <v>1.641417343604262</v>
+        <v>1.697185380300386</v>
       </c>
       <c r="U73">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.15</v>
       </c>
       <c r="W73">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.04101420629248</v>
+        <v>3.757366798029518</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1280409700322936</v>
+        <v>0.1279733562934501</v>
       </c>
       <c r="C74">
-        <v>6.459123816917048</v>
+        <v>6.330228213988986</v>
       </c>
       <c r="D74">
-        <v>15.96772381691705</v>
+        <v>15.97712821398898</v>
       </c>
       <c r="E74">
-        <v>6.327599999999999</v>
+        <v>6.4659</v>
       </c>
       <c r="F74">
-        <v>9.957599999999998</v>
+        <v>10.0959</v>
       </c>
       <c r="G74">
         <v>0.449</v>
@@ -7355,28 +7355,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M74">
-        <v>0.6104008799999998</v>
+        <v>0.61887867</v>
       </c>
       <c r="N74">
-        <v>1.68309912</v>
+        <v>1.674621329999999</v>
       </c>
       <c r="O74">
-        <v>0.252464868</v>
+        <v>0.2511931994999999</v>
       </c>
       <c r="P74">
-        <v>1.430634252</v>
+        <v>1.4234281305</v>
       </c>
       <c r="Q74">
-        <v>2.349634252</v>
+        <v>2.3424281305</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3233048929724771</v>
+        <v>0.3330989121979631</v>
       </c>
       <c r="T74">
-        <v>1.697185380300386</v>
+        <v>1.757084382677704</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.757366798029518</v>
+        <v>3.705896019974318</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1279733562934501</v>
+        <v>0.1279057425546065</v>
       </c>
       <c r="C75">
-        <v>6.330228213988986</v>
+        <v>6.20134369527123</v>
       </c>
       <c r="D75">
-        <v>15.97712821398898</v>
+        <v>15.98654369527123</v>
       </c>
       <c r="E75">
-        <v>6.4659</v>
+        <v>6.604199999999999</v>
       </c>
       <c r="F75">
-        <v>10.0959</v>
+        <v>10.2342</v>
       </c>
       <c r="G75">
         <v>0.449</v>
@@ -7437,28 +7437,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M75">
-        <v>0.61887867</v>
+        <v>0.6273564599999999</v>
       </c>
       <c r="N75">
-        <v>1.674621329999999</v>
+        <v>1.66614354</v>
       </c>
       <c r="O75">
-        <v>0.2511931994999999</v>
+        <v>0.2499215309999999</v>
       </c>
       <c r="P75">
-        <v>1.4234281305</v>
+        <v>1.416222009</v>
       </c>
       <c r="Q75">
-        <v>2.3424281305</v>
+        <v>2.335222009</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3330989121979631</v>
+        <v>0.3436463175177173</v>
       </c>
       <c r="T75">
-        <v>1.757084382677704</v>
+        <v>1.821591000622508</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.705896019974318</v>
+        <v>3.65581634402872</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1279057425546065</v>
+        <v>0.127838128815763</v>
       </c>
       <c r="C76">
-        <v>6.20134369527123</v>
+        <v>6.072470280371444</v>
       </c>
       <c r="D76">
-        <v>15.98654369527123</v>
+        <v>15.99597028037144</v>
       </c>
       <c r="E76">
-        <v>6.604199999999999</v>
+        <v>6.7425</v>
       </c>
       <c r="F76">
-        <v>10.2342</v>
+        <v>10.3725</v>
       </c>
       <c r="G76">
         <v>0.449</v>
@@ -7519,28 +7519,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M76">
-        <v>0.6273564599999999</v>
+        <v>0.6358342499999999</v>
       </c>
       <c r="N76">
-        <v>1.66614354</v>
+        <v>1.65766575</v>
       </c>
       <c r="O76">
-        <v>0.2499215309999999</v>
+        <v>0.2486498624999999</v>
       </c>
       <c r="P76">
-        <v>1.416222009</v>
+        <v>1.4090158875</v>
       </c>
       <c r="Q76">
-        <v>2.335222009</v>
+        <v>2.328015887499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3436463175177173</v>
+        <v>0.3550375152630518</v>
       </c>
       <c r="T76">
-        <v>1.821591000622508</v>
+        <v>1.891258148002896</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.65581634402872</v>
+        <v>3.607072126108337</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.127838128815763</v>
+        <v>0.1277705150769194</v>
       </c>
       <c r="C77">
-        <v>6.072470280371444</v>
+        <v>5.943607988943562</v>
       </c>
       <c r="D77">
-        <v>15.99597028037144</v>
+        <v>16.00540798894356</v>
       </c>
       <c r="E77">
-        <v>6.7425</v>
+        <v>6.880800000000001</v>
       </c>
       <c r="F77">
-        <v>10.3725</v>
+        <v>10.5108</v>
       </c>
       <c r="G77">
         <v>0.449</v>
@@ -7601,28 +7601,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M77">
-        <v>0.6358342499999999</v>
+        <v>0.64431204</v>
       </c>
       <c r="N77">
-        <v>1.65766575</v>
+        <v>1.649187959999999</v>
       </c>
       <c r="O77">
-        <v>0.2486498624999999</v>
+        <v>0.2473781939999999</v>
       </c>
       <c r="P77">
-        <v>1.4090158875</v>
+        <v>1.401809766</v>
       </c>
       <c r="Q77">
-        <v>2.328015887499999</v>
+        <v>2.320809766</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3550375152630518</v>
+        <v>0.3673779794871643</v>
       </c>
       <c r="T77">
-        <v>1.891258148002896</v>
+        <v>1.966730890998317</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.607072126108337</v>
+        <v>3.559610650764806</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1277705150769194</v>
+        <v>0.1277029013380759</v>
       </c>
       <c r="C78">
-        <v>5.943607988943562</v>
+        <v>5.814756840687936</v>
       </c>
       <c r="D78">
-        <v>16.00540798894356</v>
+        <v>16.01485684068793</v>
       </c>
       <c r="E78">
-        <v>6.880800000000001</v>
+        <v>7.0191</v>
       </c>
       <c r="F78">
-        <v>10.5108</v>
+        <v>10.6491</v>
       </c>
       <c r="G78">
         <v>0.449</v>
@@ -7683,28 +7683,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M78">
-        <v>0.64431204</v>
+        <v>0.6527898299999999</v>
       </c>
       <c r="N78">
-        <v>1.649187959999999</v>
+        <v>1.64071017</v>
       </c>
       <c r="O78">
-        <v>0.2473781939999999</v>
+        <v>0.2461065254999999</v>
       </c>
       <c r="P78">
-        <v>1.401809766</v>
+        <v>1.3946036445</v>
       </c>
       <c r="Q78">
-        <v>2.320809766</v>
+        <v>2.3136036445</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3673779794871643</v>
+        <v>0.3807915275568516</v>
       </c>
       <c r="T78">
-        <v>1.966730890998317</v>
+        <v>2.048766481210731</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.559610650764806</v>
+        <v>3.513381941014614</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1277029013380759</v>
+        <v>0.1294916875992323</v>
       </c>
       <c r="C79">
-        <v>5.814756840687936</v>
+        <v>5.430177321791218</v>
       </c>
       <c r="D79">
-        <v>16.01485684068793</v>
+        <v>15.76857732179122</v>
       </c>
       <c r="E79">
-        <v>7.0191</v>
+        <v>7.157400000000001</v>
       </c>
       <c r="F79">
-        <v>10.6491</v>
+        <v>10.7874</v>
       </c>
       <c r="G79">
         <v>0.449</v>
@@ -7765,45 +7765,45 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M79">
-        <v>0.6527898299999999</v>
+        <v>0.69147234</v>
       </c>
       <c r="N79">
-        <v>1.64071017</v>
+        <v>1.602027659999999</v>
       </c>
       <c r="O79">
-        <v>0.2461065254999999</v>
+        <v>0.2403041489999999</v>
       </c>
       <c r="P79">
-        <v>1.3946036445</v>
+        <v>1.361723510999999</v>
       </c>
       <c r="Q79">
-        <v>2.3136036445</v>
+        <v>2.280723511</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3807915275568516</v>
+        <v>0.3954244890874197</v>
       </c>
       <c r="T79">
-        <v>2.048766481210731</v>
+        <v>2.138259852351546</v>
       </c>
       <c r="U79">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V79">
         <v>0.15</v>
       </c>
       <c r="W79">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.513381941014614</v>
+        <v>3.31683549337635</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1294916875992323</v>
+        <v>0.1294478738603888</v>
       </c>
       <c r="C80">
-        <v>5.430177321791218</v>
+        <v>5.29781905609341</v>
       </c>
       <c r="D80">
-        <v>15.76857732179122</v>
+        <v>15.77451905609341</v>
       </c>
       <c r="E80">
-        <v>7.157400000000001</v>
+        <v>7.2957</v>
       </c>
       <c r="F80">
-        <v>10.7874</v>
+        <v>10.9257</v>
       </c>
       <c r="G80">
         <v>0.449</v>
@@ -7847,28 +7847,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M80">
-        <v>0.69147234</v>
+        <v>0.70033737</v>
       </c>
       <c r="N80">
-        <v>1.602027659999999</v>
+        <v>1.593162629999999</v>
       </c>
       <c r="O80">
-        <v>0.2403041489999999</v>
+        <v>0.2389743944999999</v>
       </c>
       <c r="P80">
-        <v>1.361723510999999</v>
+        <v>1.3541882355</v>
       </c>
       <c r="Q80">
-        <v>2.280723511</v>
+        <v>2.2731882355</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3954244890874197</v>
+        <v>0.4114510660018513</v>
       </c>
       <c r="T80">
-        <v>2.138259852351546</v>
+        <v>2.236276401696248</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.31683549337635</v>
+        <v>3.274850233966523</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1294478738603888</v>
+        <v>0.1294040601215452</v>
       </c>
       <c r="C81">
-        <v>5.29781905609341</v>
+        <v>5.165465269875725</v>
       </c>
       <c r="D81">
-        <v>15.77451905609341</v>
+        <v>15.78046526987572</v>
       </c>
       <c r="E81">
-        <v>7.2957</v>
+        <v>7.434000000000001</v>
       </c>
       <c r="F81">
-        <v>10.9257</v>
+        <v>11.064</v>
       </c>
       <c r="G81">
         <v>0.449</v>
@@ -7929,28 +7929,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M81">
-        <v>0.70033737</v>
+        <v>0.7092024</v>
       </c>
       <c r="N81">
-        <v>1.593162629999999</v>
+        <v>1.584297599999999</v>
       </c>
       <c r="O81">
-        <v>0.2389743944999999</v>
+        <v>0.2376446399999999</v>
       </c>
       <c r="P81">
-        <v>1.3541882355</v>
+        <v>1.346652959999999</v>
       </c>
       <c r="Q81">
-        <v>2.2731882355</v>
+        <v>2.26565296</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4114510660018513</v>
+        <v>0.4290803006077262</v>
       </c>
       <c r="T81">
-        <v>2.236276401696248</v>
+        <v>2.344094605975421</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.274850233966523</v>
+        <v>3.233914606041941</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1294040601215452</v>
+        <v>0.1293602463827017</v>
       </c>
       <c r="C82">
-        <v>5.165465269875725</v>
+        <v>5.033115968205719</v>
       </c>
       <c r="D82">
-        <v>15.78046526987572</v>
+        <v>15.78641596820572</v>
       </c>
       <c r="E82">
-        <v>7.434000000000001</v>
+        <v>7.5723</v>
       </c>
       <c r="F82">
-        <v>11.064</v>
+        <v>11.2023</v>
       </c>
       <c r="G82">
         <v>0.449</v>
@@ -8011,28 +8011,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M82">
-        <v>0.7092024</v>
+        <v>0.71806743</v>
       </c>
       <c r="N82">
-        <v>1.584297599999999</v>
+        <v>1.575432569999999</v>
       </c>
       <c r="O82">
-        <v>0.2376446399999999</v>
+        <v>0.2363148854999999</v>
       </c>
       <c r="P82">
-        <v>1.346652959999999</v>
+        <v>1.339117684499999</v>
       </c>
       <c r="Q82">
-        <v>2.26565296</v>
+        <v>2.258117684499999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4290803006077262</v>
+        <v>0.4485652441194827</v>
       </c>
       <c r="T82">
-        <v>2.344094605975421</v>
+        <v>2.46326209491556</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.233914606041941</v>
+        <v>3.193989734362412</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1293602463827017</v>
+        <v>0.1293164326438581</v>
       </c>
       <c r="C83">
-        <v>5.033115968205719</v>
+        <v>4.900771156158578</v>
       </c>
       <c r="D83">
-        <v>15.78641596820572</v>
+        <v>15.79237115615858</v>
       </c>
       <c r="E83">
-        <v>7.5723</v>
+        <v>7.710600000000001</v>
       </c>
       <c r="F83">
-        <v>11.2023</v>
+        <v>11.3406</v>
       </c>
       <c r="G83">
         <v>0.449</v>
@@ -8093,28 +8093,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M83">
-        <v>0.71806743</v>
+        <v>0.7269324600000001</v>
       </c>
       <c r="N83">
-        <v>1.575432569999999</v>
+        <v>1.566567539999999</v>
       </c>
       <c r="O83">
-        <v>0.2363148854999999</v>
+        <v>0.2349851309999999</v>
       </c>
       <c r="P83">
-        <v>1.339117684499999</v>
+        <v>1.331582408999999</v>
       </c>
       <c r="Q83">
-        <v>2.258117684499999</v>
+        <v>2.250582409</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4485652441194827</v>
+        <v>0.4702151813547676</v>
       </c>
       <c r="T83">
-        <v>2.46326209491556</v>
+        <v>2.595670415960158</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.193989734362412</v>
+        <v>3.155038640040918</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1293164326438581</v>
+        <v>0.1292726189050146</v>
       </c>
       <c r="C84">
-        <v>4.900771156158578</v>
+        <v>4.768430838817139</v>
       </c>
       <c r="D84">
-        <v>15.79237115615858</v>
+        <v>15.79833083881714</v>
       </c>
       <c r="E84">
-        <v>7.710600000000001</v>
+        <v>7.8489</v>
       </c>
       <c r="F84">
-        <v>11.3406</v>
+        <v>11.4789</v>
       </c>
       <c r="G84">
         <v>0.449</v>
@@ -8175,28 +8175,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M84">
-        <v>0.7269324600000001</v>
+        <v>0.7357974900000001</v>
       </c>
       <c r="N84">
-        <v>1.566567539999999</v>
+        <v>1.557702509999999</v>
       </c>
       <c r="O84">
-        <v>0.2349851309999999</v>
+        <v>0.2336553764999999</v>
       </c>
       <c r="P84">
-        <v>1.331582408999999</v>
+        <v>1.3240471335</v>
       </c>
       <c r="Q84">
-        <v>2.250582409</v>
+        <v>2.2430471335</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4702151813547676</v>
+        <v>0.4944121700294979</v>
       </c>
       <c r="T84">
-        <v>2.595670415960158</v>
+        <v>2.743656186539414</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.155038640040918</v>
+        <v>3.117026126305486</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1292726189050146</v>
+        <v>0.1292288051661711</v>
       </c>
       <c r="C85">
-        <v>4.768430838817139</v>
+        <v>4.636095021271927</v>
       </c>
       <c r="D85">
-        <v>15.79833083881714</v>
+        <v>15.80429502127193</v>
       </c>
       <c r="E85">
-        <v>7.8489</v>
+        <v>7.987200000000001</v>
       </c>
       <c r="F85">
-        <v>11.4789</v>
+        <v>11.6172</v>
       </c>
       <c r="G85">
         <v>0.449</v>
@@ -8257,28 +8257,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M85">
-        <v>0.7357974900000001</v>
+        <v>0.7446625200000001</v>
       </c>
       <c r="N85">
-        <v>1.557702509999999</v>
+        <v>1.548837479999999</v>
       </c>
       <c r="O85">
-        <v>0.2336553764999999</v>
+        <v>0.2323256219999999</v>
       </c>
       <c r="P85">
-        <v>1.3240471335</v>
+        <v>1.316511857999999</v>
       </c>
       <c r="Q85">
-        <v>2.2430471335</v>
+        <v>2.235511858</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4944121700294979</v>
+        <v>0.5216337822885694</v>
       </c>
       <c r="T85">
-        <v>2.743656186539414</v>
+        <v>2.910140178441078</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.117026126305486</v>
+        <v>3.079918672420896</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1292288051661711</v>
+        <v>0.1291849914273275</v>
       </c>
       <c r="C86">
-        <v>4.636095021271929</v>
+        <v>4.503763708621157</v>
       </c>
       <c r="D86">
-        <v>15.80429502127193</v>
+        <v>15.81026370862116</v>
       </c>
       <c r="E86">
-        <v>7.9872</v>
+        <v>8.125499999999999</v>
       </c>
       <c r="F86">
-        <v>11.6172</v>
+        <v>11.7555</v>
       </c>
       <c r="G86">
         <v>0.449</v>
@@ -8339,28 +8339,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M86">
-        <v>0.74466252</v>
+        <v>0.7535275499999999</v>
       </c>
       <c r="N86">
-        <v>1.54883748</v>
+        <v>1.53997245</v>
       </c>
       <c r="O86">
-        <v>0.2323256219999999</v>
+        <v>0.2309958674999999</v>
       </c>
       <c r="P86">
-        <v>1.316511858</v>
+        <v>1.3089765825</v>
       </c>
       <c r="Q86">
-        <v>2.235511858</v>
+        <v>2.2279765825</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.521633782288569</v>
+        <v>0.5524849428488501</v>
       </c>
       <c r="T86">
-        <v>2.910140178441076</v>
+        <v>3.098822035929628</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.079918672420897</v>
+        <v>3.043684335098298</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1291849914273275</v>
+        <v>0.129141177688484</v>
       </c>
       <c r="C87">
-        <v>4.503763708621157</v>
+        <v>4.371436905970736</v>
       </c>
       <c r="D87">
-        <v>15.81026370862116</v>
+        <v>15.81623690597073</v>
       </c>
       <c r="E87">
-        <v>8.125499999999999</v>
+        <v>8.2638</v>
       </c>
       <c r="F87">
-        <v>11.7555</v>
+        <v>11.8938</v>
       </c>
       <c r="G87">
         <v>0.449</v>
@@ -8421,28 +8421,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M87">
-        <v>0.7535275499999999</v>
+        <v>0.76239258</v>
       </c>
       <c r="N87">
-        <v>1.53997245</v>
+        <v>1.531107419999999</v>
       </c>
       <c r="O87">
-        <v>0.2309958674999999</v>
+        <v>0.2296661129999999</v>
       </c>
       <c r="P87">
-        <v>1.3089765825</v>
+        <v>1.301441306999999</v>
       </c>
       <c r="Q87">
-        <v>2.2279765825</v>
+        <v>2.220441307</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5524849428488501</v>
+        <v>0.5877434120605998</v>
       </c>
       <c r="T87">
-        <v>3.098822035929628</v>
+        <v>3.314458444487973</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.043684335098298</v>
+        <v>3.008292656783202</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.129141177688484</v>
+        <v>0.1348654639496404</v>
       </c>
       <c r="C88">
-        <v>4.371436905970736</v>
+        <v>3.489163753018056</v>
       </c>
       <c r="D88">
-        <v>15.81623690597073</v>
+        <v>15.07226375301805</v>
       </c>
       <c r="E88">
-        <v>8.2638</v>
+        <v>8.402099999999999</v>
       </c>
       <c r="F88">
-        <v>11.8938</v>
+        <v>12.0321</v>
       </c>
       <c r="G88">
         <v>0.449</v>
@@ -8503,45 +8503,45 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M88">
-        <v>0.76239258</v>
+        <v>0.8651079899999999</v>
       </c>
       <c r="N88">
-        <v>1.531107419999999</v>
+        <v>1.42839201</v>
       </c>
       <c r="O88">
-        <v>0.2296661129999999</v>
+        <v>0.2142588014999999</v>
       </c>
       <c r="P88">
-        <v>1.301441306999999</v>
+        <v>1.2141332085</v>
       </c>
       <c r="Q88">
-        <v>2.220441307</v>
+        <v>2.133133208499999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5877434120605998</v>
+        <v>0.6284262611510801</v>
       </c>
       <c r="T88">
-        <v>3.314458444487973</v>
+        <v>3.563269685132217</v>
       </c>
       <c r="U88">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V88">
         <v>0.15</v>
       </c>
       <c r="W88">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.008292656783202</v>
+        <v>2.651114111198996</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1348654639496404</v>
+        <v>0.1348879502107969</v>
       </c>
       <c r="C89">
-        <v>3.489163753018056</v>
+        <v>3.348079246406302</v>
       </c>
       <c r="D89">
-        <v>15.07226375301805</v>
+        <v>15.0694792464063</v>
       </c>
       <c r="E89">
-        <v>8.402099999999999</v>
+        <v>8.5404</v>
       </c>
       <c r="F89">
-        <v>12.0321</v>
+        <v>12.1704</v>
       </c>
       <c r="G89">
         <v>0.449</v>
@@ -8585,28 +8585,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M89">
-        <v>0.8651079899999999</v>
+        <v>0.87505176</v>
       </c>
       <c r="N89">
-        <v>1.42839201</v>
+        <v>1.41844824</v>
       </c>
       <c r="O89">
-        <v>0.2142588014999999</v>
+        <v>0.2127672359999999</v>
       </c>
       <c r="P89">
-        <v>1.2141332085</v>
+        <v>1.205681004</v>
       </c>
       <c r="Q89">
-        <v>2.133133208499999</v>
+        <v>2.124681004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6284262611510801</v>
+        <v>0.6758895850899741</v>
       </c>
       <c r="T89">
-        <v>3.563269685132217</v>
+        <v>3.853549465883836</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.651114111198996</v>
+        <v>2.620987814480825</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1348879502107969</v>
+        <v>0.1349104364719533</v>
       </c>
       <c r="C90">
-        <v>3.348079246406302</v>
+        <v>3.20699576844493</v>
       </c>
       <c r="D90">
-        <v>15.0694792464063</v>
+        <v>15.06669576844493</v>
       </c>
       <c r="E90">
-        <v>8.5404</v>
+        <v>8.678699999999999</v>
       </c>
       <c r="F90">
-        <v>12.1704</v>
+        <v>12.3087</v>
       </c>
       <c r="G90">
         <v>0.449</v>
@@ -8667,28 +8667,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M90">
-        <v>0.87505176</v>
+        <v>0.88499553</v>
       </c>
       <c r="N90">
-        <v>1.41844824</v>
+        <v>1.40850447</v>
       </c>
       <c r="O90">
-        <v>0.2127672359999999</v>
+        <v>0.2112756704999999</v>
       </c>
       <c r="P90">
-        <v>1.205681004</v>
+        <v>1.1972287995</v>
       </c>
       <c r="Q90">
-        <v>2.124681004</v>
+        <v>2.1162287995</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6758895850899741</v>
+        <v>0.731982604290485</v>
       </c>
       <c r="T90">
-        <v>3.853549465883836</v>
+        <v>4.196607388590294</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.620987814480825</v>
+        <v>2.591538513194524</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1349104364719533</v>
+        <v>0.1349329227331098</v>
       </c>
       <c r="C91">
-        <v>3.20699576844493</v>
+        <v>3.065913318564037</v>
       </c>
       <c r="D91">
-        <v>15.06669576844493</v>
+        <v>15.06391331856404</v>
       </c>
       <c r="E91">
-        <v>8.678699999999999</v>
+        <v>8.817</v>
       </c>
       <c r="F91">
-        <v>12.3087</v>
+        <v>12.447</v>
       </c>
       <c r="G91">
         <v>0.449</v>
@@ -8749,28 +8749,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M91">
-        <v>0.88499553</v>
+        <v>0.8949393</v>
       </c>
       <c r="N91">
-        <v>1.40850447</v>
+        <v>1.3985607</v>
       </c>
       <c r="O91">
-        <v>0.2112756704999999</v>
+        <v>0.2097841049999999</v>
       </c>
       <c r="P91">
-        <v>1.1972287995</v>
+        <v>1.188776595</v>
       </c>
       <c r="Q91">
-        <v>2.1162287995</v>
+        <v>2.107776595</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.731982604290485</v>
+        <v>0.7992942273310982</v>
       </c>
       <c r="T91">
-        <v>4.196607388590294</v>
+        <v>4.608276895838045</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.591538513194524</v>
+        <v>2.562743640825696</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1349329227331098</v>
+        <v>0.1349554089942663</v>
       </c>
       <c r="C92">
-        <v>3.065913318564037</v>
+        <v>2.924831896194149</v>
       </c>
       <c r="D92">
-        <v>15.06391331856404</v>
+        <v>15.06113189619415</v>
       </c>
       <c r="E92">
-        <v>8.817</v>
+        <v>8.955299999999999</v>
       </c>
       <c r="F92">
-        <v>12.447</v>
+        <v>12.5853</v>
       </c>
       <c r="G92">
         <v>0.449</v>
@@ -8831,28 +8831,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M92">
-        <v>0.8949393</v>
+        <v>0.9048830699999999</v>
       </c>
       <c r="N92">
-        <v>1.3985607</v>
+        <v>1.38861693</v>
       </c>
       <c r="O92">
-        <v>0.2097841049999999</v>
+        <v>0.2082925394999999</v>
       </c>
       <c r="P92">
-        <v>1.188776595</v>
+        <v>1.1803243905</v>
       </c>
       <c r="Q92">
-        <v>2.107776595</v>
+        <v>2.0993243905</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7992942273310982</v>
+        <v>0.8815639888251809</v>
       </c>
       <c r="T92">
-        <v>4.608276895838045</v>
+        <v>5.111428515807517</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.562743640825696</v>
+        <v>2.534581622794644</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1349554089942663</v>
+        <v>0.1349778952554227</v>
       </c>
       <c r="C93">
-        <v>2.924831896194149</v>
+        <v>2.783751500766208</v>
       </c>
       <c r="D93">
-        <v>15.06113189619415</v>
+        <v>15.05835150076621</v>
       </c>
       <c r="E93">
-        <v>8.955299999999999</v>
+        <v>9.0936</v>
       </c>
       <c r="F93">
-        <v>12.5853</v>
+        <v>12.7236</v>
       </c>
       <c r="G93">
         <v>0.449</v>
@@ -8913,28 +8913,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M93">
-        <v>0.9048830699999999</v>
+        <v>0.91482684</v>
       </c>
       <c r="N93">
-        <v>1.38861693</v>
+        <v>1.37867316</v>
       </c>
       <c r="O93">
-        <v>0.2082925394999999</v>
+        <v>0.2068009739999999</v>
       </c>
       <c r="P93">
-        <v>1.1803243905</v>
+        <v>1.171872186</v>
       </c>
       <c r="Q93">
-        <v>2.0993243905</v>
+        <v>2.090872185999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8815639888251809</v>
+        <v>0.9844011906927845</v>
       </c>
       <c r="T93">
-        <v>5.111428515807517</v>
+        <v>5.740368040769358</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.534581622794644</v>
+        <v>2.507031822546876</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1349778952554227</v>
+        <v>0.1380833315165792</v>
       </c>
       <c r="C94">
-        <v>2.783751500766208</v>
+        <v>2.271083927817177</v>
       </c>
       <c r="D94">
-        <v>15.05835150076621</v>
+        <v>14.68398392781718</v>
       </c>
       <c r="E94">
-        <v>9.0936</v>
+        <v>9.2319</v>
       </c>
       <c r="F94">
-        <v>12.7236</v>
+        <v>12.8619</v>
       </c>
       <c r="G94">
         <v>0.449</v>
@@ -8995,45 +8995,45 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M94">
-        <v>0.91482684</v>
+        <v>0.97493202</v>
       </c>
       <c r="N94">
-        <v>1.37867316</v>
+        <v>1.318567979999999</v>
       </c>
       <c r="O94">
-        <v>0.2068009739999999</v>
+        <v>0.1977851969999999</v>
       </c>
       <c r="P94">
-        <v>1.171872186</v>
+        <v>1.120782782999999</v>
       </c>
       <c r="Q94">
-        <v>2.090872185999999</v>
+        <v>2.039782783</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9844011906927845</v>
+        <v>1.116620450236846</v>
       </c>
       <c r="T94">
-        <v>5.740368040769358</v>
+        <v>6.549004572863153</v>
       </c>
       <c r="U94">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V94">
         <v>0.15</v>
       </c>
       <c r="W94">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.507031822546876</v>
+        <v>2.352471713873958</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1380833315165792</v>
+        <v>0.1381389677777356</v>
       </c>
       <c r="C95">
-        <v>2.271083927817177</v>
+        <v>2.126246504363351</v>
       </c>
       <c r="D95">
-        <v>14.68398392781718</v>
+        <v>14.67744650436335</v>
       </c>
       <c r="E95">
-        <v>9.2319</v>
+        <v>9.370200000000001</v>
       </c>
       <c r="F95">
-        <v>12.8619</v>
+        <v>13.0002</v>
       </c>
       <c r="G95">
         <v>0.449</v>
@@ -9077,28 +9077,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M95">
-        <v>0.97493202</v>
+        <v>0.9854151600000001</v>
       </c>
       <c r="N95">
-        <v>1.318567979999999</v>
+        <v>1.308084839999999</v>
       </c>
       <c r="O95">
-        <v>0.1977851969999999</v>
+        <v>0.1962127259999999</v>
       </c>
       <c r="P95">
-        <v>1.120782782999999</v>
+        <v>1.111872113999999</v>
       </c>
       <c r="Q95">
-        <v>2.039782783</v>
+        <v>2.030872113999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.116620450236846</v>
+        <v>1.292912796295595</v>
       </c>
       <c r="T95">
-        <v>6.549004572863153</v>
+        <v>7.62718661565488</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.352471713873958</v>
+        <v>2.327445419045511</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1381389677777356</v>
+        <v>0.1381946040388921</v>
       </c>
       <c r="C96">
-        <v>2.126246504363351</v>
+        <v>1.98141489934229</v>
       </c>
       <c r="D96">
-        <v>14.67744650436335</v>
+        <v>14.67091489934229</v>
       </c>
       <c r="E96">
-        <v>9.370200000000001</v>
+        <v>9.5085</v>
       </c>
       <c r="F96">
-        <v>13.0002</v>
+        <v>13.1385</v>
       </c>
       <c r="G96">
         <v>0.449</v>
@@ -9159,28 +9159,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M96">
-        <v>0.9854151600000001</v>
+        <v>0.9958983</v>
       </c>
       <c r="N96">
-        <v>1.308084839999999</v>
+        <v>1.2976017</v>
       </c>
       <c r="O96">
-        <v>0.1962127259999999</v>
+        <v>0.1946402549999999</v>
       </c>
       <c r="P96">
-        <v>1.111872113999999</v>
+        <v>1.102961445</v>
       </c>
       <c r="Q96">
-        <v>2.030872113999999</v>
+        <v>2.021961445</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.292912796295595</v>
+        <v>1.539722080777844</v>
       </c>
       <c r="T96">
-        <v>7.62718661565488</v>
+        <v>9.136641475563302</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.327445419045511</v>
+        <v>2.302945993581874</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1381946040388921</v>
+        <v>0.1382502403000485</v>
       </c>
       <c r="C97">
-        <v>1.98141489934229</v>
+        <v>1.836589104989683</v>
       </c>
       <c r="D97">
-        <v>14.67091489934229</v>
+        <v>14.66438910498968</v>
       </c>
       <c r="E97">
-        <v>9.5085</v>
+        <v>9.646800000000001</v>
       </c>
       <c r="F97">
-        <v>13.1385</v>
+        <v>13.2768</v>
       </c>
       <c r="G97">
         <v>0.449</v>
@@ -9241,28 +9241,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M97">
-        <v>0.9958983</v>
+        <v>1.00638144</v>
       </c>
       <c r="N97">
-        <v>1.2976017</v>
+        <v>1.287118559999999</v>
       </c>
       <c r="O97">
-        <v>0.1946402549999999</v>
+        <v>0.1930677839999999</v>
       </c>
       <c r="P97">
-        <v>1.102961445</v>
+        <v>1.094050776</v>
       </c>
       <c r="Q97">
-        <v>2.021961445</v>
+        <v>2.013050776</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.539722080777844</v>
+        <v>1.909936007501217</v>
       </c>
       <c r="T97">
-        <v>9.136641475563302</v>
+        <v>11.40082376542593</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.302945993581874</v>
+        <v>2.278956972815396</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1382502403000486</v>
+        <v>0.138305876561205</v>
       </c>
       <c r="C98">
-        <v>1.836589104989681</v>
+        <v>1.691769113555011</v>
       </c>
       <c r="D98">
-        <v>14.66438910498968</v>
+        <v>14.65786911355501</v>
       </c>
       <c r="E98">
-        <v>9.646799999999999</v>
+        <v>9.785099999999998</v>
       </c>
       <c r="F98">
-        <v>13.2768</v>
+        <v>13.4151</v>
       </c>
       <c r="G98">
         <v>0.449</v>
@@ -9323,28 +9323,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M98">
-        <v>1.00638144</v>
+        <v>1.01686458</v>
       </c>
       <c r="N98">
-        <v>1.287118559999999</v>
+        <v>1.27663542</v>
       </c>
       <c r="O98">
-        <v>0.1930677839999999</v>
+        <v>0.1914953129999999</v>
       </c>
       <c r="P98">
-        <v>1.094050776</v>
+        <v>1.085140107</v>
       </c>
       <c r="Q98">
-        <v>2.013050776</v>
+        <v>2.004140107</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.909936007501212</v>
+        <v>2.526959218706831</v>
       </c>
       <c r="T98">
-        <v>11.4008237654259</v>
+        <v>15.17446091519694</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.278956972815396</v>
+        <v>2.255462571033795</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.138305876561205</v>
+        <v>0.1383615128223615</v>
       </c>
       <c r="C99">
-        <v>1.691769113555011</v>
+        <v>1.546954917301543</v>
       </c>
       <c r="D99">
-        <v>14.65786911355501</v>
+        <v>14.65135491730154</v>
       </c>
       <c r="E99">
-        <v>9.785099999999998</v>
+        <v>9.923399999999999</v>
       </c>
       <c r="F99">
-        <v>13.4151</v>
+        <v>13.5534</v>
       </c>
       <c r="G99">
         <v>0.449</v>
@@ -9405,28 +9405,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M99">
-        <v>1.01686458</v>
+        <v>1.02734772</v>
       </c>
       <c r="N99">
-        <v>1.27663542</v>
+        <v>1.26615228</v>
       </c>
       <c r="O99">
-        <v>0.1914953129999999</v>
+        <v>0.1899228419999999</v>
       </c>
       <c r="P99">
-        <v>1.085140107</v>
+        <v>1.076229438</v>
       </c>
       <c r="Q99">
-        <v>2.004140107</v>
+        <v>1.995229438</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.526959218706831</v>
+        <v>3.76100564111807</v>
       </c>
       <c r="T99">
-        <v>15.17446091519694</v>
+        <v>22.72173521473901</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.255462571033795</v>
+        <v>2.232447646839572</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1383615128223615</v>
+        <v>0.1384171490835179</v>
       </c>
       <c r="C100">
-        <v>1.546954917301543</v>
+        <v>1.402146508506288</v>
       </c>
       <c r="D100">
-        <v>14.65135491730154</v>
+        <v>14.64484650850629</v>
       </c>
       <c r="E100">
-        <v>9.923399999999999</v>
+        <v>10.0617</v>
       </c>
       <c r="F100">
-        <v>13.5534</v>
+        <v>13.6917</v>
       </c>
       <c r="G100">
         <v>0.449</v>
@@ -9487,28 +9487,28 @@
         <v>2.293499999999999</v>
       </c>
       <c r="M100">
-        <v>1.02734772</v>
+        <v>1.03783086</v>
       </c>
       <c r="N100">
-        <v>1.26615228</v>
+        <v>1.25566914</v>
       </c>
       <c r="O100">
-        <v>0.1899228419999999</v>
+        <v>0.1883503709999999</v>
       </c>
       <c r="P100">
-        <v>1.076229438</v>
+        <v>1.067318769</v>
       </c>
       <c r="Q100">
-        <v>1.995229438</v>
+        <v>1.986318769</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.76100564111807</v>
+        <v>7.463144908351786</v>
       </c>
       <c r="T100">
-        <v>22.72173521473901</v>
+        <v>45.36355811336521</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.232447646839572</v>
+        <v>2.20989767060887</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1384171490835179</v>
-      </c>
-      <c r="C101">
-        <v>1.402146508506288</v>
-      </c>
-      <c r="D101">
-        <v>14.64484650850629</v>
-      </c>
-      <c r="E101">
-        <v>10.0617</v>
-      </c>
-      <c r="F101">
-        <v>13.6917</v>
-      </c>
-      <c r="G101">
-        <v>0.449</v>
-      </c>
-      <c r="H101">
-        <v>10.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.212499999999999</v>
-      </c>
-      <c r="K101">
-        <v>0.919</v>
-      </c>
-      <c r="L101">
-        <v>2.293499999999999</v>
-      </c>
-      <c r="M101">
-        <v>1.03783086</v>
-      </c>
-      <c r="N101">
-        <v>1.25566914</v>
-      </c>
-      <c r="O101">
-        <v>0.1883503709999999</v>
-      </c>
-      <c r="P101">
-        <v>1.067318769</v>
-      </c>
-      <c r="Q101">
-        <v>1.986318769</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.463144908351786</v>
-      </c>
-      <c r="T101">
-        <v>45.36355811336521</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.06443</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.20989767060887</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
